--- a/data/k-props/2026-08-18.xlsx
+++ b/data/k-props/2026-08-18.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="95">
   <si>
     <t>date</t>
   </si>
@@ -133,166 +133,169 @@
     <t>08/18/2026</t>
   </si>
   <si>
+    <t>Carlos Rodón</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
     <t>Shane Baz</t>
   </si>
   <si>
-    <t>New York Yankees @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>6-7</t>
   </si>
   <si>
+    <t>Keider Montero</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Carson Whisenhunt</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t>Foster Griffin</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>José Soriano</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Cade Gibson</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Role unknown</t>
+  </si>
+  <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Ranger Suarez</t>
+  </si>
+  <si>
+    <t>Robbie Ray</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ New York Mets</t>
+  </si>
+  <si>
+    <t>Zac Thornton</t>
+  </si>
+  <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Athletics @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Tyler Mahle</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Zebby Matthews</t>
+  </si>
+  <si>
+    <t>Bryce Miller</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Kyle Harrison</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Cristian Javier</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Eric Lauer</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Ryan Feltner</t>
+  </si>
+  <si>
     <t>Carlos Rodon</t>
   </si>
   <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>Carson Whisenhunt</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Foster Griffin</t>
-  </si>
-  <si>
-    <t>Keider Montero</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t>Zack Wheeler</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
-    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
-  </si>
-  <si>
     <t>Jose Soriano</t>
   </si>
   <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Ranger Suarez</t>
-  </si>
-  <si>
-    <t>Robbie Ray</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ New York Mets</t>
-  </si>
-  <si>
     <t>Zach Thornton</t>
   </si>
   <si>
-    <t>Zebby Matthews</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>Jack Perkins</t>
-  </si>
-  <si>
-    <t>Athletics @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Kyle Harrison</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Bryce Miller</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Texas Rangers</t>
-  </si>
-  <si>
     <t>Jackson Kent</t>
   </si>
   <si>
     <t>George Klassen</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Cristian Javier</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Ryan Feltner</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Eric Lauer</t>
-  </si>
-  <si>
-    <t>Carlos Rodón</t>
-  </si>
-  <si>
-    <t>José Soriano</t>
-  </si>
-  <si>
-    <t>Cade Gibson</t>
-  </si>
-  <si>
-    <t>Role unknown</t>
-  </si>
-  <si>
-    <t>Zac Thornton</t>
   </si>
 </sst>
 </file>
@@ -805,15 +808,6 @@
       <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="C2">
-        <v>5.5</v>
-      </c>
-      <c r="D2">
-        <v>-148</v>
-      </c>
-      <c r="E2">
-        <v>122</v>
-      </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
@@ -824,7 +818,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -833,46 +827,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0.204</v>
+        <v>0.268</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P2">
-        <v>4.29</v>
+        <v>4.19</v>
       </c>
       <c r="Q2">
-        <v>0.1983</v>
+        <v>0.2832</v>
       </c>
       <c r="R2">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.276</v>
+        <v>0.2797</v>
       </c>
       <c r="U2">
-        <v>0.273</v>
+        <v>0.2455</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2449</v>
+        <v>0.2568</v>
       </c>
       <c r="X2">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y2">
-        <v>1.0166</v>
+        <v>1.033</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -881,22 +875,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>6.43</v>
+        <v>7.65</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2019</v>
+        <v>0.2735</v>
       </c>
       <c r="AG2">
-        <v>1.2571</v>
+        <v>1.256</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>6.43</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -907,31 +901,73 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D3">
         <v>-148</v>
       </c>
       <c r="E3">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" t="s">
-        <v>44</v>
+      <c r="G3">
+        <v>824803</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I3">
+        <v>5.8</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
       </c>
       <c r="L3">
         <v>6</v>
       </c>
+      <c r="M3">
+        <v>0.204</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>116</v>
+      </c>
+      <c r="P3">
+        <v>4.29</v>
+      </c>
+      <c r="Q3">
+        <v>0.1983</v>
+      </c>
+      <c r="R3">
+        <v>0.367</v>
+      </c>
       <c r="S3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T3">
+        <v>0.276</v>
+      </c>
+      <c r="U3">
+        <v>0.273</v>
+      </c>
+      <c r="V3">
+        <v>9</v>
+      </c>
+      <c r="W3">
+        <v>0.2449</v>
+      </c>
+      <c r="X3">
+        <v>0.2227</v>
+      </c>
+      <c r="Y3">
+        <v>1.0166</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -939,8 +975,23 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
+      <c r="AD3">
+        <v>6.34</v>
+      </c>
       <c r="AE3" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="AF3">
+        <v>0.2019</v>
+      </c>
+      <c r="AG3">
+        <v>1.2394</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>6.34</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -948,28 +999,28 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-108</v>
+        <v>-119</v>
       </c>
       <c r="E4">
-        <v>-105</v>
+        <v>110</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4">
-        <v>824475</v>
+        <v>823341</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -981,43 +1032,43 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>0.1765</v>
+        <v>0.167</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="P4">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>0.1488</v>
+        <v>0.1379</v>
       </c>
       <c r="R4">
-        <v>0.377</v>
+        <v>0.367</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2048</v>
+        <v>0.2109</v>
       </c>
       <c r="U4">
-        <v>0.1939</v>
+        <v>0.2349</v>
       </c>
       <c r="V4">
         <v>8</v>
       </c>
       <c r="W4">
-        <v>0.1828</v>
+        <v>0.2358</v>
       </c>
       <c r="X4">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y4">
-        <v>0.9696</v>
+        <v>1.0215</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1026,22 +1077,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="AE4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF4">
-        <v>0.166</v>
+        <v>0.1563</v>
       </c>
       <c r="AG4">
-        <v>0.9329</v>
+        <v>0.947</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1049,28 +1100,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>5.5</v>
       </c>
       <c r="D5">
-        <v>121</v>
+        <v>-120</v>
       </c>
       <c r="E5">
-        <v>-135</v>
+        <v>107</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5">
-        <v>824475</v>
+        <v>823341</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1082,43 +1133,43 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>0.2108</v>
+        <v>0.27</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="P5">
-        <v>4.24</v>
+        <v>4.06</v>
       </c>
       <c r="Q5">
-        <v>0.2727</v>
+        <v>0.2389</v>
       </c>
       <c r="R5">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2608</v>
+        <v>0.1846</v>
       </c>
       <c r="U5">
-        <v>0.2682</v>
+        <v>0.1885</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2552</v>
+        <v>0.2235</v>
       </c>
       <c r="X5">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y5">
-        <v>1.036</v>
+        <v>0.9584</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1127,22 +1178,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.2</v>
+        <v>4.92</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="AF5">
-        <v>0.2328</v>
+        <v>0.2588</v>
       </c>
       <c r="AG5">
-        <v>1.1878</v>
+        <v>0.8291</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>6.2</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1150,7 +1201,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1162,7 +1213,7 @@
         <v>-106</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6">
         <v>824398</v>
@@ -1201,13 +1252,13 @@
         <v>0.349</v>
       </c>
       <c r="S6" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="T6">
-        <v>0.2161</v>
+        <v>0.1978</v>
       </c>
       <c r="U6">
-        <v>0.1981</v>
+        <v>0.1959</v>
       </c>
       <c r="V6">
         <v>9</v>
@@ -1216,10 +1267,10 @@
         <v>0.2259</v>
       </c>
       <c r="X6">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y6">
-        <v>0.9584</v>
+        <v>0.9198</v>
       </c>
       <c r="AA6" t="s">
         <v>44</v>
@@ -1228,22 +1279,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF6">
         <v>0.1754</v>
       </c>
       <c r="AG6">
-        <v>0.9842</v>
+        <v>0.8882</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>3.58</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1251,7 +1302,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>5.5</v>
@@ -1263,7 +1314,7 @@
         <v>-108</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G7">
         <v>824398</v>
@@ -1302,25 +1353,25 @@
         <v>0.377</v>
       </c>
       <c r="S7" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="T7">
-        <v>0.2088</v>
+        <v>0.2291</v>
       </c>
       <c r="U7">
-        <v>0.2058</v>
+        <v>0.2316</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>0.2271</v>
       </c>
       <c r="X7">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y7">
-        <v>0.9638</v>
+        <v>1.0041</v>
       </c>
       <c r="AA7" t="s">
         <v>44</v>
@@ -1329,22 +1380,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.06</v>
+        <v>4.57</v>
       </c>
       <c r="AE7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF7">
         <v>0.1877</v>
       </c>
       <c r="AG7">
-        <v>0.9509</v>
+        <v>1.0289</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.06</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1352,28 +1403,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D8">
-        <v>-119</v>
+        <v>121</v>
       </c>
       <c r="E8">
-        <v>110</v>
+        <v>-135</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8">
-        <v>823341</v>
+        <v>824475</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1385,43 +1436,43 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>0.167</v>
+        <v>0.2108</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>4.24</v>
       </c>
       <c r="Q8">
-        <v>0.1379</v>
+        <v>0.2727</v>
       </c>
       <c r="R8">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2109</v>
+        <v>0.2608</v>
       </c>
       <c r="U8">
-        <v>0.2349</v>
+        <v>0.2682</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2358</v>
+        <v>0.2552</v>
       </c>
       <c r="X8">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y8">
-        <v>1.0215</v>
+        <v>1.036</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1430,22 +1481,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.51</v>
+        <v>6.12</v>
       </c>
       <c r="AE8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF8">
-        <v>0.1563</v>
+        <v>0.2328</v>
       </c>
       <c r="AG8">
-        <v>0.9606</v>
+        <v>1.1711</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.51</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1453,28 +1504,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C9">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D9">
-        <v>-120</v>
+        <v>-108</v>
       </c>
       <c r="E9">
-        <v>107</v>
+        <v>-105</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9">
-        <v>823341</v>
+        <v>824475</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1486,43 +1537,43 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>0.27</v>
+        <v>0.1765</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="P9">
-        <v>4.06</v>
+        <v>4.35</v>
       </c>
       <c r="Q9">
-        <v>0.2389</v>
+        <v>0.1488</v>
       </c>
       <c r="R9">
-        <v>0.361</v>
+        <v>0.377</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.1846</v>
+        <v>0.2048</v>
       </c>
       <c r="U9">
-        <v>0.1885</v>
+        <v>0.1939</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>0.2235</v>
+        <v>0.1828</v>
       </c>
       <c r="X9">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y9">
-        <v>0.9584</v>
+        <v>0.9696</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1531,22 +1582,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.99</v>
+        <v>3.42</v>
       </c>
       <c r="AE9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF9">
-        <v>0.2588</v>
+        <v>0.166</v>
       </c>
       <c r="AG9">
-        <v>0.841</v>
+        <v>0.9198</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.99</v>
+        <v>3.42</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1554,28 +1605,19 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-      <c r="D10">
-        <v>115</v>
-      </c>
-      <c r="E10">
-        <v>-137</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>823423</v>
+        <v>822938</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1584,46 +1626,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0.3018</v>
+        <v>0.2423</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="P10">
-        <v>3.94</v>
+        <v>4.14</v>
       </c>
       <c r="Q10">
-        <v>0.2929</v>
+        <v>0.1776</v>
       </c>
       <c r="R10">
-        <v>0.331</v>
+        <v>0.349</v>
       </c>
       <c r="S10" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="T10">
-        <v>0.2372</v>
+        <v>0.1843</v>
       </c>
       <c r="U10">
-        <v>0.2276</v>
+        <v>0.1802</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2114</v>
+        <v>0.1897</v>
       </c>
       <c r="X10">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y10">
-        <v>0.9685</v>
+        <v>0.88</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1632,22 +1674,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>7.1</v>
+        <v>3.69</v>
       </c>
       <c r="AE10" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="AF10">
-        <v>0.2988</v>
+        <v>0.2197</v>
       </c>
       <c r="AG10">
-        <v>1.0803</v>
+        <v>0.8274</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>7.1</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1655,7 +1697,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>3.5</v>
@@ -1667,7 +1709,7 @@
         <v>-113</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G11">
         <v>822938</v>
@@ -1721,7 +1763,7 @@
         <v>0.19</v>
       </c>
       <c r="X11">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y11">
         <v>0.987</v>
@@ -1733,22 +1775,22 @@
         <v>44</v>
       </c>
       <c r="AD11">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="AE11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF11">
         <v>0.1366</v>
       </c>
       <c r="AG11">
-        <v>0.889</v>
+        <v>0.8764</v>
       </c>
       <c r="AH11">
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1758,32 +1800,53 @@
       <c r="B12" t="s">
         <v>62</v>
       </c>
-      <c r="C12">
+      <c r="F12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12">
+        <v>823423</v>
+      </c>
+      <c r="H12" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12">
         <v>4.5</v>
       </c>
-      <c r="D12">
-        <v>110</v>
-      </c>
-      <c r="E12">
-        <v>-135</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" t="s">
-        <v>44</v>
-      </c>
-      <c r="H12" t="s">
-        <v>44</v>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0.1859</v>
+      </c>
+      <c r="P12">
+        <v>4.63</v>
       </c>
       <c r="S12" t="s">
-        <v>44</v>
-      </c>
-      <c r="V12" t="s">
-        <v>44</v>
+        <v>54</v>
+      </c>
+      <c r="T12">
+        <v>0.1753</v>
+      </c>
+      <c r="U12">
+        <v>0.1771</v>
+      </c>
+      <c r="V12">
+        <v>9</v>
+      </c>
+      <c r="W12">
+        <v>0.233</v>
+      </c>
+      <c r="X12">
+        <v>0.2227</v>
+      </c>
+      <c r="Y12">
+        <v>0.9664</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1791,8 +1854,23 @@
       <c r="AC12" t="s">
         <v>44</v>
       </c>
+      <c r="AD12">
+        <v>2.95</v>
+      </c>
       <c r="AE12" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="AF12">
+        <v>0.1859</v>
+      </c>
+      <c r="AG12">
+        <v>0.7873</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>2.95</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1800,28 +1878,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
+        <v>65</v>
+      </c>
+      <c r="C13">
+        <v>7.5</v>
+      </c>
+      <c r="D13">
+        <v>115</v>
+      </c>
+      <c r="E13">
+        <v>-137</v>
+      </c>
+      <c r="F13" t="s">
         <v>63</v>
       </c>
-      <c r="C13">
-        <v>3.5</v>
-      </c>
-      <c r="D13">
-        <v>-135</v>
-      </c>
-      <c r="E13">
-        <v>108</v>
-      </c>
-      <c r="F13" t="s">
-        <v>64</v>
-      </c>
       <c r="G13">
-        <v>824723</v>
+        <v>823423</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1833,43 +1911,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.1513</v>
+        <v>0.3018</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="P13">
-        <v>4.34</v>
+        <v>3.94</v>
       </c>
       <c r="Q13">
-        <v>0.1818</v>
+        <v>0.2929</v>
       </c>
       <c r="R13">
-        <v>0.355</v>
+        <v>0.331</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2053</v>
+        <v>0.2372</v>
       </c>
       <c r="U13">
-        <v>0.1912</v>
+        <v>0.2276</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2168</v>
+        <v>0.2114</v>
       </c>
       <c r="X13">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y13">
-        <v>0.9813</v>
+        <v>0.9685</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1878,22 +1956,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>3.67</v>
+        <v>7</v>
       </c>
       <c r="AE13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AF13">
-        <v>0.1621</v>
+        <v>0.2988</v>
       </c>
       <c r="AG13">
-        <v>0.9352</v>
+        <v>1.0651</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>3.67</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1901,19 +1979,19 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C14">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D14">
-        <v>-112</v>
+        <v>-135</v>
       </c>
       <c r="E14">
-        <v>-102</v>
+        <v>108</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>824723</v>
@@ -1922,7 +2000,7 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -1934,43 +2012,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.2472</v>
+        <v>0.1513</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="P14">
-        <v>4.12</v>
+        <v>4.34</v>
       </c>
       <c r="Q14">
-        <v>0.2143</v>
+        <v>0.1818</v>
       </c>
       <c r="R14">
-        <v>0.296</v>
+        <v>0.355</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
       </c>
       <c r="T14">
-        <v>0.1728</v>
+        <v>0.2053</v>
       </c>
       <c r="U14">
-        <v>0.1733</v>
+        <v>0.1912</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.1751</v>
+        <v>0.2168</v>
       </c>
       <c r="X14">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y14">
-        <v>0.9042</v>
+        <v>0.9813</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -1979,22 +2057,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
       <c r="AE14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF14">
-        <v>0.2375</v>
+        <v>0.1621</v>
       </c>
       <c r="AG14">
-        <v>0.7872</v>
+        <v>0.922</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>3.58</v>
+        <v>3.61</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2002,28 +2080,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C15">
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>-114</v>
+        <v>-112</v>
       </c>
       <c r="E15">
-        <v>101</v>
+        <v>-102</v>
       </c>
       <c r="F15" t="s">
         <v>67</v>
       </c>
       <c r="G15">
-        <v>823586</v>
+        <v>824723</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2035,43 +2113,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.204</v>
+        <v>0.2472</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="P15">
-        <v>4.21</v>
+        <v>4.12</v>
       </c>
       <c r="Q15">
-        <v>0.2072</v>
+        <v>0.2143</v>
       </c>
       <c r="R15">
-        <v>0.357</v>
+        <v>0.296</v>
       </c>
       <c r="S15" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="T15">
-        <v>0.2516</v>
+        <v>0.2613</v>
       </c>
       <c r="U15">
-        <v>0.2451</v>
+        <v>0.1821</v>
       </c>
       <c r="V15">
         <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2325</v>
+        <v>0.1751</v>
       </c>
       <c r="X15">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y15">
-        <v>0.9795</v>
+        <v>0.88</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2080,22 +2158,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.28</v>
+        <v>5.19</v>
       </c>
       <c r="AE15" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF15">
-        <v>0.2051</v>
+        <v>0.2375</v>
       </c>
       <c r="AG15">
-        <v>1.146</v>
+        <v>1.1731</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.28</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2103,34 +2181,76 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C16">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D16">
-        <v>-122</v>
+        <v>-114</v>
       </c>
       <c r="E16">
-        <v>-101</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
-        <v>67</v>
-      </c>
-      <c r="G16" t="s">
-        <v>44</v>
+        <v>70</v>
+      </c>
+      <c r="G16">
+        <v>823586</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I16">
+        <v>5.4</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
       </c>
       <c r="L16">
         <v>6</v>
       </c>
+      <c r="M16">
+        <v>0.204</v>
+      </c>
+      <c r="N16">
+        <v>5</v>
+      </c>
+      <c r="O16">
+        <v>111</v>
+      </c>
+      <c r="P16">
+        <v>4.21</v>
+      </c>
+      <c r="Q16">
+        <v>0.2072</v>
+      </c>
+      <c r="R16">
+        <v>0.357</v>
+      </c>
       <c r="S16" t="s">
-        <v>44</v>
-      </c>
-      <c r="V16" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T16">
+        <v>0.2516</v>
+      </c>
+      <c r="U16">
+        <v>0.2451</v>
+      </c>
+      <c r="V16">
+        <v>9</v>
+      </c>
+      <c r="W16">
+        <v>0.2325</v>
+      </c>
+      <c r="X16">
+        <v>0.2227</v>
+      </c>
+      <c r="Y16">
+        <v>0.9795</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2138,8 +2258,23 @@
       <c r="AC16" t="s">
         <v>44</v>
       </c>
+      <c r="AD16">
+        <v>5.2</v>
+      </c>
       <c r="AE16" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="AF16">
+        <v>0.2051</v>
+      </c>
+      <c r="AG16">
+        <v>1.1298</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>5.2</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2147,22 +2282,13 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
-      </c>
-      <c r="C17">
-        <v>4.5</v>
-      </c>
-      <c r="D17">
-        <v>115</v>
-      </c>
-      <c r="E17">
-        <v>-130</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s">
         <v>70</v>
       </c>
       <c r="G17">
-        <v>823667</v>
+        <v>823586</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
@@ -2177,46 +2303,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>0.199</v>
+        <v>0.1638</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q17">
-        <v>0.2054</v>
+        <v>0.1273</v>
       </c>
       <c r="R17">
-        <v>0.359</v>
+        <v>0.355</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2372</v>
+        <v>0.1552</v>
       </c>
       <c r="U17">
-        <v>0.2298</v>
+        <v>0.1736</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2179</v>
+        <v>0.2187</v>
       </c>
       <c r="X17">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y17">
-        <v>0.996</v>
+        <v>0.9935</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2225,22 +2351,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>5.24</v>
+        <v>2.31</v>
       </c>
       <c r="AE17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF17">
-        <v>0.2013</v>
+        <v>0.1509</v>
       </c>
       <c r="AG17">
-        <v>1.0804</v>
+        <v>0.6969</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>5.24</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2248,28 +2374,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D18">
-        <v>-122</v>
+        <v>-140</v>
       </c>
       <c r="E18">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G18">
-        <v>823667</v>
+        <v>824075</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2281,43 +2407,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2344</v>
+        <v>0.25</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P18">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q18">
-        <v>0.2883</v>
+        <v>0.1964</v>
       </c>
       <c r="R18">
-        <v>0.357</v>
+        <v>0.359</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2014</v>
+        <v>0.2031</v>
       </c>
       <c r="U18">
-        <v>0.2005</v>
+        <v>0.209</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2114</v>
+        <v>0.2096</v>
       </c>
       <c r="X18">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y18">
-        <v>0.9824</v>
+        <v>0.9784</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2326,22 +2452,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>5.12</v>
+        <v>4.37</v>
       </c>
       <c r="AE18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF18">
-        <v>0.2536</v>
+        <v>0.2308</v>
       </c>
       <c r="AG18">
-        <v>0.9174</v>
+        <v>0.9121</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>5.12</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2349,28 +2475,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C19">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D19">
-        <v>-140</v>
+        <v>-122</v>
       </c>
       <c r="E19">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G19">
-        <v>824075</v>
+        <v>823667</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2382,43 +2508,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.25</v>
+        <v>0.2344</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P19">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q19">
-        <v>0.1964</v>
+        <v>0.2883</v>
       </c>
       <c r="R19">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2031</v>
+        <v>0.2014</v>
       </c>
       <c r="U19">
-        <v>0.209</v>
+        <v>0.2005</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2096</v>
+        <v>0.2114</v>
       </c>
       <c r="X19">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y19">
-        <v>0.9784</v>
+        <v>0.9824</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2427,22 +2553,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.43</v>
+        <v>5.05</v>
       </c>
       <c r="AE19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF19">
-        <v>0.2308</v>
+        <v>0.2536</v>
       </c>
       <c r="AG19">
-        <v>0.9251</v>
+        <v>0.9044</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.43</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2450,28 +2576,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C20">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D20">
-        <v>-155</v>
+        <v>115</v>
       </c>
       <c r="E20">
-        <v>128</v>
+        <v>-130</v>
       </c>
       <c r="F20" t="s">
         <v>75</v>
       </c>
       <c r="G20">
-        <v>823749</v>
+        <v>823667</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2483,43 +2609,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.2969</v>
+        <v>0.199</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="P20">
-        <v>4.11</v>
+        <v>4.25</v>
       </c>
       <c r="Q20">
-        <v>0.2872</v>
+        <v>0.2054</v>
       </c>
       <c r="R20">
-        <v>0.32</v>
+        <v>0.359</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2086</v>
+        <v>0.2372</v>
       </c>
       <c r="U20">
-        <v>0.1968</v>
+        <v>0.2298</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2395</v>
+        <v>0.2179</v>
       </c>
       <c r="X20">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y20">
-        <v>1.0092</v>
+        <v>0.996</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2528,22 +2654,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>5.69</v>
+        <v>5.16</v>
       </c>
       <c r="AE20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF20">
-        <v>0.2938</v>
+        <v>0.2013</v>
       </c>
       <c r="AG20">
-        <v>0.9499</v>
+        <v>1.0652</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>5.69</v>
+        <v>5.16</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2551,7 +2677,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C21">
         <v>5.5</v>
@@ -2563,7 +2689,7 @@
         <v>-140</v>
       </c>
       <c r="F21" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G21">
         <v>823749</v>
@@ -2617,7 +2743,7 @@
         <v>0.2155</v>
       </c>
       <c r="X21">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y21">
         <v>1.0057</v>
@@ -2629,22 +2755,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
       <c r="AE21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF21">
         <v>0.2207</v>
       </c>
       <c r="AG21">
-        <v>1.0735</v>
+        <v>1.0583</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.3</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2652,28 +2778,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C22">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D22">
-        <v>123</v>
+        <v>-155</v>
       </c>
       <c r="E22">
-        <v>-135</v>
+        <v>128</v>
       </c>
       <c r="F22" t="s">
         <v>78</v>
       </c>
       <c r="G22">
-        <v>824639</v>
+        <v>823749</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2685,43 +2811,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2347</v>
+        <v>0.2969</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="P22">
-        <v>4.23</v>
+        <v>4.11</v>
       </c>
       <c r="Q22">
-        <v>0.1864</v>
+        <v>0.2872</v>
       </c>
       <c r="R22">
-        <v>0.371</v>
+        <v>0.32</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2258</v>
+        <v>0.2086</v>
       </c>
       <c r="U22">
-        <v>0.2444</v>
+        <v>0.1968</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2368</v>
+        <v>0.2395</v>
       </c>
       <c r="X22">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y22">
-        <v>1.0402</v>
+        <v>1.0092</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2730,22 +2856,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.45</v>
+        <v>5.61</v>
       </c>
       <c r="AE22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF22">
-        <v>0.2168</v>
+        <v>0.2938</v>
       </c>
       <c r="AG22">
-        <v>1.0283</v>
+        <v>0.9365</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.45</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2753,7 +2879,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23">
         <v>3.5</v>
@@ -2765,7 +2891,7 @@
         <v>-109</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G23">
         <v>822859</v>
@@ -2819,7 +2945,7 @@
         <v>0.2076</v>
       </c>
       <c r="X23">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y23">
         <v>0.9941</v>
@@ -2831,22 +2957,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="AE23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF23">
         <v>0.1733</v>
       </c>
       <c r="AG23">
-        <v>0.949</v>
+        <v>0.9356</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2854,34 +2980,76 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="D24">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="E24">
-        <v>-151</v>
+        <v>-135</v>
       </c>
       <c r="F24" t="s">
-        <v>80</v>
-      </c>
-      <c r="G24" t="s">
-        <v>44</v>
+        <v>83</v>
+      </c>
+      <c r="G24">
+        <v>824639</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I24">
+        <v>5.6</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
+      <c r="M24">
+        <v>0.2347</v>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24">
+        <v>118</v>
+      </c>
+      <c r="P24">
+        <v>4.23</v>
+      </c>
+      <c r="Q24">
+        <v>0.1864</v>
+      </c>
+      <c r="R24">
+        <v>0.371</v>
+      </c>
       <c r="S24" t="s">
-        <v>44</v>
-      </c>
-      <c r="V24" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T24">
+        <v>0.2258</v>
+      </c>
+      <c r="U24">
+        <v>0.2444</v>
+      </c>
+      <c r="V24">
+        <v>9</v>
+      </c>
+      <c r="W24">
+        <v>0.2368</v>
+      </c>
+      <c r="X24">
+        <v>0.2227</v>
+      </c>
+      <c r="Y24">
+        <v>1.0402</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2889,8 +3057,23 @@
       <c r="AC24" t="s">
         <v>44</v>
       </c>
+      <c r="AD24">
+        <v>5.38</v>
+      </c>
       <c r="AE24" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="AF24">
+        <v>0.2168</v>
+      </c>
+      <c r="AG24">
+        <v>1.0138</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>5.38</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2898,34 +3081,76 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C25">
         <v>4.5</v>
       </c>
       <c r="D25">
-        <v>120</v>
+        <v>-113</v>
       </c>
       <c r="E25">
-        <v>-148</v>
+        <v>100</v>
       </c>
       <c r="F25" t="s">
-        <v>83</v>
-      </c>
-      <c r="G25" t="s">
-        <v>44</v>
+        <v>85</v>
+      </c>
+      <c r="G25">
+        <v>824154</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>86</v>
+      </c>
+      <c r="I25">
+        <v>3.9</v>
+      </c>
+      <c r="J25" t="b">
+        <v>0</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
       </c>
       <c r="L25">
         <v>6</v>
       </c>
+      <c r="M25">
+        <v>0.1678</v>
+      </c>
+      <c r="N25">
+        <v>5</v>
+      </c>
+      <c r="O25">
+        <v>91</v>
+      </c>
+      <c r="P25">
+        <v>4.61</v>
+      </c>
+      <c r="Q25">
+        <v>0.1209</v>
+      </c>
+      <c r="R25">
+        <v>0.313</v>
+      </c>
       <c r="S25" t="s">
-        <v>44</v>
-      </c>
-      <c r="V25" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T25">
+        <v>0.266</v>
+      </c>
+      <c r="U25">
+        <v>0.2573</v>
+      </c>
+      <c r="V25">
+        <v>9</v>
+      </c>
+      <c r="W25">
+        <v>0.2504</v>
+      </c>
+      <c r="X25">
+        <v>0.2227</v>
+      </c>
+      <c r="Y25">
+        <v>1.0381</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -2933,8 +3158,23 @@
       <c r="AC25" t="s">
         <v>44</v>
       </c>
+      <c r="AD25">
+        <v>3.4</v>
+      </c>
       <c r="AE25" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="AF25">
+        <v>0.1531</v>
+      </c>
+      <c r="AG25">
+        <v>1.1946</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>3.4</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -2942,28 +3182,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C26">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D26">
-        <v>-113</v>
+        <v>-120</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>-102</v>
       </c>
       <c r="F26" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G26">
-        <v>824154</v>
+        <v>824319</v>
       </c>
       <c r="H26" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="I26">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -2975,43 +3215,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1678</v>
+        <v>0.1514</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="P26">
-        <v>4.61</v>
+        <v>4.23</v>
       </c>
       <c r="Q26">
-        <v>0.1209</v>
+        <v>0.1624</v>
       </c>
       <c r="R26">
-        <v>0.313</v>
+        <v>0.369</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.266</v>
+        <v>0.2216</v>
       </c>
       <c r="U26">
-        <v>0.2573</v>
+        <v>0.2193</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2504</v>
+        <v>0.247</v>
       </c>
       <c r="X26">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y26">
-        <v>1.0381</v>
+        <v>1.0013</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3020,22 +3260,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
       <c r="AE26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF26">
-        <v>0.1531</v>
+        <v>0.1555</v>
       </c>
       <c r="AG26">
-        <v>1.2117</v>
+        <v>0.9952</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>3.45</v>
+        <v>3.37</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3043,7 +3283,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C27">
         <v>3.5</v>
@@ -3055,7 +3295,7 @@
         <v>-139</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G27">
         <v>824319</v>
@@ -3109,7 +3349,7 @@
         <v>0.2061</v>
       </c>
       <c r="X27">
-        <v>0.2196</v>
+        <v>0.2227</v>
       </c>
       <c r="Y27">
         <v>1.0055</v>
@@ -3121,22 +3361,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="AE27" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF27">
         <v>0.1458</v>
       </c>
       <c r="AG27">
-        <v>1.2675</v>
+        <v>1.2496</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3144,76 +3384,34 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C28">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D28">
-        <v>-120</v>
+        <v>-148</v>
       </c>
       <c r="E28">
-        <v>-102</v>
+        <v>127</v>
       </c>
       <c r="F28" t="s">
-        <v>87</v>
-      </c>
-      <c r="G28">
-        <v>824319</v>
+        <v>41</v>
+      </c>
+      <c r="G28" t="s">
+        <v>44</v>
       </c>
       <c r="H28" t="s">
-        <v>42</v>
-      </c>
-      <c r="I28">
-        <v>5.1</v>
-      </c>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L28">
         <v>6</v>
       </c>
-      <c r="M28">
-        <v>0.1514</v>
-      </c>
-      <c r="N28">
-        <v>5</v>
-      </c>
-      <c r="O28">
-        <v>117</v>
-      </c>
-      <c r="P28">
-        <v>4.23</v>
-      </c>
-      <c r="Q28">
-        <v>0.1624</v>
-      </c>
-      <c r="R28">
-        <v>0.369</v>
-      </c>
       <c r="S28" t="s">
-        <v>43</v>
-      </c>
-      <c r="T28">
-        <v>0.2216</v>
-      </c>
-      <c r="U28">
-        <v>0.2193</v>
-      </c>
-      <c r="V28">
-        <v>9</v>
-      </c>
-      <c r="W28">
-        <v>0.247</v>
-      </c>
-      <c r="X28">
-        <v>0.2196</v>
-      </c>
-      <c r="Y28">
-        <v>1.0013</v>
+        <v>44</v>
+      </c>
+      <c r="V28" t="s">
+        <v>44</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3221,23 +3419,8 @@
       <c r="AC28" t="s">
         <v>44</v>
       </c>
-      <c r="AD28">
-        <v>3.42</v>
-      </c>
       <c r="AE28" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF28">
-        <v>0.1555</v>
-      </c>
-      <c r="AG28">
-        <v>1.0095</v>
-      </c>
-      <c r="AH28">
-        <v>0</v>
-      </c>
-      <c r="AM28">
-        <v>3.42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3245,67 +3428,34 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="C29">
+        <v>4.5</v>
+      </c>
+      <c r="D29">
+        <v>110</v>
+      </c>
+      <c r="E29">
+        <v>-135</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
-      </c>
-      <c r="G29">
-        <v>824803</v>
+        <v>60</v>
+      </c>
+      <c r="G29" t="s">
+        <v>44</v>
       </c>
       <c r="H29" t="s">
-        <v>42</v>
-      </c>
-      <c r="I29">
-        <v>5.1</v>
-      </c>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L29">
-        <v>0</v>
-      </c>
-      <c r="M29">
-        <v>0.268</v>
-      </c>
-      <c r="N29">
-        <v>5</v>
-      </c>
-      <c r="O29">
-        <v>113</v>
-      </c>
-      <c r="P29">
-        <v>4.19</v>
-      </c>
-      <c r="Q29">
-        <v>0.2832</v>
-      </c>
-      <c r="R29">
-        <v>0.361</v>
+        <v>6</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
-      </c>
-      <c r="T29">
-        <v>0.2797</v>
-      </c>
-      <c r="U29">
-        <v>0.2455</v>
-      </c>
-      <c r="V29">
-        <v>9</v>
-      </c>
-      <c r="W29">
-        <v>0.2568</v>
-      </c>
-      <c r="X29">
-        <v>0.2196</v>
-      </c>
-      <c r="Y29">
-        <v>1.033</v>
+        <v>44</v>
+      </c>
+      <c r="V29" t="s">
+        <v>44</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3313,23 +3463,8 @@
       <c r="AC29" t="s">
         <v>44</v>
       </c>
-      <c r="AD29">
-        <v>7.76</v>
-      </c>
       <c r="AE29" t="s">
-        <v>59</v>
-      </c>
-      <c r="AF29">
-        <v>0.2735</v>
-      </c>
-      <c r="AG29">
-        <v>1.274</v>
-      </c>
-      <c r="AH29">
-        <v>0</v>
-      </c>
-      <c r="AM29">
-        <v>7.76</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3337,67 +3472,34 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>92</v>
+      </c>
+      <c r="C30">
+        <v>3.5</v>
+      </c>
+      <c r="D30">
+        <v>-122</v>
+      </c>
+      <c r="E30">
+        <v>-101</v>
       </c>
       <c r="F30" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30">
-        <v>822938</v>
+        <v>70</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
-      </c>
-      <c r="I30">
-        <v>5.6</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0.2423</v>
-      </c>
-      <c r="N30">
-        <v>5</v>
-      </c>
-      <c r="O30">
-        <v>107</v>
-      </c>
-      <c r="P30">
-        <v>4.14</v>
-      </c>
-      <c r="Q30">
-        <v>0.1776</v>
-      </c>
-      <c r="R30">
-        <v>0.349</v>
+        <v>6</v>
       </c>
       <c r="S30" t="s">
-        <v>43</v>
-      </c>
-      <c r="T30">
-        <v>0.1804</v>
-      </c>
-      <c r="U30">
-        <v>0.1772</v>
-      </c>
-      <c r="V30">
-        <v>9</v>
-      </c>
-      <c r="W30">
-        <v>0.1897</v>
-      </c>
-      <c r="X30">
-        <v>0.2196</v>
-      </c>
-      <c r="Y30">
-        <v>0.9191</v>
+        <v>44</v>
+      </c>
+      <c r="V30" t="s">
+        <v>44</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3405,23 +3507,8 @@
       <c r="AC30" t="s">
         <v>44</v>
       </c>
-      <c r="AD30">
-        <v>3.82</v>
-      </c>
       <c r="AE30" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF30">
-        <v>0.2197</v>
-      </c>
-      <c r="AG30">
-        <v>0.8218</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>3.82</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3429,55 +3516,34 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="C31">
+        <v>4.5</v>
+      </c>
+      <c r="D31">
+        <v>142</v>
+      </c>
+      <c r="E31">
+        <v>-151</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31">
-        <v>823423</v>
+        <v>81</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>92</v>
-      </c>
-      <c r="I31">
-        <v>4.5</v>
-      </c>
-      <c r="J31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0.1859</v>
-      </c>
-      <c r="P31">
-        <v>4.63</v>
+        <v>6</v>
       </c>
       <c r="S31" t="s">
-        <v>43</v>
-      </c>
-      <c r="T31">
-        <v>0.1753</v>
-      </c>
-      <c r="U31">
-        <v>0.1771</v>
-      </c>
-      <c r="V31">
-        <v>9</v>
-      </c>
-      <c r="W31">
-        <v>0.233</v>
-      </c>
-      <c r="X31">
-        <v>0.2196</v>
-      </c>
-      <c r="Y31">
-        <v>0.9832</v>
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3485,23 +3551,8 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
-      <c r="AD31">
-        <v>3.04</v>
-      </c>
       <c r="AE31" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF31">
-        <v>0.1859</v>
-      </c>
-      <c r="AG31">
-        <v>0.7985</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>3.04</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3509,67 +3560,34 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="C32">
+        <v>4.5</v>
+      </c>
+      <c r="D32">
+        <v>120</v>
+      </c>
+      <c r="E32">
+        <v>-148</v>
       </c>
       <c r="F32" t="s">
-        <v>67</v>
-      </c>
-      <c r="G32">
-        <v>823586</v>
+        <v>85</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32">
-        <v>5.7</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0.1638</v>
-      </c>
-      <c r="N32">
-        <v>5</v>
-      </c>
-      <c r="O32">
-        <v>110</v>
-      </c>
-      <c r="P32">
-        <v>3.9</v>
-      </c>
-      <c r="Q32">
-        <v>0.1273</v>
-      </c>
-      <c r="R32">
-        <v>0.355</v>
+        <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>43</v>
-      </c>
-      <c r="T32">
-        <v>0.1552</v>
-      </c>
-      <c r="U32">
-        <v>0.1736</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>0.2187</v>
-      </c>
-      <c r="X32">
-        <v>0.2196</v>
-      </c>
-      <c r="Y32">
-        <v>0.9935</v>
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3577,23 +3595,8 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
-      <c r="AD32">
-        <v>2.34</v>
-      </c>
       <c r="AE32" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF32">
-        <v>0.1509</v>
-      </c>
-      <c r="AG32">
-        <v>0.7069</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>2.34</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-18.xlsx
+++ b/data/k-props/2026-08-18.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="98">
   <si>
     <t>date</t>
   </si>
@@ -133,169 +133,178 @@
     <t>08/18/2026</t>
   </si>
   <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Carlos Rodon</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>Carson Whisenhunt</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Foster Griffin</t>
+  </si>
+  <si>
+    <t>Keider Montero</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
+    <t>Jose Soriano</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Ranger Suarez</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Robbie Ray</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ New York Mets</t>
+  </si>
+  <si>
+    <t>Zach Thornton</t>
+  </si>
+  <si>
+    <t>Zebby Matthews</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Tyler Mahle</t>
+  </si>
+  <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Athletics @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Kyle Harrison</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Bryce Miller</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Jackson Kent</t>
+  </si>
+  <si>
+    <t>George Klassen</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Cristian Javier</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Eric Lauer</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Ryan Feltner</t>
+  </si>
+  <si>
     <t>Carlos Rodón</t>
   </si>
   <si>
-    <t>New York Yankees @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Keider Montero</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t>Carson Whisenhunt</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t>Foster Griffin</t>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
     <t>José Soriano</t>
   </si>
   <si>
-    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
     <t>Cade Gibson</t>
   </si>
   <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
     <t>Role unknown</t>
   </si>
   <si>
-    <t>Zack Wheeler</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Ranger Suarez</t>
-  </si>
-  <si>
-    <t>Robbie Ray</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ New York Mets</t>
-  </si>
-  <si>
     <t>Zac Thornton</t>
   </si>
   <si>
-    <t>Jack Perkins</t>
-  </si>
-  <si>
-    <t>Athletics @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Zebby Matthews</t>
-  </si>
-  <si>
-    <t>Bryce Miller</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Kyle Harrison</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Texas Rangers</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Cristian Javier</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Eric Lauer</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Ryan Feltner</t>
-  </si>
-  <si>
-    <t>Carlos Rodon</t>
-  </si>
-  <si>
-    <t>Jose Soriano</t>
-  </si>
-  <si>
-    <t>Zach Thornton</t>
-  </si>
-  <si>
-    <t>Jackson Kent</t>
-  </si>
-  <si>
-    <t>George Klassen</t>
+    <t>Daniel Lynch IV</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Bryan Hudson</t>
   </si>
 </sst>
 </file>
@@ -676,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM32"/>
+  <dimension ref="A1:AM34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -808,6 +817,15 @@
       <c r="B2" t="s">
         <v>40</v>
       </c>
+      <c r="C2">
+        <v>5.5</v>
+      </c>
+      <c r="D2">
+        <v>-146</v>
+      </c>
+      <c r="E2">
+        <v>118</v>
+      </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
@@ -818,7 +836,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -827,46 +845,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>0.268</v>
+        <v>0.204</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P2">
-        <v>4.19</v>
+        <v>4.29</v>
       </c>
       <c r="Q2">
-        <v>0.2832</v>
+        <v>0.1983</v>
       </c>
       <c r="R2">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2797</v>
+        <v>0.2603</v>
       </c>
       <c r="U2">
-        <v>0.2455</v>
+        <v>0.265</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2568</v>
+        <v>0.2449</v>
       </c>
       <c r="X2">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y2">
-        <v>1.033</v>
+        <v>1.0455</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -875,22 +893,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>7.65</v>
+        <v>6.21</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2735</v>
+        <v>0.2019</v>
       </c>
       <c r="AG2">
-        <v>1.256</v>
+        <v>1.1808</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>7.65</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -901,73 +919,31 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-148</v>
+        <v>-154</v>
       </c>
       <c r="E3">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
-      <c r="G3">
-        <v>824803</v>
+      <c r="G3" t="s">
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3">
-        <v>5.8</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L3">
         <v>6</v>
       </c>
-      <c r="M3">
-        <v>0.204</v>
-      </c>
-      <c r="N3">
-        <v>5</v>
-      </c>
-      <c r="O3">
-        <v>116</v>
-      </c>
-      <c r="P3">
-        <v>4.29</v>
-      </c>
-      <c r="Q3">
-        <v>0.1983</v>
-      </c>
-      <c r="R3">
-        <v>0.367</v>
-      </c>
       <c r="S3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3">
-        <v>0.276</v>
-      </c>
-      <c r="U3">
-        <v>0.273</v>
-      </c>
-      <c r="V3">
-        <v>9</v>
-      </c>
-      <c r="W3">
-        <v>0.2449</v>
-      </c>
-      <c r="X3">
-        <v>0.2227</v>
-      </c>
-      <c r="Y3">
-        <v>1.0166</v>
+        <v>44</v>
+      </c>
+      <c r="V3" t="s">
+        <v>44</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -975,23 +951,8 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
-      <c r="AD3">
-        <v>6.34</v>
-      </c>
       <c r="AE3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF3">
-        <v>0.2019</v>
-      </c>
-      <c r="AG3">
-        <v>1.2394</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>6.34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -999,28 +960,28 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4">
+        <v>4.5</v>
+      </c>
+      <c r="D4">
+        <v>-107</v>
+      </c>
+      <c r="E4">
+        <v>-113</v>
+      </c>
+      <c r="F4" t="s">
         <v>48</v>
       </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-      <c r="D4">
-        <v>-119</v>
-      </c>
-      <c r="E4">
-        <v>110</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
       <c r="G4">
-        <v>823341</v>
+        <v>824475</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1032,43 +993,43 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>0.167</v>
+        <v>0.1765</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="Q4">
-        <v>0.1379</v>
+        <v>0.1488</v>
       </c>
       <c r="R4">
-        <v>0.367</v>
+        <v>0.377</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2109</v>
+        <v>0.2193</v>
       </c>
       <c r="U4">
-        <v>0.2349</v>
+        <v>0.199</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2358</v>
+        <v>0.1828</v>
       </c>
       <c r="X4">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y4">
-        <v>1.0215</v>
+        <v>0.9052</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1080,13 +1041,13 @@
         <v>3.46</v>
       </c>
       <c r="AE4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF4">
-        <v>0.1563</v>
+        <v>0.166</v>
       </c>
       <c r="AG4">
-        <v>0.947</v>
+        <v>0.9947</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -1100,28 +1061,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>5.5</v>
       </c>
       <c r="D5">
-        <v>-120</v>
+        <v>115</v>
       </c>
       <c r="E5">
-        <v>107</v>
+        <v>-136</v>
       </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5">
-        <v>823341</v>
+        <v>824475</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1133,43 +1094,43 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>0.27</v>
+        <v>0.2108</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P5">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="Q5">
-        <v>0.2389</v>
+        <v>0.2727</v>
       </c>
       <c r="R5">
-        <v>0.361</v>
+        <v>0.355</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1846</v>
+        <v>0.2785</v>
       </c>
       <c r="U5">
-        <v>0.1885</v>
+        <v>0.2747</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2235</v>
+        <v>0.2552</v>
       </c>
       <c r="X5">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y5">
-        <v>0.9584</v>
+        <v>1.0796</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1178,22 +1139,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.92</v>
+        <v>6.87</v>
       </c>
       <c r="AE5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2588</v>
+        <v>0.2328</v>
       </c>
       <c r="AG5">
-        <v>0.8291</v>
+        <v>1.2633</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>4.92</v>
+        <v>6.87</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1201,7 +1162,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1210,10 +1171,10 @@
         <v>-115</v>
       </c>
       <c r="E6">
-        <v>-106</v>
+        <v>-103</v>
       </c>
       <c r="F6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>824398</v>
@@ -1252,7 +1213,7 @@
         <v>0.349</v>
       </c>
       <c r="S6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="T6">
         <v>0.1978</v>
@@ -1267,7 +1228,7 @@
         <v>0.2259</v>
       </c>
       <c r="X6">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y6">
         <v>0.9198</v>
@@ -1279,22 +1240,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="AE6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF6">
         <v>0.1754</v>
       </c>
       <c r="AG6">
-        <v>0.8882</v>
+        <v>0.8972</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1302,19 +1263,19 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C7">
         <v>5.5</v>
       </c>
       <c r="D7">
-        <v>-106</v>
+        <v>-107</v>
       </c>
       <c r="E7">
-        <v>-108</v>
+        <v>-110</v>
       </c>
       <c r="F7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>824398</v>
@@ -1353,7 +1314,7 @@
         <v>0.377</v>
       </c>
       <c r="S7" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="T7">
         <v>0.2291</v>
@@ -1368,7 +1329,7 @@
         <v>0.2271</v>
       </c>
       <c r="X7">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y7">
         <v>1.0041</v>
@@ -1380,22 +1341,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="AE7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF7">
         <v>0.1877</v>
       </c>
       <c r="AG7">
-        <v>1.0289</v>
+        <v>1.0393</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1403,28 +1364,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
-        <v>121</v>
+        <v>-122</v>
       </c>
       <c r="E8">
-        <v>-135</v>
+        <v>105</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>824475</v>
+        <v>823341</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1436,43 +1397,43 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>0.2108</v>
+        <v>0.167</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="P8">
-        <v>4.24</v>
+        <v>4</v>
       </c>
       <c r="Q8">
-        <v>0.2727</v>
+        <v>0.1379</v>
       </c>
       <c r="R8">
-        <v>0.355</v>
+        <v>0.367</v>
       </c>
       <c r="S8" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="T8">
-        <v>0.2608</v>
+        <v>0.2109</v>
       </c>
       <c r="U8">
-        <v>0.2682</v>
+        <v>0.2349</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>0.2552</v>
+        <v>0.2358</v>
       </c>
       <c r="X8">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y8">
-        <v>1.036</v>
+        <v>1.0215</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1481,22 +1442,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>6.12</v>
+        <v>3.5</v>
       </c>
       <c r="AE8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF8">
-        <v>0.2328</v>
+        <v>0.1563</v>
       </c>
       <c r="AG8">
-        <v>1.1711</v>
+        <v>0.9566</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>6.12</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1504,28 +1465,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D9">
-        <v>-108</v>
+        <v>-120</v>
       </c>
       <c r="E9">
-        <v>-105</v>
+        <v>105</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9">
-        <v>824475</v>
+        <v>823341</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1537,43 +1498,43 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>0.1765</v>
+        <v>0.27</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="P9">
-        <v>4.35</v>
+        <v>4.06</v>
       </c>
       <c r="Q9">
-        <v>0.1488</v>
+        <v>0.2389</v>
       </c>
       <c r="R9">
-        <v>0.377</v>
+        <v>0.361</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2048</v>
+        <v>0.1988</v>
       </c>
       <c r="U9">
-        <v>0.1939</v>
+        <v>0.178</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>0.1828</v>
+        <v>0.2235</v>
       </c>
       <c r="X9">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y9">
-        <v>0.9696</v>
+        <v>0.8825</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1582,22 +1543,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.42</v>
+        <v>4.93</v>
       </c>
       <c r="AE9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF9">
-        <v>0.166</v>
+        <v>0.2588</v>
       </c>
       <c r="AG9">
-        <v>0.9198</v>
+        <v>0.9017</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.42</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1605,19 +1566,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+      <c r="D10">
+        <v>125</v>
+      </c>
+      <c r="E10">
+        <v>-147</v>
+      </c>
+      <c r="F10" t="s">
         <v>59</v>
       </c>
-      <c r="F10" t="s">
-        <v>60</v>
-      </c>
       <c r="G10">
-        <v>822938</v>
+        <v>823423</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1626,46 +1596,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2423</v>
+        <v>0.3018</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="P10">
-        <v>4.14</v>
+        <v>3.94</v>
       </c>
       <c r="Q10">
-        <v>0.1776</v>
+        <v>0.2929</v>
       </c>
       <c r="R10">
-        <v>0.349</v>
+        <v>0.331</v>
       </c>
       <c r="S10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T10">
-        <v>0.1843</v>
+        <v>0.2372</v>
       </c>
       <c r="U10">
-        <v>0.1802</v>
+        <v>0.2276</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.1897</v>
+        <v>0.2114</v>
       </c>
       <c r="X10">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y10">
-        <v>0.88</v>
+        <v>0.9685</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1674,22 +1644,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.69</v>
+        <v>7.07</v>
       </c>
       <c r="AE10" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF10">
-        <v>0.2197</v>
+        <v>0.2988</v>
       </c>
       <c r="AG10">
-        <v>0.8274</v>
+        <v>1.0759</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.69</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1700,73 +1670,31 @@
         <v>61</v>
       </c>
       <c r="C11">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D11">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E11">
-        <v>-113</v>
+        <v>-145</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11">
-        <v>822938</v>
+        <v>62</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11">
-        <v>6</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L11">
         <v>6</v>
       </c>
-      <c r="M11">
-        <v>0.1413</v>
-      </c>
-      <c r="N11">
-        <v>5</v>
-      </c>
-      <c r="O11">
-        <v>124</v>
-      </c>
-      <c r="P11">
-        <v>4</v>
-      </c>
-      <c r="Q11">
-        <v>0.129</v>
-      </c>
-      <c r="R11">
-        <v>0.383</v>
-      </c>
       <c r="S11" t="s">
-        <v>43</v>
-      </c>
-      <c r="T11">
-        <v>0.1952</v>
-      </c>
-      <c r="U11">
-        <v>0.1807</v>
-      </c>
-      <c r="V11">
-        <v>9</v>
-      </c>
-      <c r="W11">
-        <v>0.19</v>
-      </c>
-      <c r="X11">
-        <v>0.2227</v>
-      </c>
-      <c r="Y11">
-        <v>0.987</v>
+        <v>44</v>
+      </c>
+      <c r="V11" t="s">
+        <v>44</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1774,23 +1702,8 @@
       <c r="AC11" t="s">
         <v>44</v>
       </c>
-      <c r="AD11">
-        <v>2.84</v>
-      </c>
       <c r="AE11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF11">
-        <v>0.1366</v>
-      </c>
-      <c r="AG11">
-        <v>0.8764</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>2.84</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1798,55 +1711,76 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12">
+        <v>3.5</v>
+      </c>
+      <c r="D12">
+        <v>110</v>
+      </c>
+      <c r="E12">
+        <v>-125</v>
+      </c>
+      <c r="F12" t="s">
         <v>62</v>
       </c>
-      <c r="F12" t="s">
-        <v>63</v>
-      </c>
       <c r="G12">
-        <v>823423</v>
+        <v>822938</v>
       </c>
       <c r="H12" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>0.1859</v>
+        <v>0.1413</v>
+      </c>
+      <c r="N12">
+        <v>5</v>
+      </c>
+      <c r="O12">
+        <v>124</v>
       </c>
       <c r="P12">
-        <v>4.63</v>
+        <v>4</v>
+      </c>
+      <c r="Q12">
+        <v>0.129</v>
+      </c>
+      <c r="R12">
+        <v>0.383</v>
       </c>
       <c r="S12" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1753</v>
+        <v>0.1965</v>
       </c>
       <c r="U12">
-        <v>0.1771</v>
+        <v>0.1807</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.233</v>
+        <v>0.19</v>
       </c>
       <c r="X12">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y12">
-        <v>0.9664</v>
+        <v>0.9953</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1855,22 +1789,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="AE12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF12">
-        <v>0.1859</v>
+        <v>0.1366</v>
       </c>
       <c r="AG12">
-        <v>0.7873</v>
+        <v>0.8914</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1878,28 +1812,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13">
+        <v>4.5</v>
+      </c>
+      <c r="D13">
+        <v>-102</v>
+      </c>
+      <c r="E13">
+        <v>-106</v>
+      </c>
+      <c r="F13" t="s">
         <v>65</v>
       </c>
-      <c r="C13">
-        <v>7.5</v>
-      </c>
-      <c r="D13">
-        <v>115</v>
-      </c>
-      <c r="E13">
-        <v>-137</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
       <c r="G13">
-        <v>823423</v>
+        <v>824723</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1911,43 +1845,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.3018</v>
+        <v>0.2472</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="P13">
-        <v>3.94</v>
+        <v>4.12</v>
       </c>
       <c r="Q13">
-        <v>0.2929</v>
+        <v>0.2143</v>
       </c>
       <c r="R13">
-        <v>0.331</v>
+        <v>0.296</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2372</v>
+        <v>0.2613</v>
       </c>
       <c r="U13">
-        <v>0.2276</v>
+        <v>0.1821</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2114</v>
+        <v>0.1751</v>
       </c>
       <c r="X13">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y13">
-        <v>0.9685</v>
+        <v>0.88</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1956,22 +1890,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="AE13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="AF13">
-        <v>0.2988</v>
+        <v>0.2375</v>
       </c>
       <c r="AG13">
-        <v>1.0651</v>
+        <v>1.185</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>7</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1985,13 +1919,13 @@
         <v>3.5</v>
       </c>
       <c r="D14">
-        <v>-135</v>
+        <v>-126</v>
       </c>
       <c r="E14">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G14">
         <v>824723</v>
@@ -2033,10 +1967,10 @@
         <v>43</v>
       </c>
       <c r="T14">
-        <v>0.2053</v>
+        <v>0.1861</v>
       </c>
       <c r="U14">
-        <v>0.1912</v>
+        <v>0.197</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -2045,10 +1979,10 @@
         <v>0.2168</v>
       </c>
       <c r="X14">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y14">
-        <v>0.9813</v>
+        <v>0.9954</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2057,22 +1991,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.61</v>
+        <v>3.36</v>
       </c>
       <c r="AE14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF14">
         <v>0.1621</v>
       </c>
       <c r="AG14">
-        <v>0.922</v>
+        <v>0.844</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>3.61</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2080,28 +2014,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15">
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>-112</v>
+        <v>-113</v>
       </c>
       <c r="E15">
-        <v>-102</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G15">
-        <v>824723</v>
+        <v>823586</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2113,43 +2047,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2472</v>
+        <v>0.204</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="P15">
-        <v>4.12</v>
+        <v>4.21</v>
       </c>
       <c r="Q15">
-        <v>0.2143</v>
+        <v>0.2072</v>
       </c>
       <c r="R15">
-        <v>0.296</v>
+        <v>0.357</v>
       </c>
       <c r="S15" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2613</v>
+        <v>0.246</v>
       </c>
       <c r="U15">
-        <v>0.1821</v>
+        <v>0.249</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>0.1751</v>
+        <v>0.2325</v>
       </c>
       <c r="X15">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y15">
-        <v>0.88</v>
+        <v>0.9557</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2158,22 +2092,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.19</v>
+        <v>5.02</v>
       </c>
       <c r="AE15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF15">
-        <v>0.2375</v>
+        <v>0.2051</v>
       </c>
       <c r="AG15">
-        <v>1.1731</v>
+        <v>1.116</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.19</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2184,73 +2118,31 @@
         <v>69</v>
       </c>
       <c r="C16">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D16">
-        <v>-114</v>
+        <v>-109</v>
       </c>
       <c r="E16">
-        <v>101</v>
+        <v>-104</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16">
-        <v>823586</v>
+        <v>68</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16">
-        <v>5.4</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L16">
         <v>6</v>
       </c>
-      <c r="M16">
-        <v>0.204</v>
-      </c>
-      <c r="N16">
-        <v>5</v>
-      </c>
-      <c r="O16">
-        <v>111</v>
-      </c>
-      <c r="P16">
-        <v>4.21</v>
-      </c>
-      <c r="Q16">
-        <v>0.2072</v>
-      </c>
-      <c r="R16">
-        <v>0.357</v>
-      </c>
       <c r="S16" t="s">
-        <v>43</v>
-      </c>
-      <c r="T16">
-        <v>0.2516</v>
-      </c>
-      <c r="U16">
-        <v>0.2451</v>
-      </c>
-      <c r="V16">
-        <v>9</v>
-      </c>
-      <c r="W16">
-        <v>0.2325</v>
-      </c>
-      <c r="X16">
-        <v>0.2227</v>
-      </c>
-      <c r="Y16">
-        <v>0.9795</v>
+        <v>44</v>
+      </c>
+      <c r="V16" t="s">
+        <v>44</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2258,23 +2150,8 @@
       <c r="AC16" t="s">
         <v>44</v>
       </c>
-      <c r="AD16">
-        <v>5.2</v>
-      </c>
       <c r="AE16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF16">
-        <v>0.2051</v>
-      </c>
-      <c r="AG16">
-        <v>1.1298</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>5.2</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2282,13 +2159,22 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17">
+        <v>4.5</v>
+      </c>
+      <c r="D17">
+        <v>112</v>
+      </c>
+      <c r="E17">
+        <v>-120</v>
+      </c>
+      <c r="F17" t="s">
         <v>71</v>
       </c>
-      <c r="F17" t="s">
-        <v>70</v>
-      </c>
       <c r="G17">
-        <v>823586</v>
+        <v>823667</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
@@ -2303,46 +2189,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>0.1638</v>
+        <v>0.199</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="P17">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="Q17">
-        <v>0.1273</v>
+        <v>0.2054</v>
       </c>
       <c r="R17">
-        <v>0.355</v>
+        <v>0.359</v>
       </c>
       <c r="S17" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="T17">
-        <v>0.1552</v>
+        <v>0.2372</v>
       </c>
       <c r="U17">
-        <v>0.1736</v>
+        <v>0.2298</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2187</v>
+        <v>0.2179</v>
       </c>
       <c r="X17">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y17">
-        <v>0.9935</v>
+        <v>0.996</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2351,22 +2237,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>2.31</v>
+        <v>5.22</v>
       </c>
       <c r="AE17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF17">
-        <v>0.1509</v>
+        <v>0.2013</v>
       </c>
       <c r="AG17">
-        <v>0.6969</v>
+        <v>1.076</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>2.31</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2377,25 +2263,25 @@
         <v>72</v>
       </c>
       <c r="C18">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-140</v>
+        <v>-108</v>
       </c>
       <c r="E18">
-        <v>119</v>
+        <v>-104</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G18">
-        <v>824075</v>
+        <v>823667</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2407,43 +2293,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.25</v>
+        <v>0.2344</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P18">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="Q18">
-        <v>0.1964</v>
+        <v>0.2883</v>
       </c>
       <c r="R18">
-        <v>0.359</v>
+        <v>0.357</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2031</v>
+        <v>0.1989</v>
       </c>
       <c r="U18">
-        <v>0.209</v>
+        <v>0.1944</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2096</v>
+        <v>0.2114</v>
       </c>
       <c r="X18">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y18">
-        <v>0.9784</v>
+        <v>0.9597</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2452,22 +2338,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.37</v>
+        <v>4.92</v>
       </c>
       <c r="AE18" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF18">
-        <v>0.2308</v>
+        <v>0.2536</v>
       </c>
       <c r="AG18">
-        <v>0.9121</v>
+        <v>0.9021</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.37</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2475,28 +2361,28 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19">
+        <v>3.5</v>
+      </c>
+      <c r="D19">
+        <v>-140</v>
+      </c>
+      <c r="E19">
+        <v>130</v>
+      </c>
+      <c r="F19" t="s">
         <v>74</v>
       </c>
-      <c r="C19">
-        <v>4.5</v>
-      </c>
-      <c r="D19">
-        <v>-122</v>
-      </c>
-      <c r="E19">
-        <v>107</v>
-      </c>
-      <c r="F19" t="s">
-        <v>75</v>
-      </c>
       <c r="G19">
-        <v>823667</v>
+        <v>824075</v>
       </c>
       <c r="H19" t="s">
         <v>42</v>
       </c>
       <c r="I19">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
@@ -2508,43 +2394,43 @@
         <v>6</v>
       </c>
       <c r="M19">
-        <v>0.2344</v>
+        <v>0.25</v>
       </c>
       <c r="N19">
         <v>5</v>
       </c>
       <c r="O19">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P19">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q19">
-        <v>0.2883</v>
+        <v>0.1964</v>
       </c>
       <c r="R19">
-        <v>0.357</v>
+        <v>0.359</v>
       </c>
       <c r="S19" t="s">
         <v>43</v>
       </c>
       <c r="T19">
-        <v>0.2014</v>
+        <v>0.2029</v>
       </c>
       <c r="U19">
-        <v>0.2005</v>
+        <v>0.2085</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2114</v>
+        <v>0.2096</v>
       </c>
       <c r="X19">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y19">
-        <v>0.9824</v>
+        <v>0.9401</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2553,22 +2439,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>5.05</v>
+        <v>4.23</v>
       </c>
       <c r="AE19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF19">
-        <v>0.2536</v>
+        <v>0.2308</v>
       </c>
       <c r="AG19">
-        <v>0.9044</v>
+        <v>0.9202</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>5.05</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2576,28 +2462,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
+        <v>75</v>
+      </c>
+      <c r="C20">
+        <v>5.5</v>
+      </c>
+      <c r="D20">
+        <v>-160</v>
+      </c>
+      <c r="E20">
+        <v>135</v>
+      </c>
+      <c r="F20" t="s">
         <v>76</v>
       </c>
-      <c r="C20">
-        <v>4.5</v>
-      </c>
-      <c r="D20">
-        <v>115</v>
-      </c>
-      <c r="E20">
-        <v>-130</v>
-      </c>
-      <c r="F20" t="s">
-        <v>75</v>
-      </c>
       <c r="G20">
-        <v>823667</v>
+        <v>823749</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2609,43 +2495,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.199</v>
+        <v>0.2969</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="P20">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="Q20">
-        <v>0.2054</v>
+        <v>0.2872</v>
       </c>
       <c r="R20">
-        <v>0.359</v>
+        <v>0.32</v>
       </c>
       <c r="S20" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="T20">
-        <v>0.2372</v>
+        <v>0.2086</v>
       </c>
       <c r="U20">
-        <v>0.2298</v>
+        <v>0.1968</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2179</v>
+        <v>0.2395</v>
       </c>
       <c r="X20">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y20">
-        <v>0.996</v>
+        <v>1.0092</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2654,22 +2540,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>5.16</v>
+        <v>5.67</v>
       </c>
       <c r="AE20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF20">
-        <v>0.2013</v>
+        <v>0.2938</v>
       </c>
       <c r="AG20">
-        <v>1.0652</v>
+        <v>0.946</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>5.16</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2683,13 +2569,13 @@
         <v>5.5</v>
       </c>
       <c r="D21">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="E21">
-        <v>-140</v>
+        <v>-150</v>
       </c>
       <c r="F21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="G21">
         <v>823749</v>
@@ -2728,7 +2614,7 @@
         <v>0.367</v>
       </c>
       <c r="S21" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="T21">
         <v>0.2357</v>
@@ -2743,7 +2629,7 @@
         <v>0.2155</v>
       </c>
       <c r="X21">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y21">
         <v>1.0057</v>
@@ -2755,22 +2641,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
       <c r="AE21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF21">
         <v>0.2207</v>
       </c>
       <c r="AG21">
-        <v>1.0583</v>
+        <v>1.0691</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.23</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2778,28 +2664,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22">
+        <v>6.5</v>
+      </c>
+      <c r="D22">
+        <v>121</v>
+      </c>
+      <c r="E22">
+        <v>-138</v>
+      </c>
+      <c r="F22" t="s">
         <v>79</v>
       </c>
-      <c r="C22">
-        <v>5.5</v>
-      </c>
-      <c r="D22">
-        <v>-155</v>
-      </c>
-      <c r="E22">
-        <v>128</v>
-      </c>
-      <c r="F22" t="s">
-        <v>78</v>
-      </c>
       <c r="G22">
-        <v>823749</v>
+        <v>824639</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2811,43 +2697,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2969</v>
+        <v>0.2347</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="P22">
-        <v>4.11</v>
+        <v>4.23</v>
       </c>
       <c r="Q22">
-        <v>0.2872</v>
+        <v>0.1864</v>
       </c>
       <c r="R22">
-        <v>0.32</v>
+        <v>0.371</v>
       </c>
       <c r="S22" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="T22">
-        <v>0.2086</v>
+        <v>0.2258</v>
       </c>
       <c r="U22">
-        <v>0.1968</v>
+        <v>0.2444</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2395</v>
+        <v>0.2368</v>
       </c>
       <c r="X22">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y22">
-        <v>1.0092</v>
+        <v>1.0402</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2856,22 +2742,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.61</v>
+        <v>5.43</v>
       </c>
       <c r="AE22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF22">
-        <v>0.2938</v>
+        <v>0.2168</v>
       </c>
       <c r="AG22">
-        <v>0.9365</v>
+        <v>1.0241</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.61</v>
+        <v>5.43</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2888,7 +2774,7 @@
         <v>-105</v>
       </c>
       <c r="E23">
-        <v>-109</v>
+        <v>-103</v>
       </c>
       <c r="F23" t="s">
         <v>81</v>
@@ -2930,7 +2816,7 @@
         <v>0.357</v>
       </c>
       <c r="S23" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="T23">
         <v>0.2084</v>
@@ -2945,7 +2831,7 @@
         <v>0.2076</v>
       </c>
       <c r="X23">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y23">
         <v>0.9941</v>
@@ -2957,22 +2843,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
       <c r="AE23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF23">
         <v>0.1733</v>
       </c>
       <c r="AG23">
-        <v>0.9356</v>
+        <v>0.9451</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>3.17</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2983,73 +2869,31 @@
         <v>82</v>
       </c>
       <c r="C24">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="E24">
-        <v>-135</v>
+        <v>-156</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24">
-        <v>824639</v>
+        <v>81</v>
+      </c>
+      <c r="G24" t="s">
+        <v>44</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
-      </c>
-      <c r="I24">
-        <v>5.6</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
-      <c r="M24">
-        <v>0.2347</v>
-      </c>
-      <c r="N24">
-        <v>5</v>
-      </c>
-      <c r="O24">
-        <v>118</v>
-      </c>
-      <c r="P24">
-        <v>4.23</v>
-      </c>
-      <c r="Q24">
-        <v>0.1864</v>
-      </c>
-      <c r="R24">
-        <v>0.371</v>
-      </c>
       <c r="S24" t="s">
-        <v>43</v>
-      </c>
-      <c r="T24">
-        <v>0.2258</v>
-      </c>
-      <c r="U24">
-        <v>0.2444</v>
-      </c>
-      <c r="V24">
-        <v>9</v>
-      </c>
-      <c r="W24">
-        <v>0.2368</v>
-      </c>
-      <c r="X24">
-        <v>0.2227</v>
-      </c>
-      <c r="Y24">
-        <v>1.0402</v>
+        <v>44</v>
+      </c>
+      <c r="V24" t="s">
+        <v>44</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3057,23 +2901,8 @@
       <c r="AC24" t="s">
         <v>44</v>
       </c>
-      <c r="AD24">
-        <v>5.38</v>
-      </c>
       <c r="AE24" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF24">
-        <v>0.2168</v>
-      </c>
-      <c r="AG24">
-        <v>1.0138</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>5.38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3081,76 +2910,34 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C25">
         <v>4.5</v>
       </c>
       <c r="D25">
-        <v>-113</v>
+        <v>122</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>-153</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
-      </c>
-      <c r="G25">
-        <v>824154</v>
+        <v>84</v>
+      </c>
+      <c r="G25" t="s">
+        <v>44</v>
       </c>
       <c r="H25" t="s">
-        <v>86</v>
-      </c>
-      <c r="I25">
-        <v>3.9</v>
-      </c>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L25">
         <v>6</v>
       </c>
-      <c r="M25">
-        <v>0.1678</v>
-      </c>
-      <c r="N25">
-        <v>5</v>
-      </c>
-      <c r="O25">
-        <v>91</v>
-      </c>
-      <c r="P25">
-        <v>4.61</v>
-      </c>
-      <c r="Q25">
-        <v>0.1209</v>
-      </c>
-      <c r="R25">
-        <v>0.313</v>
-      </c>
       <c r="S25" t="s">
-        <v>43</v>
-      </c>
-      <c r="T25">
-        <v>0.266</v>
-      </c>
-      <c r="U25">
-        <v>0.2573</v>
-      </c>
-      <c r="V25">
-        <v>9</v>
-      </c>
-      <c r="W25">
-        <v>0.2504</v>
-      </c>
-      <c r="X25">
-        <v>0.2227</v>
-      </c>
-      <c r="Y25">
-        <v>1.0381</v>
+        <v>44</v>
+      </c>
+      <c r="V25" t="s">
+        <v>44</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3158,23 +2945,8 @@
       <c r="AC25" t="s">
         <v>44</v>
       </c>
-      <c r="AD25">
-        <v>3.4</v>
-      </c>
       <c r="AE25" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF25">
-        <v>0.1531</v>
-      </c>
-      <c r="AG25">
-        <v>1.1946</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>3.4</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3182,28 +2954,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C26">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D26">
-        <v>-120</v>
+        <v>-113</v>
       </c>
       <c r="E26">
-        <v>-102</v>
+        <v>-105</v>
       </c>
       <c r="F26" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G26">
-        <v>824319</v>
+        <v>824154</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="I26">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3215,43 +2987,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1514</v>
+        <v>0.1678</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="P26">
-        <v>4.23</v>
+        <v>4.61</v>
       </c>
       <c r="Q26">
-        <v>0.1624</v>
+        <v>0.1209</v>
       </c>
       <c r="R26">
-        <v>0.369</v>
+        <v>0.313</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2216</v>
+        <v>0.2136</v>
       </c>
       <c r="U26">
-        <v>0.2193</v>
+        <v>0.2242</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.247</v>
+        <v>0.2504</v>
       </c>
       <c r="X26">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y26">
-        <v>1.0013</v>
+        <v>0.9877</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3260,22 +3032,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>3.37</v>
+        <v>2.63</v>
       </c>
       <c r="AE26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF26">
-        <v>0.1555</v>
+        <v>0.1531</v>
       </c>
       <c r="AG26">
-        <v>0.9952</v>
+        <v>0.9687</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>3.37</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3283,16 +3055,16 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C27">
         <v>3.5</v>
       </c>
       <c r="D27">
-        <v>112</v>
+        <v>-120</v>
       </c>
       <c r="E27">
-        <v>-139</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s">
         <v>88</v>
@@ -3304,7 +3076,7 @@
         <v>42</v>
       </c>
       <c r="I27">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3316,43 +3088,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1597</v>
+        <v>0.1514</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P27">
-        <v>4.39</v>
+        <v>4.23</v>
       </c>
       <c r="Q27">
-        <v>0.1217</v>
+        <v>0.1624</v>
       </c>
       <c r="R27">
-        <v>0.365</v>
+        <v>0.369</v>
       </c>
       <c r="S27" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="T27">
-        <v>0.2783</v>
+        <v>0.2216</v>
       </c>
       <c r="U27">
-        <v>0.2137</v>
+        <v>0.2193</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2061</v>
+        <v>0.247</v>
       </c>
       <c r="X27">
-        <v>0.2227</v>
+        <v>0.2205</v>
       </c>
       <c r="Y27">
-        <v>1.0055</v>
+        <v>1.0013</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3361,22 +3133,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.89</v>
+        <v>3.41</v>
       </c>
       <c r="AE27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AF27">
-        <v>0.1458</v>
+        <v>0.1555</v>
       </c>
       <c r="AG27">
-        <v>1.2496</v>
+        <v>1.0053</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.89</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3384,34 +3156,76 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C28">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D28">
-        <v>-148</v>
+        <v>117</v>
       </c>
       <c r="E28">
-        <v>127</v>
+        <v>-144</v>
       </c>
       <c r="F28" t="s">
-        <v>41</v>
-      </c>
-      <c r="G28" t="s">
-        <v>44</v>
+        <v>88</v>
+      </c>
+      <c r="G28">
+        <v>824319</v>
       </c>
       <c r="H28" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I28">
+        <v>4.8</v>
+      </c>
+      <c r="J28" t="b">
+        <v>0</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
       </c>
       <c r="L28">
         <v>6</v>
       </c>
+      <c r="M28">
+        <v>0.1597</v>
+      </c>
+      <c r="N28">
+        <v>5</v>
+      </c>
+      <c r="O28">
+        <v>115</v>
+      </c>
+      <c r="P28">
+        <v>4.39</v>
+      </c>
+      <c r="Q28">
+        <v>0.1217</v>
+      </c>
+      <c r="R28">
+        <v>0.365</v>
+      </c>
       <c r="S28" t="s">
-        <v>44</v>
-      </c>
-      <c r="V28" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="T28">
+        <v>0.2783</v>
+      </c>
+      <c r="U28">
+        <v>0.2137</v>
+      </c>
+      <c r="V28">
+        <v>9</v>
+      </c>
+      <c r="W28">
+        <v>0.2061</v>
+      </c>
+      <c r="X28">
+        <v>0.2205</v>
+      </c>
+      <c r="Y28">
+        <v>1.0055</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3419,8 +3233,23 @@
       <c r="AC28" t="s">
         <v>44</v>
       </c>
+      <c r="AD28">
+        <v>3.93</v>
+      </c>
       <c r="AE28" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF28">
+        <v>0.1458</v>
+      </c>
+      <c r="AG28">
+        <v>1.2623</v>
+      </c>
+      <c r="AH28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>3.93</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3428,43 +3257,91 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29">
-        <v>4.5</v>
-      </c>
-      <c r="D29">
-        <v>110</v>
-      </c>
-      <c r="E29">
-        <v>-135</v>
+        <v>90</v>
       </c>
       <c r="F29" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29">
+        <v>824803</v>
+      </c>
+      <c r="H29" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29">
+        <v>5.1</v>
+      </c>
+      <c r="J29" t="b">
+        <v>0</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0.268</v>
+      </c>
+      <c r="N29">
+        <v>5</v>
+      </c>
+      <c r="O29">
+        <v>113</v>
+      </c>
+      <c r="P29">
+        <v>4.19</v>
+      </c>
+      <c r="Q29">
+        <v>0.2832</v>
+      </c>
+      <c r="R29">
+        <v>0.361</v>
+      </c>
+      <c r="S29" t="s">
+        <v>43</v>
+      </c>
+      <c r="T29">
+        <v>0.2607</v>
+      </c>
+      <c r="U29">
+        <v>0.246</v>
+      </c>
+      <c r="V29">
+        <v>9</v>
+      </c>
+      <c r="W29">
+        <v>0.2568</v>
+      </c>
+      <c r="X29">
+        <v>0.2205</v>
+      </c>
+      <c r="Y29">
+        <v>1.0725</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC29" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD29">
+        <v>7.48</v>
+      </c>
+      <c r="AE29" t="s">
         <v>60</v>
       </c>
-      <c r="G29" t="s">
-        <v>44</v>
-      </c>
-      <c r="H29" t="s">
-        <v>44</v>
-      </c>
-      <c r="L29">
-        <v>6</v>
-      </c>
-      <c r="S29" t="s">
-        <v>44</v>
-      </c>
-      <c r="V29" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA29" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE29" t="s">
-        <v>44</v>
+      <c r="AF29">
+        <v>0.2735</v>
+      </c>
+      <c r="AG29">
+        <v>1.1823</v>
+      </c>
+      <c r="AH29">
+        <v>0</v>
+      </c>
+      <c r="AM29">
+        <v>7.48</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3472,34 +3349,67 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>92</v>
-      </c>
-      <c r="C30">
-        <v>3.5</v>
-      </c>
-      <c r="D30">
-        <v>-122</v>
-      </c>
-      <c r="E30">
-        <v>-101</v>
+        <v>91</v>
       </c>
       <c r="F30" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" t="s">
-        <v>44</v>
+        <v>62</v>
+      </c>
+      <c r="G30">
+        <v>822938</v>
       </c>
       <c r="H30" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I30">
+        <v>5.6</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0.2423</v>
+      </c>
+      <c r="N30">
+        <v>5</v>
+      </c>
+      <c r="O30">
+        <v>107</v>
+      </c>
+      <c r="P30">
+        <v>4.14</v>
+      </c>
+      <c r="Q30">
+        <v>0.1776</v>
+      </c>
+      <c r="R30">
+        <v>0.349</v>
       </c>
       <c r="S30" t="s">
-        <v>44</v>
-      </c>
-      <c r="V30" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T30">
+        <v>0.1843</v>
+      </c>
+      <c r="U30">
+        <v>0.1802</v>
+      </c>
+      <c r="V30">
+        <v>9</v>
+      </c>
+      <c r="W30">
+        <v>0.1897</v>
+      </c>
+      <c r="X30">
+        <v>0.2205</v>
+      </c>
+      <c r="Y30">
+        <v>0.88</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3507,8 +3417,23 @@
       <c r="AC30" t="s">
         <v>44</v>
       </c>
+      <c r="AD30">
+        <v>3.72</v>
+      </c>
       <c r="AE30" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF30">
+        <v>0.2197</v>
+      </c>
+      <c r="AG30">
+        <v>0.8358</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>3.72</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3516,34 +3441,55 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31">
+        <v>823423</v>
+      </c>
+      <c r="H31" t="s">
         <v>93</v>
       </c>
-      <c r="C31">
+      <c r="I31">
         <v>4.5</v>
       </c>
-      <c r="D31">
-        <v>142</v>
-      </c>
-      <c r="E31">
-        <v>-151</v>
-      </c>
-      <c r="F31" t="s">
-        <v>81</v>
-      </c>
-      <c r="G31" t="s">
-        <v>44</v>
-      </c>
-      <c r="H31" t="s">
-        <v>44</v>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0.1859</v>
+      </c>
+      <c r="P31">
+        <v>4.63</v>
       </c>
       <c r="S31" t="s">
-        <v>44</v>
-      </c>
-      <c r="V31" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T31">
+        <v>0.1753</v>
+      </c>
+      <c r="U31">
+        <v>0.1771</v>
+      </c>
+      <c r="V31">
+        <v>9</v>
+      </c>
+      <c r="W31">
+        <v>0.233</v>
+      </c>
+      <c r="X31">
+        <v>0.2205</v>
+      </c>
+      <c r="Y31">
+        <v>0.9664</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3551,8 +3497,23 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
+      <c r="AD31">
+        <v>2.98</v>
+      </c>
       <c r="AE31" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF31">
+        <v>0.1859</v>
+      </c>
+      <c r="AG31">
+        <v>0.7952</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>2.98</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3562,32 +3523,65 @@
       <c r="B32" t="s">
         <v>94</v>
       </c>
-      <c r="C32">
-        <v>4.5</v>
-      </c>
-      <c r="D32">
-        <v>120</v>
-      </c>
-      <c r="E32">
-        <v>-148</v>
-      </c>
       <c r="F32" t="s">
-        <v>85</v>
-      </c>
-      <c r="G32" t="s">
-        <v>44</v>
+        <v>68</v>
+      </c>
+      <c r="G32">
+        <v>823586</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I32">
+        <v>5.7</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0.1638</v>
+      </c>
+      <c r="N32">
+        <v>5</v>
+      </c>
+      <c r="O32">
+        <v>110</v>
+      </c>
+      <c r="P32">
+        <v>3.9</v>
+      </c>
+      <c r="Q32">
+        <v>0.1273</v>
+      </c>
+      <c r="R32">
+        <v>0.355</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
-      </c>
-      <c r="V32" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="T32">
+        <v>0.1552</v>
+      </c>
+      <c r="U32">
+        <v>0.1736</v>
+      </c>
+      <c r="V32">
+        <v>9</v>
+      </c>
+      <c r="W32">
+        <v>0.2187</v>
+      </c>
+      <c r="X32">
+        <v>0.2205</v>
+      </c>
+      <c r="Y32">
+        <v>0.9935</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3595,8 +3589,207 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
+      <c r="AD32">
+        <v>2.33</v>
+      </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF32">
+        <v>0.1509</v>
+      </c>
+      <c r="AG32">
+        <v>0.704</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="33" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F33" t="s">
+        <v>74</v>
+      </c>
+      <c r="G33">
+        <v>824075</v>
+      </c>
+      <c r="H33" t="s">
+        <v>96</v>
+      </c>
+      <c r="I33">
+        <v>2</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0.197</v>
+      </c>
+      <c r="N33">
+        <v>2</v>
+      </c>
+      <c r="O33">
+        <v>20</v>
+      </c>
+      <c r="P33">
+        <v>4.06</v>
+      </c>
+      <c r="Q33">
+        <v>0.25</v>
+      </c>
+      <c r="R33">
+        <v>0.091</v>
+      </c>
+      <c r="S33" t="s">
+        <v>56</v>
+      </c>
+      <c r="T33">
+        <v>0.2396</v>
+      </c>
+      <c r="U33">
+        <v>0.2076</v>
+      </c>
+      <c r="V33">
+        <v>9</v>
+      </c>
+      <c r="W33">
+        <v>0.2478</v>
+      </c>
+      <c r="X33">
+        <v>0.2205</v>
+      </c>
+      <c r="Y33">
+        <v>1.0112</v>
+      </c>
+      <c r="AA33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC33" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD33">
+        <v>1.8</v>
+      </c>
+      <c r="AE33" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF33">
+        <v>0.2019</v>
+      </c>
+      <c r="AG33">
+        <v>1.087</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" t="s">
+        <v>79</v>
+      </c>
+      <c r="G34">
+        <v>824639</v>
+      </c>
+      <c r="H34" t="s">
+        <v>96</v>
+      </c>
+      <c r="I34">
+        <v>1.2</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0.2283</v>
+      </c>
+      <c r="N34">
+        <v>5</v>
+      </c>
+      <c r="O34">
+        <v>20</v>
+      </c>
+      <c r="P34">
+        <v>4.24</v>
+      </c>
+      <c r="Q34">
+        <v>0.2</v>
+      </c>
+      <c r="R34">
+        <v>0.091</v>
+      </c>
+      <c r="S34" t="s">
+        <v>56</v>
+      </c>
+      <c r="T34">
+        <v>0.2231</v>
+      </c>
+      <c r="U34">
+        <v>0.2215</v>
+      </c>
+      <c r="V34">
+        <v>9</v>
+      </c>
+      <c r="W34">
+        <v>0.2191</v>
+      </c>
+      <c r="X34">
+        <v>0.2205</v>
+      </c>
+      <c r="Y34">
+        <v>0.9381</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD34">
+        <v>1.06</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF34">
+        <v>0.2257</v>
+      </c>
+      <c r="AG34">
+        <v>1.0119</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>1.06</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-18.xlsx
+++ b/data/k-props/2026-08-18.xlsx
@@ -133,178 +133,178 @@
     <t>08/18/2026</t>
   </si>
   <si>
+    <t>Carlos Rodón</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>&gt;=7</t>
+  </si>
+  <si>
     <t>Shane Baz</t>
   </si>
   <si>
-    <t>New York Yankees @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>6-7</t>
   </si>
   <si>
+    <t>Keider Montero</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_projected_regulars</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Carson Whisenhunt</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Foster Griffin</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>José Soriano</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Cade Gibson</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Role unknown</t>
+  </si>
+  <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Ranger Suarez</t>
+  </si>
+  <si>
+    <t>Robbie Ray</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ New York Mets</t>
+  </si>
+  <si>
+    <t>Zac Thornton</t>
+  </si>
+  <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Athletics @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Daniel Lynch IV</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
+  </si>
+  <si>
+    <t>Tyler Mahle</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Zebby Matthews</t>
+  </si>
+  <si>
+    <t>Bryce Miller</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Kyle Harrison</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Bryan Hudson</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>Cristian Javier</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Eric Lauer</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Ryan Feltner</t>
+  </si>
+  <si>
     <t>Carlos Rodon</t>
   </si>
   <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>Carson Whisenhunt</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Foster Griffin</t>
-  </si>
-  <si>
-    <t>Keider Montero</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t>Zack Wheeler</t>
-  </si>
-  <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
-    <t>&gt;=7</t>
-  </si>
-  <si>
     <t>Jose Soriano</t>
   </si>
   <si>
-    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
-    <t>Ranger Suarez</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Robbie Ray</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ New York Mets</t>
-  </si>
-  <si>
     <t>Zach Thornton</t>
   </si>
   <si>
-    <t>Zebby Matthews</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>Jack Perkins</t>
-  </si>
-  <si>
-    <t>Athletics @ Kansas City Royals</t>
-  </si>
-  <si>
-    <t>Kyle Harrison</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Bryce Miller</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Texas Rangers</t>
-  </si>
-  <si>
     <t>Jackson Kent</t>
   </si>
   <si>
     <t>George Klassen</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Cristian Javier</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Eric Lauer</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Ryan Feltner</t>
-  </si>
-  <si>
-    <t>Carlos Rodón</t>
-  </si>
-  <si>
-    <t>José Soriano</t>
-  </si>
-  <si>
-    <t>Cade Gibson</t>
-  </si>
-  <si>
-    <t>Role unknown</t>
-  </si>
-  <si>
-    <t>Zac Thornton</t>
-  </si>
-  <si>
-    <t>Daniel Lynch IV</t>
-  </si>
-  <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Bryan Hudson</t>
   </si>
 </sst>
 </file>
@@ -817,15 +817,6 @@
       <c r="B2" t="s">
         <v>40</v>
       </c>
-      <c r="C2">
-        <v>5.5</v>
-      </c>
-      <c r="D2">
-        <v>-146</v>
-      </c>
-      <c r="E2">
-        <v>118</v>
-      </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
@@ -836,7 +827,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -845,46 +836,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>0.204</v>
+        <v>0.268</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="P2">
-        <v>4.29</v>
+        <v>4.19</v>
       </c>
       <c r="Q2">
-        <v>0.1983</v>
+        <v>0.2832</v>
       </c>
       <c r="R2">
-        <v>0.367</v>
+        <v>0.361</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2603</v>
+        <v>0.2607</v>
       </c>
       <c r="U2">
-        <v>0.265</v>
+        <v>0.246</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2449</v>
+        <v>0.2568</v>
       </c>
       <c r="X2">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y2">
-        <v>1.0455</v>
+        <v>1.0725</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -893,22 +884,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>6.21</v>
+        <v>7.37</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2019</v>
+        <v>0.2735</v>
       </c>
       <c r="AG2">
-        <v>1.1808</v>
+        <v>1.1662</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>6.21</v>
+        <v>7.37</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -919,31 +910,73 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D3">
-        <v>-154</v>
+        <v>-146</v>
       </c>
       <c r="E3">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" t="s">
-        <v>44</v>
+      <c r="G3">
+        <v>824803</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I3">
+        <v>5.8</v>
+      </c>
+      <c r="J3" t="b">
+        <v>0</v>
+      </c>
+      <c r="K3" t="b">
+        <v>0</v>
       </c>
       <c r="L3">
         <v>6</v>
       </c>
+      <c r="M3">
+        <v>0.204</v>
+      </c>
+      <c r="N3">
+        <v>5</v>
+      </c>
+      <c r="O3">
+        <v>116</v>
+      </c>
+      <c r="P3">
+        <v>4.29</v>
+      </c>
+      <c r="Q3">
+        <v>0.1983</v>
+      </c>
+      <c r="R3">
+        <v>0.367</v>
+      </c>
       <c r="S3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V3" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T3">
+        <v>0.2603</v>
+      </c>
+      <c r="U3">
+        <v>0.265</v>
+      </c>
+      <c r="V3">
+        <v>9</v>
+      </c>
+      <c r="W3">
+        <v>0.2449</v>
+      </c>
+      <c r="X3">
+        <v>0.2235</v>
+      </c>
+      <c r="Y3">
+        <v>1.0455</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -951,8 +984,23 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
+      <c r="AD3">
+        <v>6.13</v>
+      </c>
       <c r="AE3" t="s">
-        <v>44</v>
+        <v>47</v>
+      </c>
+      <c r="AF3">
+        <v>0.2019</v>
+      </c>
+      <c r="AG3">
+        <v>1.1647</v>
+      </c>
+      <c r="AH3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>6.13</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -960,28 +1008,28 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D4">
-        <v>-107</v>
+        <v>-122</v>
       </c>
       <c r="E4">
-        <v>-113</v>
+        <v>105</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4">
-        <v>824475</v>
+        <v>823341</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -993,43 +1041,43 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>0.1765</v>
+        <v>0.167</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="P4">
-        <v>4.35</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>0.1488</v>
+        <v>0.1379</v>
       </c>
       <c r="R4">
-        <v>0.377</v>
+        <v>0.367</v>
       </c>
       <c r="S4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="T4">
-        <v>0.2193</v>
+        <v>0.2109</v>
       </c>
       <c r="U4">
-        <v>0.199</v>
+        <v>0.2349</v>
       </c>
       <c r="V4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>0.1828</v>
+        <v>0.2358</v>
       </c>
       <c r="X4">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y4">
-        <v>0.9052</v>
+        <v>1.0215</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1038,22 +1086,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AE4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF4">
-        <v>0.166</v>
+        <v>0.1563</v>
       </c>
       <c r="AG4">
-        <v>0.9947</v>
+        <v>0.9436</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1061,28 +1109,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>5.5</v>
       </c>
       <c r="D5">
-        <v>115</v>
+        <v>-120</v>
       </c>
       <c r="E5">
-        <v>-136</v>
+        <v>105</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5">
-        <v>824475</v>
+        <v>823341</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1094,43 +1142,43 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>0.2108</v>
+        <v>0.27</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="P5">
-        <v>4.24</v>
+        <v>4.06</v>
       </c>
       <c r="Q5">
-        <v>0.2727</v>
+        <v>0.2389</v>
       </c>
       <c r="R5">
-        <v>0.355</v>
+        <v>0.361</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.2785</v>
+        <v>0.1988</v>
       </c>
       <c r="U5">
-        <v>0.2747</v>
+        <v>0.178</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2552</v>
+        <v>0.2235</v>
       </c>
       <c r="X5">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y5">
-        <v>1.0796</v>
+        <v>0.8825</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1139,22 +1187,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>6.87</v>
+        <v>4.86</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AF5">
-        <v>0.2328</v>
+        <v>0.2588</v>
       </c>
       <c r="AG5">
-        <v>1.2633</v>
+        <v>0.8895</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>6.87</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1162,7 +1210,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1174,7 +1222,7 @@
         <v>-103</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>824398</v>
@@ -1228,7 +1276,7 @@
         <v>0.2259</v>
       </c>
       <c r="X6">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y6">
         <v>0.9198</v>
@@ -1240,22 +1288,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
       <c r="AE6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF6">
         <v>0.1754</v>
       </c>
       <c r="AG6">
-        <v>0.8972</v>
+        <v>0.885</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>3.14</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1263,7 +1311,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>5.5</v>
@@ -1275,7 +1323,7 @@
         <v>-110</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G7">
         <v>824398</v>
@@ -1329,7 +1377,7 @@
         <v>0.2271</v>
       </c>
       <c r="X7">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y7">
         <v>1.0041</v>
@@ -1341,22 +1389,22 @@
         <v>44</v>
       </c>
       <c r="AD7">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="AE7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF7">
         <v>0.1877</v>
       </c>
       <c r="AG7">
-        <v>1.0393</v>
+        <v>1.0252</v>
       </c>
       <c r="AH7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="8" spans="1:39" x14ac:dyDescent="0.25">
@@ -1364,28 +1412,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C8">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="D8">
-        <v>-122</v>
+        <v>115</v>
       </c>
       <c r="E8">
-        <v>105</v>
+        <v>-136</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8">
-        <v>823341</v>
+        <v>824475</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1397,43 +1445,43 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>0.167</v>
+        <v>0.2108</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="P8">
-        <v>4</v>
+        <v>4.24</v>
       </c>
       <c r="Q8">
-        <v>0.1379</v>
+        <v>0.2727</v>
       </c>
       <c r="R8">
-        <v>0.367</v>
+        <v>0.355</v>
       </c>
       <c r="S8" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2109</v>
+        <v>0.2785</v>
       </c>
       <c r="U8">
-        <v>0.2349</v>
+        <v>0.2747</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>0.2358</v>
+        <v>0.2552</v>
       </c>
       <c r="X8">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y8">
-        <v>1.0215</v>
+        <v>1.0796</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1442,22 +1490,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>3.5</v>
+        <v>6.78</v>
       </c>
       <c r="AE8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF8">
-        <v>0.1563</v>
+        <v>0.2328</v>
       </c>
       <c r="AG8">
-        <v>0.9566</v>
+        <v>1.2461</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>3.5</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1465,28 +1513,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9">
+        <v>4.5</v>
+      </c>
+      <c r="D9">
+        <v>-107</v>
+      </c>
+      <c r="E9">
+        <v>-113</v>
+      </c>
+      <c r="F9" t="s">
         <v>57</v>
       </c>
-      <c r="C9">
-        <v>5.5</v>
-      </c>
-      <c r="D9">
-        <v>-120</v>
-      </c>
-      <c r="E9">
-        <v>105</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
       <c r="G9">
-        <v>823341</v>
+        <v>824475</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1498,43 +1546,43 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>0.27</v>
+        <v>0.1765</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="P9">
-        <v>4.06</v>
+        <v>4.35</v>
       </c>
       <c r="Q9">
-        <v>0.2389</v>
+        <v>0.1488</v>
       </c>
       <c r="R9">
-        <v>0.361</v>
+        <v>0.377</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.1988</v>
+        <v>0.2193</v>
       </c>
       <c r="U9">
-        <v>0.178</v>
+        <v>0.199</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
+        <v>0.1828</v>
+      </c>
+      <c r="X9">
         <v>0.2235</v>
       </c>
-      <c r="X9">
-        <v>0.2205</v>
-      </c>
       <c r="Y9">
-        <v>0.8825</v>
+        <v>0.9052</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1543,22 +1591,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>4.93</v>
+        <v>3.41</v>
       </c>
       <c r="AE9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF9">
-        <v>0.2588</v>
+        <v>0.166</v>
       </c>
       <c r="AG9">
-        <v>0.9017</v>
+        <v>0.9812</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>4.93</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1566,28 +1614,19 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C10">
-        <v>7.5</v>
-      </c>
-      <c r="D10">
-        <v>125</v>
-      </c>
-      <c r="E10">
-        <v>-147</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G10">
-        <v>823423</v>
+        <v>822938</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1596,46 +1635,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M10">
-        <v>0.3018</v>
+        <v>0.2423</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="P10">
-        <v>3.94</v>
+        <v>4.14</v>
       </c>
       <c r="Q10">
-        <v>0.2929</v>
+        <v>0.1776</v>
       </c>
       <c r="R10">
-        <v>0.331</v>
+        <v>0.349</v>
       </c>
       <c r="S10" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T10">
-        <v>0.2372</v>
+        <v>0.1843</v>
       </c>
       <c r="U10">
-        <v>0.2276</v>
+        <v>0.1802</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.2114</v>
+        <v>0.1897</v>
       </c>
       <c r="X10">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y10">
-        <v>0.9685</v>
+        <v>0.88</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1644,22 +1683,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>7.07</v>
+        <v>3.67</v>
       </c>
       <c r="AE10" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="AF10">
-        <v>0.2988</v>
+        <v>0.2197</v>
       </c>
       <c r="AG10">
-        <v>1.0759</v>
+        <v>0.8244</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>7.07</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1670,31 +1709,73 @@
         <v>61</v>
       </c>
       <c r="C11">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D11">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E11">
-        <v>-145</v>
+        <v>-125</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="G11">
+        <v>822938</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
       </c>
       <c r="L11">
         <v>6</v>
       </c>
+      <c r="M11">
+        <v>0.1413</v>
+      </c>
+      <c r="N11">
+        <v>5</v>
+      </c>
+      <c r="O11">
+        <v>124</v>
+      </c>
+      <c r="P11">
+        <v>4</v>
+      </c>
+      <c r="Q11">
+        <v>0.129</v>
+      </c>
+      <c r="R11">
+        <v>0.383</v>
+      </c>
       <c r="S11" t="s">
-        <v>44</v>
-      </c>
-      <c r="V11" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T11">
+        <v>0.1965</v>
+      </c>
+      <c r="U11">
+        <v>0.1807</v>
+      </c>
+      <c r="V11">
+        <v>9</v>
+      </c>
+      <c r="W11">
+        <v>0.19</v>
+      </c>
+      <c r="X11">
+        <v>0.2235</v>
+      </c>
+      <c r="Y11">
+        <v>0.9953</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1702,8 +1783,23 @@
       <c r="AC11" t="s">
         <v>44</v>
       </c>
+      <c r="AD11">
+        <v>2.87</v>
+      </c>
       <c r="AE11" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AF11">
+        <v>0.1366</v>
+      </c>
+      <c r="AG11">
+        <v>0.8793</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>2.87</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1711,76 +1807,55 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" t="s">
         <v>63</v>
       </c>
-      <c r="C12">
-        <v>3.5</v>
-      </c>
-      <c r="D12">
-        <v>110</v>
-      </c>
-      <c r="E12">
-        <v>-125</v>
-      </c>
-      <c r="F12" t="s">
-        <v>62</v>
-      </c>
       <c r="G12">
-        <v>822938</v>
+        <v>823423</v>
       </c>
       <c r="H12" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="I12">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>0.1413</v>
-      </c>
-      <c r="N12">
-        <v>5</v>
-      </c>
-      <c r="O12">
-        <v>124</v>
+        <v>0.1859</v>
       </c>
       <c r="P12">
-        <v>4</v>
-      </c>
-      <c r="Q12">
-        <v>0.129</v>
-      </c>
-      <c r="R12">
-        <v>0.383</v>
+        <v>4.63</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1965</v>
+        <v>0.1753</v>
       </c>
       <c r="U12">
-        <v>0.1807</v>
+        <v>0.1771</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.19</v>
+        <v>0.233</v>
       </c>
       <c r="X12">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y12">
-        <v>0.9953</v>
+        <v>0.9664</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1789,22 +1864,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
       <c r="AE12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF12">
-        <v>0.1366</v>
+        <v>0.1859</v>
       </c>
       <c r="AG12">
-        <v>0.8914</v>
+        <v>0.7844</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>2.91</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1812,28 +1887,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C13">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="D13">
-        <v>-102</v>
+        <v>125</v>
       </c>
       <c r="E13">
-        <v>-106</v>
+        <v>-147</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G13">
-        <v>824723</v>
+        <v>823423</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1845,43 +1920,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.2472</v>
+        <v>0.3018</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="P13">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="Q13">
-        <v>0.2143</v>
+        <v>0.2929</v>
       </c>
       <c r="R13">
-        <v>0.296</v>
+        <v>0.331</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2613</v>
+        <v>0.2393</v>
       </c>
       <c r="U13">
-        <v>0.1821</v>
+        <v>0.2184</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.1751</v>
+        <v>0.2114</v>
       </c>
       <c r="X13">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y13">
-        <v>0.88</v>
+        <v>0.8983</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1890,22 +1965,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>5.25</v>
+        <v>6.52</v>
       </c>
       <c r="AE13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF13">
-        <v>0.2375</v>
+        <v>0.2988</v>
       </c>
       <c r="AG13">
-        <v>1.185</v>
+        <v>1.0707</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>5.25</v>
+        <v>6.52</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1925,7 +2000,7 @@
         <v>110</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>824723</v>
@@ -1979,7 +2054,7 @@
         <v>0.2168</v>
       </c>
       <c r="X14">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y14">
         <v>0.9954</v>
@@ -1991,22 +2066,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="AE14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF14">
         <v>0.1621</v>
       </c>
       <c r="AG14">
-        <v>0.844</v>
+        <v>0.8325</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2014,28 +2089,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C15">
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>-113</v>
+        <v>-102</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>-106</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G15">
-        <v>823586</v>
+        <v>824723</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2047,43 +2122,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.204</v>
+        <v>0.2472</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="P15">
-        <v>4.21</v>
+        <v>4.12</v>
       </c>
       <c r="Q15">
-        <v>0.2072</v>
+        <v>0.2143</v>
       </c>
       <c r="R15">
-        <v>0.357</v>
+        <v>0.296</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.246</v>
+        <v>0.2613</v>
       </c>
       <c r="U15">
-        <v>0.249</v>
+        <v>0.1821</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W15">
-        <v>0.2325</v>
+        <v>0.1751</v>
       </c>
       <c r="X15">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y15">
-        <v>0.9557</v>
+        <v>0.88</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2092,22 +2167,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.02</v>
+        <v>5.18</v>
       </c>
       <c r="AE15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF15">
-        <v>0.2051</v>
+        <v>0.2375</v>
       </c>
       <c r="AG15">
-        <v>1.116</v>
+        <v>1.1689</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.02</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2118,31 +2193,73 @@
         <v>69</v>
       </c>
       <c r="C16">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D16">
-        <v>-109</v>
+        <v>-113</v>
       </c>
       <c r="E16">
-        <v>-104</v>
+        <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>68</v>
-      </c>
-      <c r="G16" t="s">
-        <v>44</v>
+        <v>70</v>
+      </c>
+      <c r="G16">
+        <v>823586</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I16">
+        <v>5.4</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>0</v>
       </c>
       <c r="L16">
         <v>6</v>
       </c>
+      <c r="M16">
+        <v>0.204</v>
+      </c>
+      <c r="N16">
+        <v>5</v>
+      </c>
+      <c r="O16">
+        <v>111</v>
+      </c>
+      <c r="P16">
+        <v>4.21</v>
+      </c>
+      <c r="Q16">
+        <v>0.2072</v>
+      </c>
+      <c r="R16">
+        <v>0.357</v>
+      </c>
       <c r="S16" t="s">
-        <v>44</v>
-      </c>
-      <c r="V16" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T16">
+        <v>0.246</v>
+      </c>
+      <c r="U16">
+        <v>0.249</v>
+      </c>
+      <c r="V16">
+        <v>8</v>
+      </c>
+      <c r="W16">
+        <v>0.2325</v>
+      </c>
+      <c r="X16">
+        <v>0.2235</v>
+      </c>
+      <c r="Y16">
+        <v>0.9557</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2150,8 +2267,23 @@
       <c r="AC16" t="s">
         <v>44</v>
       </c>
+      <c r="AD16">
+        <v>4.95</v>
+      </c>
       <c r="AE16" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AF16">
+        <v>0.2051</v>
+      </c>
+      <c r="AG16">
+        <v>1.1008</v>
+      </c>
+      <c r="AH16">
+        <v>0</v>
+      </c>
+      <c r="AM16">
+        <v>4.95</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2159,22 +2291,13 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" t="s">
         <v>70</v>
       </c>
-      <c r="C17">
-        <v>4.5</v>
-      </c>
-      <c r="D17">
-        <v>112</v>
-      </c>
-      <c r="E17">
-        <v>-120</v>
-      </c>
-      <c r="F17" t="s">
-        <v>71</v>
-      </c>
       <c r="G17">
-        <v>823667</v>
+        <v>823586</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
@@ -2189,46 +2312,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M17">
-        <v>0.199</v>
+        <v>0.1638</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="P17">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="Q17">
-        <v>0.2054</v>
+        <v>0.1273</v>
       </c>
       <c r="R17">
-        <v>0.359</v>
+        <v>0.355</v>
       </c>
       <c r="S17" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T17">
-        <v>0.2372</v>
+        <v>0.183</v>
       </c>
       <c r="U17">
-        <v>0.2298</v>
+        <v>0.1798</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2179</v>
+        <v>0.2187</v>
       </c>
       <c r="X17">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y17">
-        <v>0.996</v>
+        <v>1.0025</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2237,22 +2360,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>5.22</v>
+        <v>2.74</v>
       </c>
       <c r="AE17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF17">
-        <v>0.2013</v>
+        <v>0.1509</v>
       </c>
       <c r="AG17">
-        <v>1.076</v>
+        <v>0.8189</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>5.22</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2263,25 +2386,25 @@
         <v>72</v>
       </c>
       <c r="C18">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D18">
-        <v>-108</v>
+        <v>-140</v>
       </c>
       <c r="E18">
-        <v>-104</v>
+        <v>130</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G18">
-        <v>823667</v>
+        <v>824075</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2293,43 +2416,43 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.2344</v>
+        <v>0.25</v>
       </c>
       <c r="N18">
         <v>5</v>
       </c>
       <c r="O18">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P18">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Q18">
-        <v>0.2883</v>
+        <v>0.1964</v>
       </c>
       <c r="R18">
-        <v>0.357</v>
+        <v>0.359</v>
       </c>
       <c r="S18" t="s">
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.1989</v>
+        <v>0.2029</v>
       </c>
       <c r="U18">
-        <v>0.1944</v>
+        <v>0.2085</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2114</v>
+        <v>0.2096</v>
       </c>
       <c r="X18">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y18">
-        <v>0.9597</v>
+        <v>0.9401</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2338,22 +2461,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.92</v>
+        <v>4.18</v>
       </c>
       <c r="AE18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF18">
-        <v>0.2536</v>
+        <v>0.2308</v>
       </c>
       <c r="AG18">
-        <v>0.9021</v>
+        <v>0.9077</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.92</v>
+        <v>4.18</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2361,76 +2484,67 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" t="s">
         <v>73</v>
-      </c>
-      <c r="C19">
-        <v>3.5</v>
-      </c>
-      <c r="D19">
-        <v>-140</v>
-      </c>
-      <c r="E19">
-        <v>130</v>
-      </c>
-      <c r="F19" t="s">
-        <v>74</v>
       </c>
       <c r="G19">
         <v>824075</v>
       </c>
       <c r="H19" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="I19">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="J19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="b">
         <v>0</v>
       </c>
       <c r="L19">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M19">
+        <v>0.197</v>
+      </c>
+      <c r="N19">
+        <v>2</v>
+      </c>
+      <c r="O19">
+        <v>20</v>
+      </c>
+      <c r="P19">
+        <v>4.06</v>
+      </c>
+      <c r="Q19">
         <v>0.25</v>
       </c>
-      <c r="N19">
-        <v>5</v>
-      </c>
-      <c r="O19">
-        <v>112</v>
-      </c>
-      <c r="P19">
-        <v>4.6</v>
-      </c>
-      <c r="Q19">
-        <v>0.1964</v>
-      </c>
       <c r="R19">
-        <v>0.359</v>
+        <v>0.091</v>
       </c>
       <c r="S19" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="T19">
-        <v>0.2029</v>
+        <v>0.2396</v>
       </c>
       <c r="U19">
-        <v>0.2085</v>
+        <v>0.2076</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>0.2096</v>
+        <v>0.2478</v>
       </c>
       <c r="X19">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y19">
-        <v>0.9401</v>
+        <v>1.0112</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2439,22 +2553,22 @@
         <v>44</v>
       </c>
       <c r="AD19">
-        <v>4.23</v>
+        <v>1.78</v>
       </c>
       <c r="AE19" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF19">
-        <v>0.2308</v>
+        <v>0.2019</v>
       </c>
       <c r="AG19">
-        <v>0.9202</v>
+        <v>1.0722</v>
       </c>
       <c r="AH19">
         <v>0</v>
       </c>
       <c r="AM19">
-        <v>4.23</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2462,28 +2576,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C20">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D20">
-        <v>-160</v>
+        <v>-108</v>
       </c>
       <c r="E20">
-        <v>135</v>
+        <v>-104</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20">
-        <v>823749</v>
+        <v>823667</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2495,43 +2609,43 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>0.2969</v>
+        <v>0.2344</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="P20">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>0.2872</v>
+        <v>0.2883</v>
       </c>
       <c r="R20">
-        <v>0.32</v>
+        <v>0.357</v>
       </c>
       <c r="S20" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T20">
-        <v>0.2086</v>
+        <v>0.1989</v>
       </c>
       <c r="U20">
-        <v>0.1968</v>
+        <v>0.1944</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2395</v>
+        <v>0.2114</v>
       </c>
       <c r="X20">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y20">
-        <v>1.0092</v>
+        <v>0.9597</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2540,22 +2654,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>5.67</v>
+        <v>4.85</v>
       </c>
       <c r="AE20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF20">
-        <v>0.2938</v>
+        <v>0.2536</v>
       </c>
       <c r="AG20">
-        <v>0.946</v>
+        <v>0.8898</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>5.67</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2563,22 +2677,22 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
+        <v>78</v>
+      </c>
+      <c r="C21">
+        <v>4.5</v>
+      </c>
+      <c r="D21">
+        <v>112</v>
+      </c>
+      <c r="E21">
+        <v>-120</v>
+      </c>
+      <c r="F21" t="s">
         <v>77</v>
       </c>
-      <c r="C21">
-        <v>5.5</v>
-      </c>
-      <c r="D21">
-        <v>120</v>
-      </c>
-      <c r="E21">
-        <v>-150</v>
-      </c>
-      <c r="F21" t="s">
-        <v>76</v>
-      </c>
       <c r="G21">
-        <v>823749</v>
+        <v>823667</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
@@ -2596,43 +2710,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.2538</v>
+        <v>0.199</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="P21">
-        <v>3.89</v>
+        <v>4.25</v>
       </c>
       <c r="Q21">
-        <v>0.1638</v>
+        <v>0.2054</v>
       </c>
       <c r="R21">
-        <v>0.367</v>
+        <v>0.359</v>
       </c>
       <c r="S21" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2357</v>
+        <v>0.2465</v>
       </c>
       <c r="U21">
-        <v>0.234</v>
+        <v>0.2254</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2155</v>
+        <v>0.2179</v>
       </c>
       <c r="X21">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y21">
-        <v>1.0057</v>
+        <v>0.9903</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2641,22 +2755,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.28</v>
+        <v>5.32</v>
       </c>
       <c r="AE21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF21">
-        <v>0.2207</v>
+        <v>0.2013</v>
       </c>
       <c r="AG21">
-        <v>1.0691</v>
+        <v>1.1027</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.28</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2664,28 +2778,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C22">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="D22">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E22">
-        <v>-138</v>
+        <v>-150</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G22">
-        <v>824639</v>
+        <v>823749</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2697,43 +2811,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2347</v>
+        <v>0.2538</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="P22">
-        <v>4.23</v>
+        <v>3.89</v>
       </c>
       <c r="Q22">
-        <v>0.1864</v>
+        <v>0.1638</v>
       </c>
       <c r="R22">
-        <v>0.371</v>
+        <v>0.367</v>
       </c>
       <c r="S22" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="T22">
-        <v>0.2258</v>
+        <v>0.2357</v>
       </c>
       <c r="U22">
-        <v>0.2444</v>
+        <v>0.234</v>
       </c>
       <c r="V22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>0.2368</v>
+        <v>0.2155</v>
       </c>
       <c r="X22">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y22">
-        <v>1.0402</v>
+        <v>1.0057</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2742,22 +2856,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.43</v>
+        <v>5.21</v>
       </c>
       <c r="AE22" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF22">
-        <v>0.2168</v>
+        <v>0.2207</v>
       </c>
       <c r="AG22">
-        <v>1.0241</v>
+        <v>1.0545</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.43</v>
+        <v>5.21</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2765,28 +2879,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
+        <v>81</v>
+      </c>
+      <c r="C23">
+        <v>5.5</v>
+      </c>
+      <c r="D23">
+        <v>-160</v>
+      </c>
+      <c r="E23">
+        <v>135</v>
+      </c>
+      <c r="F23" t="s">
         <v>80</v>
       </c>
-      <c r="C23">
-        <v>3.5</v>
-      </c>
-      <c r="D23">
-        <v>-105</v>
-      </c>
-      <c r="E23">
-        <v>-103</v>
-      </c>
-      <c r="F23" t="s">
-        <v>81</v>
-      </c>
       <c r="G23">
-        <v>822859</v>
+        <v>823749</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2798,43 +2912,43 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.1644</v>
+        <v>0.2969</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="P23">
-        <v>4.22</v>
+        <v>4.11</v>
       </c>
       <c r="Q23">
-        <v>0.1892</v>
+        <v>0.2872</v>
       </c>
       <c r="R23">
-        <v>0.357</v>
+        <v>0.32</v>
       </c>
       <c r="S23" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2084</v>
+        <v>0.2048</v>
       </c>
       <c r="U23">
-        <v>0.2123</v>
+        <v>0.1923</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2076</v>
+        <v>0.2395</v>
       </c>
       <c r="X23">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y23">
-        <v>0.9941</v>
+        <v>1.0058</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2843,22 +2957,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>3.2</v>
+        <v>5.47</v>
       </c>
       <c r="AE23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF23">
-        <v>0.1733</v>
+        <v>0.2938</v>
       </c>
       <c r="AG23">
-        <v>0.9451</v>
+        <v>0.9161</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>3.2</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2869,31 +2983,73 @@
         <v>82</v>
       </c>
       <c r="C24">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D24">
-        <v>142</v>
+        <v>-105</v>
       </c>
       <c r="E24">
-        <v>-156</v>
+        <v>-103</v>
       </c>
       <c r="F24" t="s">
-        <v>81</v>
-      </c>
-      <c r="G24" t="s">
-        <v>44</v>
+        <v>83</v>
+      </c>
+      <c r="G24">
+        <v>822859</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I24">
+        <v>4.7</v>
+      </c>
+      <c r="J24" t="b">
+        <v>0</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
+      <c r="M24">
+        <v>0.1644</v>
+      </c>
+      <c r="N24">
+        <v>5</v>
+      </c>
+      <c r="O24">
+        <v>111</v>
+      </c>
+      <c r="P24">
+        <v>4.22</v>
+      </c>
+      <c r="Q24">
+        <v>0.1892</v>
+      </c>
+      <c r="R24">
+        <v>0.357</v>
+      </c>
       <c r="S24" t="s">
-        <v>44</v>
-      </c>
-      <c r="V24" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T24">
+        <v>0.2271</v>
+      </c>
+      <c r="U24">
+        <v>0.2265</v>
+      </c>
+      <c r="V24">
+        <v>9</v>
+      </c>
+      <c r="W24">
+        <v>0.2076</v>
+      </c>
+      <c r="X24">
+        <v>0.2235</v>
+      </c>
+      <c r="Y24">
+        <v>0.989</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -2901,8 +3057,23 @@
       <c r="AC24" t="s">
         <v>44</v>
       </c>
+      <c r="AD24">
+        <v>3.43</v>
+      </c>
       <c r="AE24" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AF24">
+        <v>0.1733</v>
+      </c>
+      <c r="AG24">
+        <v>1.016</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>3.43</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2910,34 +3081,67 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25">
-        <v>4.5</v>
-      </c>
-      <c r="D25">
-        <v>122</v>
-      </c>
-      <c r="E25">
-        <v>-153</v>
+        <v>84</v>
       </c>
       <c r="F25" t="s">
-        <v>84</v>
-      </c>
-      <c r="G25" t="s">
-        <v>44</v>
+        <v>85</v>
+      </c>
+      <c r="G25">
+        <v>824639</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>75</v>
+      </c>
+      <c r="I25">
+        <v>1.2</v>
+      </c>
+      <c r="J25" t="b">
+        <v>1</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
       </c>
       <c r="L25">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0.2283</v>
+      </c>
+      <c r="N25">
+        <v>5</v>
+      </c>
+      <c r="O25">
+        <v>20</v>
+      </c>
+      <c r="P25">
+        <v>4.24</v>
+      </c>
+      <c r="Q25">
+        <v>0.2</v>
+      </c>
+      <c r="R25">
+        <v>0.091</v>
       </c>
       <c r="S25" t="s">
-        <v>44</v>
-      </c>
-      <c r="V25" t="s">
-        <v>44</v>
+        <v>50</v>
+      </c>
+      <c r="T25">
+        <v>0.2231</v>
+      </c>
+      <c r="U25">
+        <v>0.2215</v>
+      </c>
+      <c r="V25">
+        <v>9</v>
+      </c>
+      <c r="W25">
+        <v>0.2191</v>
+      </c>
+      <c r="X25">
+        <v>0.2235</v>
+      </c>
+      <c r="Y25">
+        <v>0.9381</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -2945,8 +3149,23 @@
       <c r="AC25" t="s">
         <v>44</v>
       </c>
+      <c r="AD25">
+        <v>1.05</v>
+      </c>
       <c r="AE25" t="s">
-        <v>44</v>
+        <v>51</v>
+      </c>
+      <c r="AF25">
+        <v>0.2257</v>
+      </c>
+      <c r="AG25">
+        <v>0.9981</v>
+      </c>
+      <c r="AH25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>1.05</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -2954,28 +3173,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C26">
+        <v>6.5</v>
+      </c>
+      <c r="D26">
+        <v>121</v>
+      </c>
+      <c r="E26">
+        <v>-138</v>
+      </c>
+      <c r="F26" t="s">
         <v>85</v>
       </c>
-      <c r="C26">
-        <v>4.5</v>
-      </c>
-      <c r="D26">
-        <v>-113</v>
-      </c>
-      <c r="E26">
-        <v>-105</v>
-      </c>
-      <c r="F26" t="s">
-        <v>84</v>
-      </c>
       <c r="G26">
-        <v>824154</v>
+        <v>824639</v>
       </c>
       <c r="H26" t="s">
-        <v>86</v>
+        <v>42</v>
       </c>
       <c r="I26">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -2987,43 +3206,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.1678</v>
+        <v>0.2347</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="P26">
-        <v>4.61</v>
+        <v>4.23</v>
       </c>
       <c r="Q26">
-        <v>0.1209</v>
+        <v>0.1864</v>
       </c>
       <c r="R26">
-        <v>0.313</v>
+        <v>0.371</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2136</v>
+        <v>0.2459</v>
       </c>
       <c r="U26">
-        <v>0.2242</v>
+        <v>0.2514</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2504</v>
+        <v>0.2368</v>
       </c>
       <c r="X26">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y26">
-        <v>0.9877</v>
+        <v>1.0865</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3032,22 +3251,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>2.63</v>
+        <v>6.1</v>
       </c>
       <c r="AE26" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AF26">
-        <v>0.1531</v>
+        <v>0.2168</v>
       </c>
       <c r="AG26">
-        <v>0.9687</v>
+        <v>1.1002</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>2.63</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3058,25 +3277,25 @@
         <v>87</v>
       </c>
       <c r="C27">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D27">
-        <v>-120</v>
+        <v>-113</v>
       </c>
       <c r="E27">
-        <v>103</v>
+        <v>-105</v>
       </c>
       <c r="F27" t="s">
         <v>88</v>
       </c>
       <c r="G27">
-        <v>824319</v>
+        <v>824154</v>
       </c>
       <c r="H27" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="I27">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3088,43 +3307,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1514</v>
+        <v>0.1678</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="P27">
-        <v>4.23</v>
+        <v>4.61</v>
       </c>
       <c r="Q27">
-        <v>0.1624</v>
+        <v>0.1209</v>
       </c>
       <c r="R27">
-        <v>0.369</v>
+        <v>0.313</v>
       </c>
       <c r="S27" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2216</v>
+        <v>0.2136</v>
       </c>
       <c r="U27">
-        <v>0.2193</v>
+        <v>0.2242</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.247</v>
+        <v>0.2504</v>
       </c>
       <c r="X27">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y27">
-        <v>1.0013</v>
+        <v>0.9877</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3133,22 +3352,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>3.41</v>
+        <v>2.59</v>
       </c>
       <c r="AE27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF27">
-        <v>0.1555</v>
+        <v>0.1531</v>
       </c>
       <c r="AG27">
-        <v>1.0053</v>
+        <v>0.9555</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>3.41</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3156,19 +3375,19 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28">
         <v>3.5</v>
       </c>
       <c r="D28">
-        <v>117</v>
+        <v>-120</v>
       </c>
       <c r="E28">
-        <v>-144</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="G28">
         <v>824319</v>
@@ -3177,7 +3396,7 @@
         <v>42</v>
       </c>
       <c r="I28">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J28" t="b">
         <v>0</v>
@@ -3189,43 +3408,43 @@
         <v>6</v>
       </c>
       <c r="M28">
-        <v>0.1597</v>
+        <v>0.1514</v>
       </c>
       <c r="N28">
         <v>5</v>
       </c>
       <c r="O28">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P28">
-        <v>4.39</v>
+        <v>4.23</v>
       </c>
       <c r="Q28">
-        <v>0.1217</v>
+        <v>0.1624</v>
       </c>
       <c r="R28">
-        <v>0.365</v>
+        <v>0.369</v>
       </c>
       <c r="S28" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="T28">
-        <v>0.2783</v>
+        <v>0.2216</v>
       </c>
       <c r="U28">
-        <v>0.2137</v>
+        <v>0.2193</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>0.2061</v>
+        <v>0.247</v>
       </c>
       <c r="X28">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y28">
-        <v>1.0055</v>
+        <v>1.0013</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3234,22 +3453,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>3.93</v>
+        <v>3.36</v>
       </c>
       <c r="AE28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF28">
-        <v>0.1458</v>
+        <v>0.1555</v>
       </c>
       <c r="AG28">
-        <v>1.2623</v>
+        <v>0.9917</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>3.93</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3257,19 +3476,28 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>90</v>
+        <v>92</v>
+      </c>
+      <c r="C29">
+        <v>3.5</v>
+      </c>
+      <c r="D29">
+        <v>117</v>
+      </c>
+      <c r="E29">
+        <v>-144</v>
       </c>
       <c r="F29" t="s">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="G29">
-        <v>824803</v>
+        <v>824319</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3278,46 +3506,46 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M29">
-        <v>0.268</v>
+        <v>0.1597</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="P29">
-        <v>4.19</v>
+        <v>4.39</v>
       </c>
       <c r="Q29">
-        <v>0.2832</v>
+        <v>0.1217</v>
       </c>
       <c r="R29">
-        <v>0.361</v>
+        <v>0.365</v>
       </c>
       <c r="S29" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="T29">
-        <v>0.2607</v>
+        <v>0.2783</v>
       </c>
       <c r="U29">
-        <v>0.246</v>
+        <v>0.2137</v>
       </c>
       <c r="V29">
         <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2568</v>
+        <v>0.2061</v>
       </c>
       <c r="X29">
-        <v>0.2205</v>
+        <v>0.2235</v>
       </c>
       <c r="Y29">
-        <v>1.0725</v>
+        <v>1.0055</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3326,22 +3554,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>7.48</v>
+        <v>3.87</v>
       </c>
       <c r="AE29" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="AF29">
-        <v>0.2735</v>
+        <v>0.1458</v>
       </c>
       <c r="AG29">
-        <v>1.1823</v>
+        <v>1.2451</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>7.48</v>
+        <v>3.87</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3349,67 +3577,34 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>91</v>
+        <v>93</v>
+      </c>
+      <c r="C30">
+        <v>4.5</v>
+      </c>
+      <c r="D30">
+        <v>-154</v>
+      </c>
+      <c r="E30">
+        <v>121</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
-      </c>
-      <c r="G30">
-        <v>822938</v>
+        <v>41</v>
+      </c>
+      <c r="G30" t="s">
+        <v>44</v>
       </c>
       <c r="H30" t="s">
-        <v>42</v>
-      </c>
-      <c r="I30">
-        <v>5.6</v>
-      </c>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L30">
-        <v>0</v>
-      </c>
-      <c r="M30">
-        <v>0.2423</v>
-      </c>
-      <c r="N30">
-        <v>5</v>
-      </c>
-      <c r="O30">
-        <v>107</v>
-      </c>
-      <c r="P30">
-        <v>4.14</v>
-      </c>
-      <c r="Q30">
-        <v>0.1776</v>
-      </c>
-      <c r="R30">
-        <v>0.349</v>
+        <v>6</v>
       </c>
       <c r="S30" t="s">
-        <v>43</v>
-      </c>
-      <c r="T30">
-        <v>0.1843</v>
-      </c>
-      <c r="U30">
-        <v>0.1802</v>
-      </c>
-      <c r="V30">
-        <v>9</v>
-      </c>
-      <c r="W30">
-        <v>0.1897</v>
-      </c>
-      <c r="X30">
-        <v>0.2205</v>
-      </c>
-      <c r="Y30">
-        <v>0.88</v>
+        <v>44</v>
+      </c>
+      <c r="V30" t="s">
+        <v>44</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3417,23 +3612,8 @@
       <c r="AC30" t="s">
         <v>44</v>
       </c>
-      <c r="AD30">
-        <v>3.72</v>
-      </c>
       <c r="AE30" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF30">
-        <v>0.2197</v>
-      </c>
-      <c r="AG30">
-        <v>0.8358</v>
-      </c>
-      <c r="AH30">
-        <v>0</v>
-      </c>
-      <c r="AM30">
-        <v>3.72</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3441,55 +3621,34 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>94</v>
+      </c>
+      <c r="C31">
+        <v>4.5</v>
+      </c>
+      <c r="D31">
+        <v>120</v>
+      </c>
+      <c r="E31">
+        <v>-145</v>
       </c>
       <c r="F31" t="s">
-        <v>59</v>
-      </c>
-      <c r="G31">
-        <v>823423</v>
+        <v>60</v>
+      </c>
+      <c r="G31" t="s">
+        <v>44</v>
       </c>
       <c r="H31" t="s">
-        <v>93</v>
-      </c>
-      <c r="I31">
-        <v>4.5</v>
-      </c>
-      <c r="J31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L31">
-        <v>0</v>
-      </c>
-      <c r="M31">
-        <v>0.1859</v>
-      </c>
-      <c r="P31">
-        <v>4.63</v>
+        <v>6</v>
       </c>
       <c r="S31" t="s">
-        <v>43</v>
-      </c>
-      <c r="T31">
-        <v>0.1753</v>
-      </c>
-      <c r="U31">
-        <v>0.1771</v>
-      </c>
-      <c r="V31">
-        <v>9</v>
-      </c>
-      <c r="W31">
-        <v>0.233</v>
-      </c>
-      <c r="X31">
-        <v>0.2205</v>
-      </c>
-      <c r="Y31">
-        <v>0.9664</v>
+        <v>44</v>
+      </c>
+      <c r="V31" t="s">
+        <v>44</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3497,23 +3656,8 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
-      <c r="AD31">
-        <v>2.98</v>
-      </c>
       <c r="AE31" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF31">
-        <v>0.1859</v>
-      </c>
-      <c r="AG31">
-        <v>0.7952</v>
-      </c>
-      <c r="AH31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>2.98</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3521,67 +3665,34 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="C32">
+        <v>3.5</v>
+      </c>
+      <c r="D32">
+        <v>-109</v>
+      </c>
+      <c r="E32">
+        <v>-104</v>
       </c>
       <c r="F32" t="s">
-        <v>68</v>
-      </c>
-      <c r="G32">
-        <v>823586</v>
+        <v>70</v>
+      </c>
+      <c r="G32" t="s">
+        <v>44</v>
       </c>
       <c r="H32" t="s">
-        <v>42</v>
-      </c>
-      <c r="I32">
-        <v>5.7</v>
-      </c>
-      <c r="J32" t="b">
-        <v>0</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0.1638</v>
-      </c>
-      <c r="N32">
-        <v>5</v>
-      </c>
-      <c r="O32">
-        <v>110</v>
-      </c>
-      <c r="P32">
-        <v>3.9</v>
-      </c>
-      <c r="Q32">
-        <v>0.1273</v>
-      </c>
-      <c r="R32">
-        <v>0.355</v>
+        <v>6</v>
       </c>
       <c r="S32" t="s">
-        <v>56</v>
-      </c>
-      <c r="T32">
-        <v>0.1552</v>
-      </c>
-      <c r="U32">
-        <v>0.1736</v>
-      </c>
-      <c r="V32">
-        <v>9</v>
-      </c>
-      <c r="W32">
-        <v>0.2187</v>
-      </c>
-      <c r="X32">
-        <v>0.2205</v>
-      </c>
-      <c r="Y32">
-        <v>0.9935</v>
+        <v>44</v>
+      </c>
+      <c r="V32" t="s">
+        <v>44</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3589,23 +3700,8 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
-      <c r="AD32">
-        <v>2.33</v>
-      </c>
       <c r="AE32" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF32">
-        <v>0.1509</v>
-      </c>
-      <c r="AG32">
-        <v>0.704</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>2.33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3613,67 +3709,34 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="C33">
+        <v>4.5</v>
+      </c>
+      <c r="D33">
+        <v>142</v>
+      </c>
+      <c r="E33">
+        <v>-156</v>
       </c>
       <c r="F33" t="s">
-        <v>74</v>
-      </c>
-      <c r="G33">
-        <v>824075</v>
+        <v>83</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
       </c>
       <c r="H33" t="s">
-        <v>96</v>
-      </c>
-      <c r="I33">
-        <v>2</v>
-      </c>
-      <c r="J33" t="b">
-        <v>1</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0.197</v>
-      </c>
-      <c r="N33">
-        <v>2</v>
-      </c>
-      <c r="O33">
-        <v>20</v>
-      </c>
-      <c r="P33">
-        <v>4.06</v>
-      </c>
-      <c r="Q33">
-        <v>0.25</v>
-      </c>
-      <c r="R33">
-        <v>0.091</v>
+        <v>6</v>
       </c>
       <c r="S33" t="s">
-        <v>56</v>
-      </c>
-      <c r="T33">
-        <v>0.2396</v>
-      </c>
-      <c r="U33">
-        <v>0.2076</v>
-      </c>
-      <c r="V33">
-        <v>9</v>
-      </c>
-      <c r="W33">
-        <v>0.2478</v>
-      </c>
-      <c r="X33">
-        <v>0.2205</v>
-      </c>
-      <c r="Y33">
-        <v>1.0112</v>
+        <v>44</v>
+      </c>
+      <c r="V33" t="s">
+        <v>44</v>
       </c>
       <c r="AA33" t="s">
         <v>44</v>
@@ -3681,23 +3744,8 @@
       <c r="AC33" t="s">
         <v>44</v>
       </c>
-      <c r="AD33">
-        <v>1.8</v>
-      </c>
       <c r="AE33" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF33">
-        <v>0.2019</v>
-      </c>
-      <c r="AG33">
-        <v>1.087</v>
-      </c>
-      <c r="AH33">
-        <v>0</v>
-      </c>
-      <c r="AM33">
-        <v>1.8</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.25">
@@ -3707,65 +3755,32 @@
       <c r="B34" t="s">
         <v>97</v>
       </c>
+      <c r="C34">
+        <v>4.5</v>
+      </c>
+      <c r="D34">
+        <v>122</v>
+      </c>
+      <c r="E34">
+        <v>-153</v>
+      </c>
       <c r="F34" t="s">
-        <v>79</v>
-      </c>
-      <c r="G34">
-        <v>824639</v>
+        <v>88</v>
+      </c>
+      <c r="G34" t="s">
+        <v>44</v>
       </c>
       <c r="H34" t="s">
-        <v>96</v>
-      </c>
-      <c r="I34">
-        <v>1.2</v>
-      </c>
-      <c r="J34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L34">
-        <v>0</v>
-      </c>
-      <c r="M34">
-        <v>0.2283</v>
-      </c>
-      <c r="N34">
-        <v>5</v>
-      </c>
-      <c r="O34">
-        <v>20</v>
-      </c>
-      <c r="P34">
-        <v>4.24</v>
-      </c>
-      <c r="Q34">
-        <v>0.2</v>
-      </c>
-      <c r="R34">
-        <v>0.091</v>
+        <v>6</v>
       </c>
       <c r="S34" t="s">
-        <v>56</v>
-      </c>
-      <c r="T34">
-        <v>0.2231</v>
-      </c>
-      <c r="U34">
-        <v>0.2215</v>
-      </c>
-      <c r="V34">
-        <v>9</v>
-      </c>
-      <c r="W34">
-        <v>0.2191</v>
-      </c>
-      <c r="X34">
-        <v>0.2205</v>
-      </c>
-      <c r="Y34">
-        <v>0.9381</v>
+        <v>44</v>
+      </c>
+      <c r="V34" t="s">
+        <v>44</v>
       </c>
       <c r="AA34" t="s">
         <v>44</v>
@@ -3773,23 +3788,8 @@
       <c r="AC34" t="s">
         <v>44</v>
       </c>
-      <c r="AD34">
-        <v>1.06</v>
-      </c>
       <c r="AE34" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF34">
-        <v>0.2257</v>
-      </c>
-      <c r="AG34">
-        <v>1.0119</v>
-      </c>
-      <c r="AH34">
-        <v>0</v>
-      </c>
-      <c r="AM34">
-        <v>1.06</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-18.xlsx
+++ b/data/k-props/2026-08-18.xlsx
@@ -872,7 +872,7 @@
         <v>0.2568</v>
       </c>
       <c r="X2">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y2">
         <v>1.0725</v>
@@ -884,7 +884,7 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>7.37</v>
+        <v>7.38</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
@@ -893,13 +893,13 @@
         <v>0.2735</v>
       </c>
       <c r="AG2">
-        <v>1.1662</v>
+        <v>1.1668</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>7.37</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -973,7 +973,7 @@
         <v>0.2449</v>
       </c>
       <c r="X3">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y3">
         <v>1.0455</v>
@@ -994,7 +994,7 @@
         <v>0.2019</v>
       </c>
       <c r="AG3">
-        <v>1.1647</v>
+        <v>1.1653</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -1074,7 +1074,7 @@
         <v>0.2358</v>
       </c>
       <c r="X4">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y4">
         <v>1.0215</v>
@@ -1095,7 +1095,7 @@
         <v>0.1563</v>
       </c>
       <c r="AG4">
-        <v>0.9436</v>
+        <v>0.944</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0.2235</v>
       </c>
       <c r="X5">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y5">
         <v>0.8825</v>
@@ -1196,7 +1196,7 @@
         <v>0.2588</v>
       </c>
       <c r="AG5">
-        <v>0.8895</v>
+        <v>0.8899</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>0.2259</v>
       </c>
       <c r="X6">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y6">
         <v>0.9198</v>
@@ -1297,7 +1297,7 @@
         <v>0.1754</v>
       </c>
       <c r="AG6">
-        <v>0.885</v>
+        <v>0.8854</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>0.2271</v>
       </c>
       <c r="X7">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y7">
         <v>1.0041</v>
@@ -1398,7 +1398,7 @@
         <v>0.1877</v>
       </c>
       <c r="AG7">
-        <v>1.0252</v>
+        <v>1.0257</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>0.2552</v>
       </c>
       <c r="X8">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y8">
         <v>1.0796</v>
@@ -1499,7 +1499,7 @@
         <v>0.2328</v>
       </c>
       <c r="AG8">
-        <v>1.2461</v>
+        <v>1.2466</v>
       </c>
       <c r="AH8">
         <v>0</v>
@@ -1579,7 +1579,7 @@
         <v>0.1828</v>
       </c>
       <c r="X9">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y9">
         <v>0.9052</v>
@@ -1600,7 +1600,7 @@
         <v>0.166</v>
       </c>
       <c r="AG9">
-        <v>0.9812</v>
+        <v>0.9817</v>
       </c>
       <c r="AH9">
         <v>0</v>
@@ -1671,7 +1671,7 @@
         <v>0.1897</v>
       </c>
       <c r="X10">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y10">
         <v>0.88</v>
@@ -1683,7 +1683,7 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="AE10" t="s">
         <v>51</v>
@@ -1692,13 +1692,13 @@
         <v>0.2197</v>
       </c>
       <c r="AG10">
-        <v>0.8244</v>
+        <v>0.8248</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1772,7 +1772,7 @@
         <v>0.19</v>
       </c>
       <c r="X11">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y11">
         <v>0.9953</v>
@@ -1793,7 +1793,7 @@
         <v>0.1366</v>
       </c>
       <c r="AG11">
-        <v>0.8793</v>
+        <v>0.8797</v>
       </c>
       <c r="AH11">
         <v>0</v>
@@ -1852,7 +1852,7 @@
         <v>0.233</v>
       </c>
       <c r="X12">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y12">
         <v>0.9664</v>
@@ -1873,7 +1873,7 @@
         <v>0.1859</v>
       </c>
       <c r="AG12">
-        <v>0.7844</v>
+        <v>0.7848</v>
       </c>
       <c r="AH12">
         <v>0</v>
@@ -1953,7 +1953,7 @@
         <v>0.2114</v>
       </c>
       <c r="X13">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y13">
         <v>0.8983</v>
@@ -1965,7 +1965,7 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
       <c r="AE13" t="s">
         <v>47</v>
@@ -1974,13 +1974,13 @@
         <v>0.2988</v>
       </c>
       <c r="AG13">
-        <v>1.0707</v>
+        <v>1.0712</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>6.52</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -2054,7 +2054,7 @@
         <v>0.2168</v>
       </c>
       <c r="X14">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y14">
         <v>0.9954</v>
@@ -2075,7 +2075,7 @@
         <v>0.1621</v>
       </c>
       <c r="AG14">
-        <v>0.8325</v>
+        <v>0.8329</v>
       </c>
       <c r="AH14">
         <v>0</v>
@@ -2155,7 +2155,7 @@
         <v>0.1751</v>
       </c>
       <c r="X15">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y15">
         <v>0.88</v>
@@ -2176,7 +2176,7 @@
         <v>0.2375</v>
       </c>
       <c r="AG15">
-        <v>1.1689</v>
+        <v>1.1694</v>
       </c>
       <c r="AH15">
         <v>0</v>
@@ -2256,7 +2256,7 @@
         <v>0.2325</v>
       </c>
       <c r="X16">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y16">
         <v>0.9557</v>
@@ -2277,7 +2277,7 @@
         <v>0.2051</v>
       </c>
       <c r="AG16">
-        <v>1.1008</v>
+        <v>1.1013</v>
       </c>
       <c r="AH16">
         <v>0</v>
@@ -2348,7 +2348,7 @@
         <v>0.2187</v>
       </c>
       <c r="X17">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y17">
         <v>1.0025</v>
@@ -2369,7 +2369,7 @@
         <v>0.1509</v>
       </c>
       <c r="AG17">
-        <v>0.8189</v>
+        <v>0.8193</v>
       </c>
       <c r="AH17">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>0.2096</v>
       </c>
       <c r="X18">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y18">
         <v>0.9401</v>
@@ -2470,7 +2470,7 @@
         <v>0.2308</v>
       </c>
       <c r="AG18">
-        <v>0.9077</v>
+        <v>0.9081</v>
       </c>
       <c r="AH18">
         <v>0</v>
@@ -2541,7 +2541,7 @@
         <v>0.2478</v>
       </c>
       <c r="X19">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y19">
         <v>1.0112</v>
@@ -2562,7 +2562,7 @@
         <v>0.2019</v>
       </c>
       <c r="AG19">
-        <v>1.0722</v>
+        <v>1.0727</v>
       </c>
       <c r="AH19">
         <v>0</v>
@@ -2642,7 +2642,7 @@
         <v>0.2114</v>
       </c>
       <c r="X20">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y20">
         <v>0.9597</v>
@@ -2663,7 +2663,7 @@
         <v>0.2536</v>
       </c>
       <c r="AG20">
-        <v>0.8898</v>
+        <v>0.8902</v>
       </c>
       <c r="AH20">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>0.2179</v>
       </c>
       <c r="X21">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y21">
         <v>0.9903</v>
@@ -2764,7 +2764,7 @@
         <v>0.2013</v>
       </c>
       <c r="AG21">
-        <v>1.1027</v>
+        <v>1.1032</v>
       </c>
       <c r="AH21">
         <v>0</v>
@@ -2829,25 +2829,25 @@
         <v>0.367</v>
       </c>
       <c r="S22" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2357</v>
+        <v>0.2326</v>
       </c>
       <c r="U22">
-        <v>0.234</v>
+        <v>0.2315</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W22">
         <v>0.2155</v>
       </c>
       <c r="X22">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y22">
-        <v>1.0057</v>
+        <v>1.0453</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2856,7 +2856,7 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.21</v>
+        <v>5.35</v>
       </c>
       <c r="AE22" t="s">
         <v>51</v>
@@ -2865,13 +2865,13 @@
         <v>0.2207</v>
       </c>
       <c r="AG22">
-        <v>1.0545</v>
+        <v>1.0411</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.21</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2945,7 +2945,7 @@
         <v>0.2395</v>
       </c>
       <c r="X23">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y23">
         <v>1.0058</v>
@@ -2966,7 +2966,7 @@
         <v>0.2938</v>
       </c>
       <c r="AG23">
-        <v>0.9161</v>
+        <v>0.9165</v>
       </c>
       <c r="AH23">
         <v>0</v>
@@ -3046,7 +3046,7 @@
         <v>0.2076</v>
       </c>
       <c r="X24">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y24">
         <v>0.989</v>
@@ -3067,7 +3067,7 @@
         <v>0.1733</v>
       </c>
       <c r="AG24">
-        <v>1.016</v>
+        <v>1.0164</v>
       </c>
       <c r="AH24">
         <v>0</v>
@@ -3138,7 +3138,7 @@
         <v>0.2191</v>
       </c>
       <c r="X25">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y25">
         <v>0.9381</v>
@@ -3159,7 +3159,7 @@
         <v>0.2257</v>
       </c>
       <c r="AG25">
-        <v>0.9981</v>
+        <v>0.9986</v>
       </c>
       <c r="AH25">
         <v>0</v>
@@ -3239,7 +3239,7 @@
         <v>0.2368</v>
       </c>
       <c r="X26">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y26">
         <v>1.0865</v>
@@ -3260,7 +3260,7 @@
         <v>0.2168</v>
       </c>
       <c r="AG26">
-        <v>1.1002</v>
+        <v>1.1007</v>
       </c>
       <c r="AH26">
         <v>0</v>
@@ -3340,7 +3340,7 @@
         <v>0.2504</v>
       </c>
       <c r="X27">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y27">
         <v>0.9877</v>
@@ -3361,7 +3361,7 @@
         <v>0.1531</v>
       </c>
       <c r="AG27">
-        <v>0.9555</v>
+        <v>0.9559</v>
       </c>
       <c r="AH27">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0.247</v>
       </c>
       <c r="X28">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y28">
         <v>1.0013</v>
@@ -3462,7 +3462,7 @@
         <v>0.1555</v>
       </c>
       <c r="AG28">
-        <v>0.9917</v>
+        <v>0.9921</v>
       </c>
       <c r="AH28">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0.2061</v>
       </c>
       <c r="X29">
-        <v>0.2235</v>
+        <v>0.2234</v>
       </c>
       <c r="Y29">
         <v>1.0055</v>
@@ -3554,7 +3554,7 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="AE29" t="s">
         <v>51</v>
@@ -3563,13 +3563,13 @@
         <v>0.1458</v>
       </c>
       <c r="AG29">
-        <v>1.2451</v>
+        <v>1.2457</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">

--- a/data/k-props/2026-08-18.xlsx
+++ b/data/k-props/2026-08-18.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="98">
   <si>
     <t>date</t>
   </si>
@@ -133,178 +133,178 @@
     <t>08/18/2026</t>
   </si>
   <si>
+    <t>Shane Baz</t>
+  </si>
+  <si>
+    <t>New York Yankees @ Baltimore Orioles</t>
+  </si>
+  <si>
+    <t>Traditional starter</t>
+  </si>
+  <si>
+    <t>lineup_unweighted_30d_posted</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>6-7</t>
+  </si>
+  <si>
+    <t>Carlos Rodon</t>
+  </si>
+  <si>
+    <t>Andrew Abbott</t>
+  </si>
+  <si>
+    <t>St. Louis Cardinals @ Cincinnati Reds</t>
+  </si>
+  <si>
+    <t>&lt;6</t>
+  </si>
+  <si>
+    <t>Kyle Leahy</t>
+  </si>
+  <si>
+    <t>Carson Whisenhunt</t>
+  </si>
+  <si>
+    <t>San Francisco Giants @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>Foster Griffin</t>
+  </si>
+  <si>
+    <t>Keider Montero</t>
+  </si>
+  <si>
+    <t>Detroit Tigers @ Pittsburgh Pirates</t>
+  </si>
+  <si>
+    <t>Braxton Ashcraft</t>
+  </si>
+  <si>
+    <t>Zack Wheeler</t>
+  </si>
+  <si>
+    <t>Miami Marlins @ Philadelphia Phillies</t>
+  </si>
+  <si>
+    <t>Jose Soriano</t>
+  </si>
+  <si>
+    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
+  </si>
+  <si>
+    <t>Nick Martinez</t>
+  </si>
+  <si>
+    <t>Merrill Kelly</t>
+  </si>
+  <si>
+    <t>Arizona Diamondbacks @ Boston Red Sox</t>
+  </si>
+  <si>
+    <t>Ranger Suarez</t>
+  </si>
+  <si>
+    <t>Robbie Ray</t>
+  </si>
+  <si>
+    <t>San Diego Padres @ New York Mets</t>
+  </si>
+  <si>
+    <t>Zach Thornton</t>
+  </si>
+  <si>
+    <t>Tyler Mahle</t>
+  </si>
+  <si>
+    <t>Atlanta Braves @ Minnesota Twins</t>
+  </si>
+  <si>
+    <t>Zebby Matthews</t>
+  </si>
+  <si>
+    <t>Jack Perkins</t>
+  </si>
+  <si>
+    <t>Athletics @ Kansas City Royals</t>
+  </si>
+  <si>
+    <t>Kyle Harrison</t>
+  </si>
+  <si>
+    <t>Seattle Mariners @ Milwaukee Brewers</t>
+  </si>
+  <si>
+    <t>Bryce Miller</t>
+  </si>
+  <si>
+    <t>Kevin Gausman</t>
+  </si>
+  <si>
+    <t>Chicago White Sox @ Chicago Cubs</t>
+  </si>
+  <si>
+    <t>Cal Quantrill</t>
+  </si>
+  <si>
+    <t>Washington Nationals @ Texas Rangers</t>
+  </si>
+  <si>
+    <t>Jackson Kent</t>
+  </si>
+  <si>
+    <t>George Klassen</t>
+  </si>
+  <si>
+    <t>Los Angeles Angels @ Houston Astros</t>
+  </si>
+  <si>
+    <t>Cristian Javier</t>
+  </si>
+  <si>
+    <t>Limited starter</t>
+  </si>
+  <si>
+    <t>Ryan Feltner</t>
+  </si>
+  <si>
+    <t>Los Angeles Dodgers @ Colorado Rockies</t>
+  </si>
+  <si>
+    <t>Eric Lauer</t>
+  </si>
+  <si>
     <t>Carlos Rodón</t>
   </si>
   <si>
-    <t>New York Yankees @ Baltimore Orioles</t>
-  </si>
-  <si>
-    <t>Traditional starter</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_posted</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
     <t>&gt;=7</t>
   </si>
   <si>
-    <t>Shane Baz</t>
-  </si>
-  <si>
-    <t>6-7</t>
-  </si>
-  <si>
-    <t>Keider Montero</t>
-  </si>
-  <si>
-    <t>Detroit Tigers @ Pittsburgh Pirates</t>
-  </si>
-  <si>
-    <t>lineup_unweighted_30d_projected_regulars</t>
-  </si>
-  <si>
-    <t>&lt;6</t>
-  </si>
-  <si>
-    <t>Braxton Ashcraft</t>
-  </si>
-  <si>
-    <t>Carson Whisenhunt</t>
-  </si>
-  <si>
-    <t>San Francisco Giants @ Cleveland Guardians</t>
-  </si>
-  <si>
-    <t>Foster Griffin</t>
-  </si>
-  <si>
-    <t>Kyle Leahy</t>
-  </si>
-  <si>
-    <t>St. Louis Cardinals @ Cincinnati Reds</t>
-  </si>
-  <si>
-    <t>Andrew Abbott</t>
-  </si>
-  <si>
     <t>José Soriano</t>
   </si>
   <si>
-    <t>Toronto Blue Jays @ Tampa Bay Rays</t>
-  </si>
-  <si>
-    <t>Nick Martinez</t>
-  </si>
-  <si>
     <t>Cade Gibson</t>
   </si>
   <si>
-    <t>Miami Marlins @ Philadelphia Phillies</t>
-  </si>
-  <si>
     <t>Role unknown</t>
   </si>
   <si>
-    <t>Zack Wheeler</t>
-  </si>
-  <si>
-    <t>Merrill Kelly</t>
-  </si>
-  <si>
-    <t>Arizona Diamondbacks @ Boston Red Sox</t>
-  </si>
-  <si>
-    <t>Ranger Suarez</t>
-  </si>
-  <si>
-    <t>Robbie Ray</t>
-  </si>
-  <si>
-    <t>San Diego Padres @ New York Mets</t>
-  </si>
-  <si>
     <t>Zac Thornton</t>
   </si>
   <si>
-    <t>Jack Perkins</t>
-  </si>
-  <si>
-    <t>Athletics @ Kansas City Royals</t>
+    <t>Brady Basso</t>
+  </si>
+  <si>
+    <t>Opener / bullpen game</t>
   </si>
   <si>
     <t>Daniel Lynch IV</t>
   </si>
   <si>
-    <t>Opener / bullpen game</t>
-  </si>
-  <si>
-    <t>Tyler Mahle</t>
-  </si>
-  <si>
-    <t>Atlanta Braves @ Minnesota Twins</t>
-  </si>
-  <si>
-    <t>Zebby Matthews</t>
-  </si>
-  <si>
-    <t>Bryce Miller</t>
-  </si>
-  <si>
-    <t>Seattle Mariners @ Milwaukee Brewers</t>
-  </si>
-  <si>
-    <t>Kyle Harrison</t>
-  </si>
-  <si>
-    <t>Cal Quantrill</t>
-  </si>
-  <si>
-    <t>Washington Nationals @ Texas Rangers</t>
-  </si>
-  <si>
     <t>Bryan Hudson</t>
-  </si>
-  <si>
-    <t>Chicago White Sox @ Chicago Cubs</t>
-  </si>
-  <si>
-    <t>Kevin Gausman</t>
-  </si>
-  <si>
-    <t>Cristian Javier</t>
-  </si>
-  <si>
-    <t>Los Angeles Angels @ Houston Astros</t>
-  </si>
-  <si>
-    <t>Limited starter</t>
-  </si>
-  <si>
-    <t>Eric Lauer</t>
-  </si>
-  <si>
-    <t>Los Angeles Dodgers @ Colorado Rockies</t>
-  </si>
-  <si>
-    <t>Ryan Feltner</t>
-  </si>
-  <si>
-    <t>Carlos Rodon</t>
-  </si>
-  <si>
-    <t>Jose Soriano</t>
-  </si>
-  <si>
-    <t>Zach Thornton</t>
-  </si>
-  <si>
-    <t>Jackson Kent</t>
-  </si>
-  <si>
-    <t>George Klassen</t>
   </si>
 </sst>
 </file>
@@ -685,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM34"/>
+  <dimension ref="A1:AM35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="39" width="16" customWidth="1"/>
@@ -817,6 +817,15 @@
       <c r="B2" t="s">
         <v>40</v>
       </c>
+      <c r="C2">
+        <v>5.5</v>
+      </c>
+      <c r="D2">
+        <v>-142</v>
+      </c>
+      <c r="E2">
+        <v>120</v>
+      </c>
       <c r="F2" t="s">
         <v>41</v>
       </c>
@@ -827,7 +836,7 @@
         <v>42</v>
       </c>
       <c r="I2">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="b">
         <v>0</v>
@@ -836,46 +845,46 @@
         <v>0</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2">
-        <v>0.268</v>
+        <v>0.204</v>
       </c>
       <c r="N2">
         <v>5</v>
       </c>
       <c r="O2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="P2">
-        <v>4.19</v>
+        <v>4.29</v>
       </c>
       <c r="Q2">
-        <v>0.2832</v>
+        <v>0.1983</v>
       </c>
       <c r="R2">
-        <v>0.361</v>
+        <v>0.367</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>0.2607</v>
+        <v>0.2603</v>
       </c>
       <c r="U2">
-        <v>0.246</v>
+        <v>0.265</v>
       </c>
       <c r="V2">
         <v>9</v>
       </c>
       <c r="W2">
-        <v>0.2568</v>
+        <v>0.2449</v>
       </c>
       <c r="X2">
         <v>0.2234</v>
       </c>
       <c r="Y2">
-        <v>1.0725</v>
+        <v>1.0455</v>
       </c>
       <c r="AA2" t="s">
         <v>44</v>
@@ -884,22 +893,22 @@
         <v>44</v>
       </c>
       <c r="AD2">
-        <v>7.38</v>
+        <v>6.13</v>
       </c>
       <c r="AE2" t="s">
         <v>45</v>
       </c>
       <c r="AF2">
-        <v>0.2735</v>
+        <v>0.2019</v>
       </c>
       <c r="AG2">
-        <v>1.1668</v>
+        <v>1.1655</v>
       </c>
       <c r="AH2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>7.38</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="3" spans="1:39" x14ac:dyDescent="0.25">
@@ -910,73 +919,31 @@
         <v>46</v>
       </c>
       <c r="C3">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="D3">
-        <v>-146</v>
+        <v>-154</v>
       </c>
       <c r="E3">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F3" t="s">
         <v>41</v>
       </c>
-      <c r="G3">
-        <v>824803</v>
+      <c r="G3" t="s">
+        <v>44</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3">
-        <v>5.8</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L3">
         <v>6</v>
       </c>
-      <c r="M3">
-        <v>0.204</v>
-      </c>
-      <c r="N3">
-        <v>5</v>
-      </c>
-      <c r="O3">
-        <v>116</v>
-      </c>
-      <c r="P3">
-        <v>4.29</v>
-      </c>
-      <c r="Q3">
-        <v>0.1983</v>
-      </c>
-      <c r="R3">
-        <v>0.367</v>
-      </c>
       <c r="S3" t="s">
-        <v>43</v>
-      </c>
-      <c r="T3">
-        <v>0.2603</v>
-      </c>
-      <c r="U3">
-        <v>0.265</v>
-      </c>
-      <c r="V3">
-        <v>9</v>
-      </c>
-      <c r="W3">
-        <v>0.2449</v>
-      </c>
-      <c r="X3">
-        <v>0.2234</v>
-      </c>
-      <c r="Y3">
-        <v>1.0455</v>
+        <v>44</v>
+      </c>
+      <c r="V3" t="s">
+        <v>44</v>
       </c>
       <c r="AA3" t="s">
         <v>44</v>
@@ -984,23 +951,8 @@
       <c r="AC3" t="s">
         <v>44</v>
       </c>
-      <c r="AD3">
-        <v>6.13</v>
-      </c>
       <c r="AE3" t="s">
-        <v>47</v>
-      </c>
-      <c r="AF3">
-        <v>0.2019</v>
-      </c>
-      <c r="AG3">
-        <v>1.1653</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>6.13</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -1008,28 +960,28 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C4">
+        <v>4.5</v>
+      </c>
+      <c r="D4">
+        <v>105</v>
+      </c>
+      <c r="E4">
+        <v>-126</v>
+      </c>
+      <c r="F4" t="s">
         <v>48</v>
       </c>
-      <c r="C4">
-        <v>3.5</v>
-      </c>
-      <c r="D4">
-        <v>-122</v>
-      </c>
-      <c r="E4">
-        <v>105</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
-      </c>
       <c r="G4">
-        <v>823341</v>
+        <v>824475</v>
       </c>
       <c r="H4" t="s">
         <v>42</v>
       </c>
       <c r="I4">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J4" t="b">
         <v>0</v>
@@ -1041,43 +993,43 @@
         <v>5</v>
       </c>
       <c r="M4">
-        <v>0.167</v>
+        <v>0.1765</v>
       </c>
       <c r="N4">
         <v>5</v>
       </c>
       <c r="O4">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="P4">
-        <v>4</v>
+        <v>4.35</v>
       </c>
       <c r="Q4">
-        <v>0.1379</v>
+        <v>0.1488</v>
       </c>
       <c r="R4">
-        <v>0.367</v>
+        <v>0.377</v>
       </c>
       <c r="S4" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T4">
-        <v>0.2109</v>
+        <v>0.2193</v>
       </c>
       <c r="U4">
-        <v>0.2349</v>
+        <v>0.199</v>
       </c>
       <c r="V4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W4">
-        <v>0.2358</v>
+        <v>0.1828</v>
       </c>
       <c r="X4">
         <v>0.2234</v>
       </c>
       <c r="Y4">
-        <v>1.0215</v>
+        <v>0.9052</v>
       </c>
       <c r="AA4" t="s">
         <v>44</v>
@@ -1086,22 +1038,22 @@
         <v>44</v>
       </c>
       <c r="AD4">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
       <c r="AE4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF4">
-        <v>0.1563</v>
+        <v>0.166</v>
       </c>
       <c r="AG4">
-        <v>0.944</v>
+        <v>0.9819</v>
       </c>
       <c r="AH4">
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>3.45</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="5" spans="1:39" x14ac:dyDescent="0.25">
@@ -1109,28 +1061,28 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5">
         <v>5.5</v>
       </c>
       <c r="D5">
+        <v>105</v>
+      </c>
+      <c r="E5">
         <v>-120</v>
       </c>
-      <c r="E5">
-        <v>105</v>
-      </c>
       <c r="F5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G5">
-        <v>823341</v>
+        <v>824475</v>
       </c>
       <c r="H5" t="s">
         <v>42</v>
       </c>
       <c r="I5">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="J5" t="b">
         <v>0</v>
@@ -1142,43 +1094,43 @@
         <v>5</v>
       </c>
       <c r="M5">
-        <v>0.27</v>
+        <v>0.2108</v>
       </c>
       <c r="N5">
         <v>5</v>
       </c>
       <c r="O5">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="P5">
-        <v>4.06</v>
+        <v>4.24</v>
       </c>
       <c r="Q5">
-        <v>0.2389</v>
+        <v>0.2727</v>
       </c>
       <c r="R5">
-        <v>0.361</v>
+        <v>0.355</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>0.1988</v>
+        <v>0.2785</v>
       </c>
       <c r="U5">
-        <v>0.178</v>
+        <v>0.2747</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>0.2235</v>
+        <v>0.2552</v>
       </c>
       <c r="X5">
         <v>0.2234</v>
       </c>
       <c r="Y5">
-        <v>0.8825</v>
+        <v>1.0796</v>
       </c>
       <c r="AA5" t="s">
         <v>44</v>
@@ -1187,22 +1139,22 @@
         <v>44</v>
       </c>
       <c r="AD5">
-        <v>4.86</v>
+        <v>6.79</v>
       </c>
       <c r="AE5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF5">
-        <v>0.2588</v>
+        <v>0.2328</v>
       </c>
       <c r="AG5">
-        <v>0.8899</v>
+        <v>1.247</v>
       </c>
       <c r="AH5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>4.86</v>
+        <v>6.79</v>
       </c>
     </row>
     <row r="6" spans="1:39" x14ac:dyDescent="0.25">
@@ -1210,7 +1162,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1219,10 +1171,10 @@
         <v>-115</v>
       </c>
       <c r="E6">
-        <v>-103</v>
+        <v>-107</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G6">
         <v>824398</v>
@@ -1288,22 +1240,22 @@
         <v>44</v>
       </c>
       <c r="AD6">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="AE6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF6">
         <v>0.1754</v>
       </c>
       <c r="AG6">
-        <v>0.8854</v>
+        <v>0.8856</v>
       </c>
       <c r="AH6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="7" spans="1:39" x14ac:dyDescent="0.25">
@@ -1311,19 +1263,19 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C7">
         <v>5.5</v>
       </c>
       <c r="D7">
-        <v>-107</v>
+        <v>-112</v>
       </c>
       <c r="E7">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G7">
         <v>824398</v>
@@ -1392,13 +1344,13 @@
         <v>4.56</v>
       </c>
       <c r="AE7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF7">
         <v>0.1877</v>
       </c>
       <c r="AG7">
-        <v>1.0257</v>
+        <v>1.0259</v>
       </c>
       <c r="AH7">
         <v>0</v>
@@ -1412,28 +1364,28 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C8">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D8">
-        <v>115</v>
+        <v>-135</v>
       </c>
       <c r="E8">
-        <v>-136</v>
+        <v>122</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8">
-        <v>824475</v>
+        <v>823341</v>
       </c>
       <c r="H8" t="s">
         <v>42</v>
       </c>
       <c r="I8">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
@@ -1445,43 +1397,43 @@
         <v>5</v>
       </c>
       <c r="M8">
-        <v>0.2108</v>
+        <v>0.167</v>
       </c>
       <c r="N8">
         <v>5</v>
       </c>
       <c r="O8">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="P8">
-        <v>4.24</v>
+        <v>4</v>
       </c>
       <c r="Q8">
-        <v>0.2727</v>
+        <v>0.1379</v>
       </c>
       <c r="R8">
-        <v>0.355</v>
+        <v>0.367</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.2785</v>
+        <v>0.2583</v>
       </c>
       <c r="U8">
-        <v>0.2747</v>
+        <v>0.2746</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>0.2552</v>
+        <v>0.2358</v>
       </c>
       <c r="X8">
         <v>0.2234</v>
       </c>
       <c r="Y8">
-        <v>1.0796</v>
+        <v>1.0856</v>
       </c>
       <c r="AA8" t="s">
         <v>44</v>
@@ -1490,22 +1442,22 @@
         <v>44</v>
       </c>
       <c r="AD8">
-        <v>6.78</v>
+        <v>4.49</v>
       </c>
       <c r="AE8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF8">
-        <v>0.2328</v>
+        <v>0.1563</v>
       </c>
       <c r="AG8">
-        <v>1.2466</v>
+        <v>1.1563</v>
       </c>
       <c r="AH8">
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>6.78</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="9" spans="1:39" x14ac:dyDescent="0.25">
@@ -1513,28 +1465,28 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D9">
-        <v>-107</v>
+        <v>-120</v>
       </c>
       <c r="E9">
-        <v>-113</v>
+        <v>104</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9">
-        <v>824475</v>
+        <v>823341</v>
       </c>
       <c r="H9" t="s">
         <v>42</v>
       </c>
       <c r="I9">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
@@ -1546,43 +1498,43 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>0.1765</v>
+        <v>0.27</v>
       </c>
       <c r="N9">
         <v>5</v>
       </c>
       <c r="O9">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="P9">
-        <v>4.35</v>
+        <v>4.06</v>
       </c>
       <c r="Q9">
-        <v>0.1488</v>
+        <v>0.2389</v>
       </c>
       <c r="R9">
-        <v>0.377</v>
+        <v>0.361</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>0.2193</v>
+        <v>0.1988</v>
       </c>
       <c r="U9">
-        <v>0.199</v>
+        <v>0.178</v>
       </c>
       <c r="V9">
         <v>9</v>
       </c>
       <c r="W9">
-        <v>0.1828</v>
+        <v>0.2235</v>
       </c>
       <c r="X9">
         <v>0.2234</v>
       </c>
       <c r="Y9">
-        <v>0.9052</v>
+        <v>0.8825</v>
       </c>
       <c r="AA9" t="s">
         <v>44</v>
@@ -1591,22 +1543,22 @@
         <v>44</v>
       </c>
       <c r="AD9">
-        <v>3.41</v>
+        <v>4.86</v>
       </c>
       <c r="AE9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF9">
-        <v>0.166</v>
+        <v>0.2588</v>
       </c>
       <c r="AG9">
-        <v>0.9817</v>
+        <v>0.8901</v>
       </c>
       <c r="AH9">
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>3.41</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="10" spans="1:39" x14ac:dyDescent="0.25">
@@ -1614,19 +1566,28 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="C10">
+        <v>7.5</v>
+      </c>
+      <c r="D10">
+        <v>120</v>
+      </c>
+      <c r="E10">
+        <v>-136</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10">
-        <v>822938</v>
+        <v>823423</v>
       </c>
       <c r="H10" t="s">
         <v>42</v>
       </c>
       <c r="I10">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
@@ -1635,46 +1596,46 @@
         <v>0</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M10">
-        <v>0.2423</v>
+        <v>0.3018</v>
       </c>
       <c r="N10">
         <v>5</v>
       </c>
       <c r="O10">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="P10">
-        <v>4.14</v>
+        <v>3.94</v>
       </c>
       <c r="Q10">
-        <v>0.1776</v>
+        <v>0.2929</v>
       </c>
       <c r="R10">
-        <v>0.349</v>
+        <v>0.331</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>0.1843</v>
+        <v>0.2393</v>
       </c>
       <c r="U10">
-        <v>0.1802</v>
+        <v>0.2184</v>
       </c>
       <c r="V10">
         <v>9</v>
       </c>
       <c r="W10">
-        <v>0.1897</v>
+        <v>0.2114</v>
       </c>
       <c r="X10">
         <v>0.2234</v>
       </c>
       <c r="Y10">
-        <v>0.88</v>
+        <v>0.8983</v>
       </c>
       <c r="AA10" t="s">
         <v>44</v>
@@ -1683,22 +1644,22 @@
         <v>44</v>
       </c>
       <c r="AD10">
-        <v>3.68</v>
+        <v>6.53</v>
       </c>
       <c r="AE10" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF10">
-        <v>0.2197</v>
+        <v>0.2988</v>
       </c>
       <c r="AG10">
-        <v>0.8248</v>
+        <v>1.0714</v>
       </c>
       <c r="AH10">
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>3.68</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="11" spans="1:39" x14ac:dyDescent="0.25">
@@ -1706,76 +1667,34 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C11">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D11">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="E11">
-        <v>-125</v>
+        <v>-142</v>
       </c>
       <c r="F11" t="s">
         <v>60</v>
       </c>
-      <c r="G11">
-        <v>822938</v>
+      <c r="G11" t="s">
+        <v>44</v>
       </c>
       <c r="H11" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11">
-        <v>6</v>
-      </c>
-      <c r="J11" t="b">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L11">
         <v>6</v>
       </c>
-      <c r="M11">
-        <v>0.1413</v>
-      </c>
-      <c r="N11">
-        <v>5</v>
-      </c>
-      <c r="O11">
-        <v>124</v>
-      </c>
-      <c r="P11">
-        <v>4</v>
-      </c>
-      <c r="Q11">
-        <v>0.129</v>
-      </c>
-      <c r="R11">
-        <v>0.383</v>
-      </c>
       <c r="S11" t="s">
-        <v>43</v>
-      </c>
-      <c r="T11">
-        <v>0.1965</v>
-      </c>
-      <c r="U11">
-        <v>0.1807</v>
-      </c>
-      <c r="V11">
-        <v>9</v>
-      </c>
-      <c r="W11">
-        <v>0.19</v>
-      </c>
-      <c r="X11">
-        <v>0.2234</v>
-      </c>
-      <c r="Y11">
-        <v>0.9953</v>
+        <v>44</v>
+      </c>
+      <c r="V11" t="s">
+        <v>44</v>
       </c>
       <c r="AA11" t="s">
         <v>44</v>
@@ -1783,23 +1702,8 @@
       <c r="AC11" t="s">
         <v>44</v>
       </c>
-      <c r="AD11">
-        <v>2.87</v>
-      </c>
       <c r="AE11" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF11">
-        <v>0.1366</v>
-      </c>
-      <c r="AG11">
-        <v>0.8797</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>2.87</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1807,55 +1711,76 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>62</v>
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>3.5</v>
+      </c>
+      <c r="D12">
+        <v>117</v>
+      </c>
+      <c r="E12">
+        <v>-136</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G12">
-        <v>823423</v>
+        <v>822938</v>
       </c>
       <c r="H12" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="b">
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M12">
-        <v>0.1859</v>
+        <v>0.1413</v>
+      </c>
+      <c r="N12">
+        <v>5</v>
+      </c>
+      <c r="O12">
+        <v>124</v>
       </c>
       <c r="P12">
-        <v>4.63</v>
+        <v>4</v>
+      </c>
+      <c r="Q12">
+        <v>0.129</v>
+      </c>
+      <c r="R12">
+        <v>0.383</v>
       </c>
       <c r="S12" t="s">
         <v>43</v>
       </c>
       <c r="T12">
-        <v>0.1753</v>
+        <v>0.1965</v>
       </c>
       <c r="U12">
-        <v>0.1771</v>
+        <v>0.1807</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>0.233</v>
+        <v>0.19</v>
       </c>
       <c r="X12">
         <v>0.2234</v>
       </c>
       <c r="Y12">
-        <v>0.9664</v>
+        <v>0.9953</v>
       </c>
       <c r="AA12" t="s">
         <v>44</v>
@@ -1864,22 +1789,22 @@
         <v>44</v>
       </c>
       <c r="AD12">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
       <c r="AE12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF12">
-        <v>0.1859</v>
+        <v>0.1366</v>
       </c>
       <c r="AG12">
-        <v>0.7848</v>
+        <v>0.8799</v>
       </c>
       <c r="AH12">
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>2.94</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="13" spans="1:39" x14ac:dyDescent="0.25">
@@ -1887,28 +1812,28 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C13">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="D13">
-        <v>125</v>
+        <v>-125</v>
       </c>
       <c r="E13">
-        <v>-147</v>
+        <v>110</v>
       </c>
       <c r="F13" t="s">
         <v>63</v>
       </c>
       <c r="G13">
-        <v>823423</v>
+        <v>824723</v>
       </c>
       <c r="H13" t="s">
         <v>42</v>
       </c>
       <c r="I13">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
@@ -1920,43 +1845,43 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>0.3018</v>
+        <v>0.1513</v>
       </c>
       <c r="N13">
         <v>5</v>
       </c>
       <c r="O13">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="P13">
-        <v>3.94</v>
+        <v>4.34</v>
       </c>
       <c r="Q13">
-        <v>0.2929</v>
+        <v>0.1818</v>
       </c>
       <c r="R13">
-        <v>0.331</v>
+        <v>0.355</v>
       </c>
       <c r="S13" t="s">
         <v>43</v>
       </c>
       <c r="T13">
-        <v>0.2393</v>
+        <v>0.1861</v>
       </c>
       <c r="U13">
-        <v>0.2184</v>
+        <v>0.197</v>
       </c>
       <c r="V13">
         <v>9</v>
       </c>
       <c r="W13">
-        <v>0.2114</v>
+        <v>0.2168</v>
       </c>
       <c r="X13">
         <v>0.2234</v>
       </c>
       <c r="Y13">
-        <v>0.8983</v>
+        <v>0.9954</v>
       </c>
       <c r="AA13" t="s">
         <v>44</v>
@@ -1965,22 +1890,22 @@
         <v>44</v>
       </c>
       <c r="AD13">
-        <v>6.53</v>
+        <v>3.31</v>
       </c>
       <c r="AE13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF13">
-        <v>0.2988</v>
+        <v>0.1621</v>
       </c>
       <c r="AG13">
-        <v>1.0712</v>
+        <v>0.8331</v>
       </c>
       <c r="AH13">
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>6.53</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="14" spans="1:39" x14ac:dyDescent="0.25">
@@ -1988,19 +1913,19 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C14">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D14">
-        <v>-126</v>
+        <v>-102</v>
       </c>
       <c r="E14">
-        <v>110</v>
+        <v>-105</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G14">
         <v>824723</v>
@@ -2009,7 +1934,7 @@
         <v>42</v>
       </c>
       <c r="I14">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="b">
         <v>0</v>
@@ -2021,43 +1946,43 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>0.1513</v>
+        <v>0.2472</v>
       </c>
       <c r="N14">
         <v>5</v>
       </c>
       <c r="O14">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="P14">
-        <v>4.34</v>
+        <v>4.12</v>
       </c>
       <c r="Q14">
-        <v>0.1818</v>
+        <v>0.2143</v>
       </c>
       <c r="R14">
-        <v>0.355</v>
+        <v>0.296</v>
       </c>
       <c r="S14" t="s">
         <v>43</v>
       </c>
       <c r="T14">
-        <v>0.1861</v>
+        <v>0.2613</v>
       </c>
       <c r="U14">
-        <v>0.197</v>
+        <v>0.1821</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>0.2168</v>
+        <v>0.1751</v>
       </c>
       <c r="X14">
         <v>0.2234</v>
       </c>
       <c r="Y14">
-        <v>0.9954</v>
+        <v>0.88</v>
       </c>
       <c r="AA14" t="s">
         <v>44</v>
@@ -2066,22 +1991,22 @@
         <v>44</v>
       </c>
       <c r="AD14">
-        <v>3.31</v>
+        <v>5.18</v>
       </c>
       <c r="AE14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF14">
-        <v>0.1621</v>
+        <v>0.2375</v>
       </c>
       <c r="AG14">
-        <v>0.8329</v>
+        <v>1.1697</v>
       </c>
       <c r="AH14">
         <v>0</v>
       </c>
       <c r="AM14">
-        <v>3.31</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="15" spans="1:39" x14ac:dyDescent="0.25">
@@ -2089,28 +2014,28 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C15">
         <v>4.5</v>
       </c>
       <c r="D15">
-        <v>-102</v>
+        <v>-113</v>
       </c>
       <c r="E15">
-        <v>-106</v>
+        <v>100</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G15">
-        <v>824723</v>
+        <v>823586</v>
       </c>
       <c r="H15" t="s">
         <v>42</v>
       </c>
       <c r="I15">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="b">
         <v>0</v>
@@ -2122,43 +2047,43 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>0.2472</v>
+        <v>0.204</v>
       </c>
       <c r="N15">
         <v>5</v>
       </c>
       <c r="O15">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="P15">
-        <v>4.12</v>
+        <v>4.21</v>
       </c>
       <c r="Q15">
-        <v>0.2143</v>
+        <v>0.2072</v>
       </c>
       <c r="R15">
-        <v>0.296</v>
+        <v>0.357</v>
       </c>
       <c r="S15" t="s">
         <v>43</v>
       </c>
       <c r="T15">
-        <v>0.2613</v>
+        <v>0.246</v>
       </c>
       <c r="U15">
-        <v>0.1821</v>
+        <v>0.249</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>0.1751</v>
+        <v>0.2325</v>
       </c>
       <c r="X15">
         <v>0.2234</v>
       </c>
       <c r="Y15">
-        <v>0.88</v>
+        <v>0.9557</v>
       </c>
       <c r="AA15" t="s">
         <v>44</v>
@@ -2167,22 +2092,22 @@
         <v>44</v>
       </c>
       <c r="AD15">
-        <v>5.18</v>
+        <v>4.95</v>
       </c>
       <c r="AE15" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF15">
-        <v>0.2375</v>
+        <v>0.2051</v>
       </c>
       <c r="AG15">
-        <v>1.1694</v>
+        <v>1.1016</v>
       </c>
       <c r="AH15">
         <v>0</v>
       </c>
       <c r="AM15">
-        <v>5.18</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="16" spans="1:39" x14ac:dyDescent="0.25">
@@ -2190,76 +2115,34 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C16">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D16">
-        <v>-113</v>
+        <v>-110</v>
       </c>
       <c r="E16">
         <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16">
-        <v>823586</v>
+        <v>66</v>
+      </c>
+      <c r="G16" t="s">
+        <v>44</v>
       </c>
       <c r="H16" t="s">
-        <v>42</v>
-      </c>
-      <c r="I16">
-        <v>5.4</v>
-      </c>
-      <c r="J16" t="b">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L16">
         <v>6</v>
       </c>
-      <c r="M16">
-        <v>0.204</v>
-      </c>
-      <c r="N16">
-        <v>5</v>
-      </c>
-      <c r="O16">
-        <v>111</v>
-      </c>
-      <c r="P16">
-        <v>4.21</v>
-      </c>
-      <c r="Q16">
-        <v>0.2072</v>
-      </c>
-      <c r="R16">
-        <v>0.357</v>
-      </c>
       <c r="S16" t="s">
-        <v>43</v>
-      </c>
-      <c r="T16">
-        <v>0.246</v>
-      </c>
-      <c r="U16">
-        <v>0.249</v>
-      </c>
-      <c r="V16">
-        <v>8</v>
-      </c>
-      <c r="W16">
-        <v>0.2325</v>
-      </c>
-      <c r="X16">
-        <v>0.2234</v>
-      </c>
-      <c r="Y16">
-        <v>0.9557</v>
+        <v>44</v>
+      </c>
+      <c r="V16" t="s">
+        <v>44</v>
       </c>
       <c r="AA16" t="s">
         <v>44</v>
@@ -2267,23 +2150,8 @@
       <c r="AC16" t="s">
         <v>44</v>
       </c>
-      <c r="AD16">
-        <v>4.95</v>
-      </c>
       <c r="AE16" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF16">
-        <v>0.2051</v>
-      </c>
-      <c r="AG16">
-        <v>1.1013</v>
-      </c>
-      <c r="AH16">
-        <v>0</v>
-      </c>
-      <c r="AM16">
-        <v>4.95</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2291,19 +2159,28 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>68</v>
+      </c>
+      <c r="C17">
+        <v>4.5</v>
+      </c>
+      <c r="D17">
+        <v>-113</v>
+      </c>
+      <c r="E17">
+        <v>-106</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G17">
-        <v>823586</v>
+        <v>823667</v>
       </c>
       <c r="H17" t="s">
         <v>42</v>
       </c>
       <c r="I17">
-        <v>5.7</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="b">
         <v>0</v>
@@ -2312,46 +2189,46 @@
         <v>0</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>0.1638</v>
+        <v>0.2344</v>
       </c>
       <c r="N17">
         <v>5</v>
       </c>
       <c r="O17">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P17">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="Q17">
-        <v>0.1273</v>
+        <v>0.2883</v>
       </c>
       <c r="R17">
-        <v>0.355</v>
+        <v>0.357</v>
       </c>
       <c r="S17" t="s">
         <v>43</v>
       </c>
       <c r="T17">
-        <v>0.183</v>
+        <v>0.1989</v>
       </c>
       <c r="U17">
-        <v>0.1798</v>
+        <v>0.1944</v>
       </c>
       <c r="V17">
         <v>9</v>
       </c>
       <c r="W17">
-        <v>0.2187</v>
+        <v>0.2114</v>
       </c>
       <c r="X17">
         <v>0.2234</v>
       </c>
       <c r="Y17">
-        <v>1.0025</v>
+        <v>0.9597</v>
       </c>
       <c r="AA17" t="s">
         <v>44</v>
@@ -2360,22 +2237,22 @@
         <v>44</v>
       </c>
       <c r="AD17">
-        <v>2.74</v>
+        <v>4.85</v>
       </c>
       <c r="AE17" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF17">
-        <v>0.1509</v>
+        <v>0.2536</v>
       </c>
       <c r="AG17">
-        <v>0.8193</v>
+        <v>0.8905</v>
       </c>
       <c r="AH17">
         <v>0</v>
       </c>
       <c r="AM17">
-        <v>2.74</v>
+        <v>4.85</v>
       </c>
     </row>
     <row r="18" spans="1:39" x14ac:dyDescent="0.25">
@@ -2383,28 +2260,28 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C18">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D18">
-        <v>-140</v>
+        <v>103</v>
       </c>
       <c r="E18">
-        <v>130</v>
+        <v>-123</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G18">
-        <v>824075</v>
+        <v>823667</v>
       </c>
       <c r="H18" t="s">
         <v>42</v>
       </c>
       <c r="I18">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="J18" t="b">
         <v>0</v>
@@ -2416,7 +2293,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>0.25</v>
+        <v>0.199</v>
       </c>
       <c r="N18">
         <v>5</v>
@@ -2425,10 +2302,10 @@
         <v>112</v>
       </c>
       <c r="P18">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="Q18">
-        <v>0.1964</v>
+        <v>0.2054</v>
       </c>
       <c r="R18">
         <v>0.359</v>
@@ -2437,22 +2314,22 @@
         <v>43</v>
       </c>
       <c r="T18">
-        <v>0.2029</v>
+        <v>0.2465</v>
       </c>
       <c r="U18">
-        <v>0.2085</v>
+        <v>0.2254</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>0.2096</v>
+        <v>0.2179</v>
       </c>
       <c r="X18">
         <v>0.2234</v>
       </c>
       <c r="Y18">
-        <v>0.9401</v>
+        <v>0.9903</v>
       </c>
       <c r="AA18" t="s">
         <v>44</v>
@@ -2461,22 +2338,22 @@
         <v>44</v>
       </c>
       <c r="AD18">
-        <v>4.18</v>
+        <v>5.32</v>
       </c>
       <c r="AE18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF18">
-        <v>0.2308</v>
+        <v>0.2013</v>
       </c>
       <c r="AG18">
-        <v>0.9081</v>
+        <v>1.1035</v>
       </c>
       <c r="AH18">
         <v>0</v>
       </c>
       <c r="AM18">
-        <v>4.18</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="19" spans="1:39" x14ac:dyDescent="0.25">
@@ -2484,67 +2361,34 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>71</v>
+      </c>
+      <c r="C19">
+        <v>3.5</v>
+      </c>
+      <c r="D19">
+        <v>-155</v>
+      </c>
+      <c r="E19">
+        <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19">
-        <v>824075</v>
+        <v>72</v>
+      </c>
+      <c r="G19" t="s">
+        <v>44</v>
       </c>
       <c r="H19" t="s">
-        <v>75</v>
-      </c>
-      <c r="I19">
-        <v>2</v>
-      </c>
-      <c r="J19" t="b">
-        <v>1</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0.197</v>
-      </c>
-      <c r="N19">
-        <v>2</v>
-      </c>
-      <c r="O19">
-        <v>20</v>
-      </c>
-      <c r="P19">
-        <v>4.06</v>
-      </c>
-      <c r="Q19">
-        <v>0.25</v>
-      </c>
-      <c r="R19">
-        <v>0.091</v>
+        <v>3</v>
       </c>
       <c r="S19" t="s">
-        <v>50</v>
-      </c>
-      <c r="T19">
-        <v>0.2396</v>
-      </c>
-      <c r="U19">
-        <v>0.2076</v>
-      </c>
-      <c r="V19">
-        <v>9</v>
-      </c>
-      <c r="W19">
-        <v>0.2478</v>
-      </c>
-      <c r="X19">
-        <v>0.2234</v>
-      </c>
-      <c r="Y19">
-        <v>1.0112</v>
+        <v>44</v>
+      </c>
+      <c r="V19" t="s">
+        <v>44</v>
       </c>
       <c r="AA19" t="s">
         <v>44</v>
@@ -2552,23 +2396,8 @@
       <c r="AC19" t="s">
         <v>44</v>
       </c>
-      <c r="AD19">
-        <v>1.78</v>
-      </c>
       <c r="AE19" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF19">
-        <v>0.2019</v>
-      </c>
-      <c r="AG19">
-        <v>1.0727</v>
-      </c>
-      <c r="AH19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>1.78</v>
+        <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2576,28 +2405,28 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C20">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D20">
-        <v>-108</v>
+        <v>-157</v>
       </c>
       <c r="E20">
-        <v>-104</v>
+        <v>135</v>
       </c>
       <c r="F20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G20">
-        <v>823667</v>
+        <v>823749</v>
       </c>
       <c r="H20" t="s">
         <v>42</v>
       </c>
       <c r="I20">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J20" t="b">
         <v>0</v>
@@ -2606,46 +2435,46 @@
         <v>0</v>
       </c>
       <c r="L20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M20">
-        <v>0.2344</v>
+        <v>0.2969</v>
       </c>
       <c r="N20">
         <v>5</v>
       </c>
       <c r="O20">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>4.11</v>
       </c>
       <c r="Q20">
-        <v>0.2883</v>
+        <v>0.2872</v>
       </c>
       <c r="R20">
-        <v>0.357</v>
+        <v>0.32</v>
       </c>
       <c r="S20" t="s">
         <v>43</v>
       </c>
       <c r="T20">
-        <v>0.1989</v>
+        <v>0.2048</v>
       </c>
       <c r="U20">
-        <v>0.1944</v>
+        <v>0.1923</v>
       </c>
       <c r="V20">
         <v>9</v>
       </c>
       <c r="W20">
-        <v>0.2114</v>
+        <v>0.2395</v>
       </c>
       <c r="X20">
         <v>0.2234</v>
       </c>
       <c r="Y20">
-        <v>0.9597</v>
+        <v>1.0058</v>
       </c>
       <c r="AA20" t="s">
         <v>44</v>
@@ -2654,22 +2483,22 @@
         <v>44</v>
       </c>
       <c r="AD20">
-        <v>4.85</v>
+        <v>5.47</v>
       </c>
       <c r="AE20" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF20">
-        <v>0.2536</v>
+        <v>0.2938</v>
       </c>
       <c r="AG20">
-        <v>0.8902</v>
+        <v>0.9167</v>
       </c>
       <c r="AH20">
         <v>0</v>
       </c>
       <c r="AM20">
-        <v>4.85</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="21" spans="1:39" x14ac:dyDescent="0.25">
@@ -2677,22 +2506,22 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C21">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="D21">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="E21">
-        <v>-120</v>
+        <v>-154</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="G21">
-        <v>823667</v>
+        <v>823749</v>
       </c>
       <c r="H21" t="s">
         <v>42</v>
@@ -2710,43 +2539,43 @@
         <v>6</v>
       </c>
       <c r="M21">
-        <v>0.199</v>
+        <v>0.2538</v>
       </c>
       <c r="N21">
         <v>5</v>
       </c>
       <c r="O21">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="P21">
-        <v>4.25</v>
+        <v>3.89</v>
       </c>
       <c r="Q21">
-        <v>0.2054</v>
+        <v>0.1638</v>
       </c>
       <c r="R21">
-        <v>0.359</v>
+        <v>0.367</v>
       </c>
       <c r="S21" t="s">
         <v>43</v>
       </c>
       <c r="T21">
-        <v>0.2465</v>
+        <v>0.2326</v>
       </c>
       <c r="U21">
-        <v>0.2254</v>
+        <v>0.2315</v>
       </c>
       <c r="V21">
         <v>9</v>
       </c>
       <c r="W21">
-        <v>0.2179</v>
+        <v>0.2155</v>
       </c>
       <c r="X21">
         <v>0.2234</v>
       </c>
       <c r="Y21">
-        <v>0.9903</v>
+        <v>1.0453</v>
       </c>
       <c r="AA21" t="s">
         <v>44</v>
@@ -2755,22 +2584,22 @@
         <v>44</v>
       </c>
       <c r="AD21">
-        <v>5.32</v>
+        <v>5.35</v>
       </c>
       <c r="AE21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF21">
-        <v>0.2013</v>
+        <v>0.2207</v>
       </c>
       <c r="AG21">
-        <v>1.1032</v>
+        <v>1.0414</v>
       </c>
       <c r="AH21">
         <v>0</v>
       </c>
       <c r="AM21">
-        <v>5.32</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="22" spans="1:39" x14ac:dyDescent="0.25">
@@ -2778,28 +2607,28 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C22">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="D22">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E22">
-        <v>-150</v>
+        <v>-138</v>
       </c>
       <c r="F22" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G22">
-        <v>823749</v>
+        <v>824639</v>
       </c>
       <c r="H22" t="s">
         <v>42</v>
       </c>
       <c r="I22">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J22" t="b">
         <v>0</v>
@@ -2811,43 +2640,43 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>0.2538</v>
+        <v>0.2347</v>
       </c>
       <c r="N22">
         <v>5</v>
       </c>
       <c r="O22">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="P22">
-        <v>3.89</v>
+        <v>4.23</v>
       </c>
       <c r="Q22">
-        <v>0.1638</v>
+        <v>0.1864</v>
       </c>
       <c r="R22">
-        <v>0.367</v>
+        <v>0.371</v>
       </c>
       <c r="S22" t="s">
         <v>43</v>
       </c>
       <c r="T22">
-        <v>0.2326</v>
+        <v>0.2459</v>
       </c>
       <c r="U22">
-        <v>0.2315</v>
+        <v>0.2514</v>
       </c>
       <c r="V22">
         <v>9</v>
       </c>
       <c r="W22">
-        <v>0.2155</v>
+        <v>0.2368</v>
       </c>
       <c r="X22">
         <v>0.2234</v>
       </c>
       <c r="Y22">
-        <v>1.0453</v>
+        <v>1.0865</v>
       </c>
       <c r="AA22" t="s">
         <v>44</v>
@@ -2856,22 +2685,22 @@
         <v>44</v>
       </c>
       <c r="AD22">
-        <v>5.35</v>
+        <v>6.1</v>
       </c>
       <c r="AE22" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AF22">
-        <v>0.2207</v>
+        <v>0.2168</v>
       </c>
       <c r="AG22">
-        <v>1.0411</v>
+        <v>1.101</v>
       </c>
       <c r="AH22">
         <v>0</v>
       </c>
       <c r="AM22">
-        <v>5.35</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="23" spans="1:39" x14ac:dyDescent="0.25">
@@ -2879,28 +2708,28 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C23">
-        <v>5.5</v>
+        <v>3.5</v>
       </c>
       <c r="D23">
-        <v>-160</v>
+        <v>-115</v>
       </c>
       <c r="E23">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="F23" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G23">
-        <v>823749</v>
+        <v>822859</v>
       </c>
       <c r="H23" t="s">
         <v>42</v>
       </c>
       <c r="I23">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="J23" t="b">
         <v>0</v>
@@ -2912,43 +2741,43 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>0.2969</v>
+        <v>0.1644</v>
       </c>
       <c r="N23">
         <v>5</v>
       </c>
       <c r="O23">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="P23">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="Q23">
-        <v>0.2872</v>
+        <v>0.1892</v>
       </c>
       <c r="R23">
-        <v>0.32</v>
+        <v>0.357</v>
       </c>
       <c r="S23" t="s">
         <v>43</v>
       </c>
       <c r="T23">
-        <v>0.2048</v>
+        <v>0.2271</v>
       </c>
       <c r="U23">
-        <v>0.1923</v>
+        <v>0.2265</v>
       </c>
       <c r="V23">
         <v>9</v>
       </c>
       <c r="W23">
-        <v>0.2395</v>
+        <v>0.2076</v>
       </c>
       <c r="X23">
         <v>0.2234</v>
       </c>
       <c r="Y23">
-        <v>1.0058</v>
+        <v>0.989</v>
       </c>
       <c r="AA23" t="s">
         <v>44</v>
@@ -2957,22 +2786,22 @@
         <v>44</v>
       </c>
       <c r="AD23">
-        <v>5.47</v>
+        <v>3.43</v>
       </c>
       <c r="AE23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF23">
-        <v>0.2938</v>
+        <v>0.1733</v>
       </c>
       <c r="AG23">
-        <v>0.9165</v>
+        <v>1.0167</v>
       </c>
       <c r="AH23">
         <v>0</v>
       </c>
       <c r="AM23">
-        <v>5.47</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="24" spans="1:39" x14ac:dyDescent="0.25">
@@ -2980,76 +2809,34 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C24">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="D24">
-        <v>-105</v>
+        <v>134</v>
       </c>
       <c r="E24">
-        <v>-103</v>
+        <v>-153</v>
       </c>
       <c r="F24" t="s">
-        <v>83</v>
-      </c>
-      <c r="G24">
-        <v>822859</v>
+        <v>79</v>
+      </c>
+      <c r="G24" t="s">
+        <v>44</v>
       </c>
       <c r="H24" t="s">
-        <v>42</v>
-      </c>
-      <c r="I24">
-        <v>4.7</v>
-      </c>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
-      <c r="M24">
-        <v>0.1644</v>
-      </c>
-      <c r="N24">
-        <v>5</v>
-      </c>
-      <c r="O24">
-        <v>111</v>
-      </c>
-      <c r="P24">
-        <v>4.22</v>
-      </c>
-      <c r="Q24">
-        <v>0.1892</v>
-      </c>
-      <c r="R24">
-        <v>0.357</v>
-      </c>
       <c r="S24" t="s">
-        <v>43</v>
-      </c>
-      <c r="T24">
-        <v>0.2271</v>
-      </c>
-      <c r="U24">
-        <v>0.2265</v>
-      </c>
-      <c r="V24">
-        <v>9</v>
-      </c>
-      <c r="W24">
-        <v>0.2076</v>
-      </c>
-      <c r="X24">
-        <v>0.2234</v>
-      </c>
-      <c r="Y24">
-        <v>0.989</v>
+        <v>44</v>
+      </c>
+      <c r="V24" t="s">
+        <v>44</v>
       </c>
       <c r="AA24" t="s">
         <v>44</v>
@@ -3057,23 +2844,8 @@
       <c r="AC24" t="s">
         <v>44</v>
       </c>
-      <c r="AD24">
-        <v>3.43</v>
-      </c>
       <c r="AE24" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF24">
-        <v>0.1733</v>
-      </c>
-      <c r="AG24">
-        <v>1.0164</v>
-      </c>
-      <c r="AH24">
-        <v>0</v>
-      </c>
-      <c r="AM24">
-        <v>3.43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -3081,67 +2853,34 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>84</v>
+        <v>81</v>
+      </c>
+      <c r="C25">
+        <v>4.5</v>
+      </c>
+      <c r="D25">
+        <v>127</v>
+      </c>
+      <c r="E25">
+        <v>-150</v>
       </c>
       <c r="F25" t="s">
-        <v>85</v>
-      </c>
-      <c r="G25">
-        <v>824639</v>
+        <v>82</v>
+      </c>
+      <c r="G25" t="s">
+        <v>44</v>
       </c>
       <c r="H25" t="s">
-        <v>75</v>
-      </c>
-      <c r="I25">
-        <v>1.2</v>
-      </c>
-      <c r="J25" t="b">
-        <v>1</v>
-      </c>
-      <c r="K25" t="b">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0.2283</v>
-      </c>
-      <c r="N25">
-        <v>5</v>
-      </c>
-      <c r="O25">
-        <v>20</v>
-      </c>
-      <c r="P25">
-        <v>4.24</v>
-      </c>
-      <c r="Q25">
-        <v>0.2</v>
-      </c>
-      <c r="R25">
-        <v>0.091</v>
+        <v>6</v>
       </c>
       <c r="S25" t="s">
-        <v>50</v>
-      </c>
-      <c r="T25">
-        <v>0.2231</v>
-      </c>
-      <c r="U25">
-        <v>0.2215</v>
-      </c>
-      <c r="V25">
-        <v>9</v>
-      </c>
-      <c r="W25">
-        <v>0.2191</v>
-      </c>
-      <c r="X25">
-        <v>0.2234</v>
-      </c>
-      <c r="Y25">
-        <v>0.9381</v>
+        <v>44</v>
+      </c>
+      <c r="V25" t="s">
+        <v>44</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
@@ -3149,23 +2888,8 @@
       <c r="AC25" t="s">
         <v>44</v>
       </c>
-      <c r="AD25">
-        <v>1.05</v>
-      </c>
       <c r="AE25" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF25">
-        <v>0.2257</v>
-      </c>
-      <c r="AG25">
-        <v>0.9986</v>
-      </c>
-      <c r="AH25">
-        <v>0</v>
-      </c>
-      <c r="AM25">
-        <v>1.05</v>
+        <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -3173,28 +2897,28 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C26">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="D26">
-        <v>121</v>
+        <v>-112</v>
       </c>
       <c r="E26">
-        <v>-138</v>
+        <v>-106</v>
       </c>
       <c r="F26" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G26">
-        <v>824639</v>
+        <v>824154</v>
       </c>
       <c r="H26" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="I26">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="J26" t="b">
         <v>0</v>
@@ -3206,43 +2930,43 @@
         <v>6</v>
       </c>
       <c r="M26">
-        <v>0.2347</v>
+        <v>0.1678</v>
       </c>
       <c r="N26">
         <v>5</v>
       </c>
       <c r="O26">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="P26">
-        <v>4.23</v>
+        <v>4.61</v>
       </c>
       <c r="Q26">
-        <v>0.1864</v>
+        <v>0.1209</v>
       </c>
       <c r="R26">
-        <v>0.371</v>
+        <v>0.313</v>
       </c>
       <c r="S26" t="s">
         <v>43</v>
       </c>
       <c r="T26">
-        <v>0.2459</v>
+        <v>0.2136</v>
       </c>
       <c r="U26">
-        <v>0.2514</v>
+        <v>0.2242</v>
       </c>
       <c r="V26">
         <v>9</v>
       </c>
       <c r="W26">
-        <v>0.2368</v>
+        <v>0.2504</v>
       </c>
       <c r="X26">
         <v>0.2234</v>
       </c>
       <c r="Y26">
-        <v>1.0865</v>
+        <v>0.9877</v>
       </c>
       <c r="AA26" t="s">
         <v>44</v>
@@ -3251,22 +2975,22 @@
         <v>44</v>
       </c>
       <c r="AD26">
-        <v>6.1</v>
+        <v>2.59</v>
       </c>
       <c r="AE26" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="AF26">
-        <v>0.2168</v>
+        <v>0.1531</v>
       </c>
       <c r="AG26">
-        <v>1.1007</v>
+        <v>0.9562</v>
       </c>
       <c r="AH26">
         <v>0</v>
       </c>
       <c r="AM26">
-        <v>6.1</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="27" spans="1:39" x14ac:dyDescent="0.25">
@@ -3274,28 +2998,28 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C27">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="D27">
-        <v>-113</v>
+        <v>119</v>
       </c>
       <c r="E27">
-        <v>-105</v>
+        <v>-141</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G27">
-        <v>824154</v>
+        <v>824319</v>
       </c>
       <c r="H27" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="I27">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="J27" t="b">
         <v>0</v>
@@ -3307,43 +3031,43 @@
         <v>6</v>
       </c>
       <c r="M27">
-        <v>0.1678</v>
+        <v>0.1597</v>
       </c>
       <c r="N27">
         <v>5</v>
       </c>
       <c r="O27">
-        <v>91</v>
+        <v>115</v>
       </c>
       <c r="P27">
-        <v>4.61</v>
+        <v>4.39</v>
       </c>
       <c r="Q27">
-        <v>0.1209</v>
+        <v>0.1217</v>
       </c>
       <c r="R27">
-        <v>0.313</v>
+        <v>0.365</v>
       </c>
       <c r="S27" t="s">
         <v>43</v>
       </c>
       <c r="T27">
-        <v>0.2136</v>
+        <v>0.1963</v>
       </c>
       <c r="U27">
-        <v>0.2242</v>
+        <v>0.1991</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>0.2504</v>
+        <v>0.2061</v>
       </c>
       <c r="X27">
         <v>0.2234</v>
       </c>
       <c r="Y27">
-        <v>0.9877</v>
+        <v>0.9839</v>
       </c>
       <c r="AA27" t="s">
         <v>44</v>
@@ -3352,22 +3076,22 @@
         <v>44</v>
       </c>
       <c r="AD27">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
       <c r="AE27" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF27">
-        <v>0.1531</v>
+        <v>0.1458</v>
       </c>
       <c r="AG27">
-        <v>0.9559</v>
+        <v>0.8791</v>
       </c>
       <c r="AH27">
         <v>0</v>
       </c>
       <c r="AM27">
-        <v>2.59</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="28" spans="1:39" x14ac:dyDescent="0.25">
@@ -3375,19 +3099,19 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C28">
         <v>3.5</v>
       </c>
       <c r="D28">
-        <v>-120</v>
+        <v>-125</v>
       </c>
       <c r="E28">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F28" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G28">
         <v>824319</v>
@@ -3426,13 +3150,13 @@
         <v>0.369</v>
       </c>
       <c r="S28" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T28">
-        <v>0.2216</v>
+        <v>0.2403</v>
       </c>
       <c r="U28">
-        <v>0.2193</v>
+        <v>0.2113</v>
       </c>
       <c r="V28">
         <v>9</v>
@@ -3444,7 +3168,7 @@
         <v>0.2234</v>
       </c>
       <c r="Y28">
-        <v>1.0013</v>
+        <v>1.0214</v>
       </c>
       <c r="AA28" t="s">
         <v>44</v>
@@ -3453,22 +3177,22 @@
         <v>44</v>
       </c>
       <c r="AD28">
-        <v>3.36</v>
+        <v>3.72</v>
       </c>
       <c r="AE28" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="AF28">
         <v>0.1555</v>
       </c>
       <c r="AG28">
-        <v>0.9921</v>
+        <v>1.0758</v>
       </c>
       <c r="AH28">
         <v>0</v>
       </c>
       <c r="AM28">
-        <v>3.36</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="29" spans="1:39" x14ac:dyDescent="0.25">
@@ -3476,28 +3200,19 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C29">
-        <v>3.5</v>
-      </c>
-      <c r="D29">
-        <v>117</v>
-      </c>
-      <c r="E29">
-        <v>-144</v>
+        <v>88</v>
       </c>
       <c r="F29" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="G29">
-        <v>824319</v>
+        <v>824803</v>
       </c>
       <c r="H29" t="s">
         <v>42</v>
       </c>
       <c r="I29">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="b">
         <v>0</v>
@@ -3506,46 +3221,46 @@
         <v>0</v>
       </c>
       <c r="L29">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M29">
-        <v>0.1597</v>
+        <v>0.268</v>
       </c>
       <c r="N29">
         <v>5</v>
       </c>
       <c r="O29">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="P29">
-        <v>4.39</v>
+        <v>4.19</v>
       </c>
       <c r="Q29">
-        <v>0.1217</v>
+        <v>0.2832</v>
       </c>
       <c r="R29">
-        <v>0.365</v>
+        <v>0.361</v>
       </c>
       <c r="S29" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="T29">
-        <v>0.2783</v>
+        <v>0.2607</v>
       </c>
       <c r="U29">
-        <v>0.2137</v>
+        <v>0.246</v>
       </c>
       <c r="V29">
         <v>9</v>
       </c>
       <c r="W29">
-        <v>0.2061</v>
+        <v>0.2568</v>
       </c>
       <c r="X29">
         <v>0.2234</v>
       </c>
       <c r="Y29">
-        <v>1.0055</v>
+        <v>1.0725</v>
       </c>
       <c r="AA29" t="s">
         <v>44</v>
@@ -3554,22 +3269,22 @@
         <v>44</v>
       </c>
       <c r="AD29">
-        <v>3.88</v>
+        <v>7.38</v>
       </c>
       <c r="AE29" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="AF29">
-        <v>0.1458</v>
+        <v>0.2735</v>
       </c>
       <c r="AG29">
-        <v>1.2457</v>
+        <v>1.167</v>
       </c>
       <c r="AH29">
         <v>0</v>
       </c>
       <c r="AM29">
-        <v>3.88</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="30" spans="1:39" x14ac:dyDescent="0.25">
@@ -3577,34 +3292,67 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30">
-        <v>4.5</v>
-      </c>
-      <c r="D30">
-        <v>-154</v>
-      </c>
-      <c r="E30">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="F30" t="s">
-        <v>41</v>
-      </c>
-      <c r="G30" t="s">
-        <v>44</v>
+        <v>60</v>
+      </c>
+      <c r="G30">
+        <v>822938</v>
       </c>
       <c r="H30" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I30">
+        <v>5.6</v>
+      </c>
+      <c r="J30" t="b">
+        <v>0</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0.2423</v>
+      </c>
+      <c r="N30">
+        <v>5</v>
+      </c>
+      <c r="O30">
+        <v>107</v>
+      </c>
+      <c r="P30">
+        <v>4.14</v>
+      </c>
+      <c r="Q30">
+        <v>0.1776</v>
+      </c>
+      <c r="R30">
+        <v>0.349</v>
       </c>
       <c r="S30" t="s">
-        <v>44</v>
-      </c>
-      <c r="V30" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T30">
+        <v>0.1843</v>
+      </c>
+      <c r="U30">
+        <v>0.1802</v>
+      </c>
+      <c r="V30">
+        <v>9</v>
+      </c>
+      <c r="W30">
+        <v>0.1897</v>
+      </c>
+      <c r="X30">
+        <v>0.2234</v>
+      </c>
+      <c r="Y30">
+        <v>0.88</v>
       </c>
       <c r="AA30" t="s">
         <v>44</v>
@@ -3612,8 +3360,23 @@
       <c r="AC30" t="s">
         <v>44</v>
       </c>
+      <c r="AD30">
+        <v>3.68</v>
+      </c>
       <c r="AE30" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF30">
+        <v>0.2197</v>
+      </c>
+      <c r="AG30">
+        <v>0.825</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AM30">
+        <v>3.68</v>
       </c>
     </row>
     <row r="31" spans="1:39" x14ac:dyDescent="0.25">
@@ -3621,34 +3384,55 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
-      </c>
-      <c r="C31">
+        <v>91</v>
+      </c>
+      <c r="F31" t="s">
+        <v>58</v>
+      </c>
+      <c r="G31">
+        <v>823423</v>
+      </c>
+      <c r="H31" t="s">
+        <v>92</v>
+      </c>
+      <c r="I31">
         <v>4.5</v>
       </c>
-      <c r="D31">
-        <v>120</v>
-      </c>
-      <c r="E31">
-        <v>-145</v>
-      </c>
-      <c r="F31" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" t="s">
-        <v>44</v>
-      </c>
-      <c r="H31" t="s">
-        <v>44</v>
+      <c r="J31" t="b">
+        <v>1</v>
+      </c>
+      <c r="K31" t="b">
+        <v>0</v>
       </c>
       <c r="L31">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0.1859</v>
+      </c>
+      <c r="P31">
+        <v>4.63</v>
       </c>
       <c r="S31" t="s">
-        <v>44</v>
-      </c>
-      <c r="V31" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T31">
+        <v>0.1753</v>
+      </c>
+      <c r="U31">
+        <v>0.1771</v>
+      </c>
+      <c r="V31">
+        <v>9</v>
+      </c>
+      <c r="W31">
+        <v>0.233</v>
+      </c>
+      <c r="X31">
+        <v>0.2234</v>
+      </c>
+      <c r="Y31">
+        <v>0.9664</v>
       </c>
       <c r="AA31" t="s">
         <v>44</v>
@@ -3656,8 +3440,23 @@
       <c r="AC31" t="s">
         <v>44</v>
       </c>
+      <c r="AD31">
+        <v>2.94</v>
+      </c>
       <c r="AE31" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF31">
+        <v>0.1859</v>
+      </c>
+      <c r="AG31">
+        <v>0.785</v>
+      </c>
+      <c r="AH31">
+        <v>0</v>
+      </c>
+      <c r="AM31">
+        <v>2.94</v>
       </c>
     </row>
     <row r="32" spans="1:39" x14ac:dyDescent="0.25">
@@ -3665,34 +3464,67 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
-      </c>
-      <c r="C32">
-        <v>3.5</v>
-      </c>
-      <c r="D32">
-        <v>-109</v>
-      </c>
-      <c r="E32">
-        <v>-104</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s">
-        <v>70</v>
-      </c>
-      <c r="G32" t="s">
-        <v>44</v>
+        <v>66</v>
+      </c>
+      <c r="G32">
+        <v>823586</v>
       </c>
       <c r="H32" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="I32">
+        <v>5.7</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
       </c>
       <c r="L32">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0.1638</v>
+      </c>
+      <c r="N32">
+        <v>5</v>
+      </c>
+      <c r="O32">
+        <v>110</v>
+      </c>
+      <c r="P32">
+        <v>3.9</v>
+      </c>
+      <c r="Q32">
+        <v>0.1273</v>
+      </c>
+      <c r="R32">
+        <v>0.355</v>
       </c>
       <c r="S32" t="s">
-        <v>44</v>
-      </c>
-      <c r="V32" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T32">
+        <v>0.183</v>
+      </c>
+      <c r="U32">
+        <v>0.1798</v>
+      </c>
+      <c r="V32">
+        <v>9</v>
+      </c>
+      <c r="W32">
+        <v>0.2187</v>
+      </c>
+      <c r="X32">
+        <v>0.2234</v>
+      </c>
+      <c r="Y32">
+        <v>1.0025</v>
       </c>
       <c r="AA32" t="s">
         <v>44</v>
@@ -3700,8 +3532,23 @@
       <c r="AC32" t="s">
         <v>44</v>
       </c>
+      <c r="AD32">
+        <v>2.74</v>
+      </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF32">
+        <v>0.1509</v>
+      </c>
+      <c r="AG32">
+        <v>0.8195</v>
+      </c>
+      <c r="AH32">
+        <v>0</v>
+      </c>
+      <c r="AM32">
+        <v>2.74</v>
       </c>
     </row>
     <row r="33" spans="1:39" x14ac:dyDescent="0.25">
@@ -3709,34 +3556,67 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
-      </c>
-      <c r="C33">
-        <v>4.5</v>
-      </c>
-      <c r="D33">
-        <v>142</v>
-      </c>
-      <c r="E33">
-        <v>-156</v>
+        <v>94</v>
       </c>
       <c r="F33" t="s">
-        <v>83</v>
-      </c>
-      <c r="G33" t="s">
-        <v>44</v>
+        <v>72</v>
+      </c>
+      <c r="G33">
+        <v>824075</v>
       </c>
       <c r="H33" t="s">
-        <v>44</v>
+        <v>95</v>
+      </c>
+      <c r="I33">
+        <v>2.3</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
       </c>
       <c r="L33">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0.1978</v>
+      </c>
+      <c r="N33">
+        <v>1</v>
+      </c>
+      <c r="O33">
+        <v>10</v>
+      </c>
+      <c r="P33">
+        <v>4.4</v>
+      </c>
+      <c r="Q33">
+        <v>0.3</v>
+      </c>
+      <c r="R33">
+        <v>0.048</v>
       </c>
       <c r="S33" t="s">
-        <v>44</v>
-      </c>
-      <c r="V33" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="T33">
+        <v>0.2029</v>
+      </c>
+      <c r="U33">
+        <v>0.2085</v>
+      </c>
+      <c r="V33">
+        <v>9</v>
+      </c>
+      <c r="W33">
+        <v>0.2181</v>
+      </c>
+      <c r="X33">
+        <v>0.2234</v>
+      </c>
+      <c r="Y33">
+        <v>0.924</v>
       </c>
       <c r="AA33" t="s">
         <v>44</v>
@@ -3744,8 +3624,23 @@
       <c r="AC33" t="s">
         <v>44</v>
       </c>
+      <c r="AD33">
+        <v>1.75</v>
+      </c>
       <c r="AE33" t="s">
-        <v>44</v>
+        <v>49</v>
+      </c>
+      <c r="AF33">
+        <v>0.2027</v>
+      </c>
+      <c r="AG33">
+        <v>0.9083</v>
+      </c>
+      <c r="AH33">
+        <v>0</v>
+      </c>
+      <c r="AM33">
+        <v>1.75</v>
       </c>
     </row>
     <row r="34" spans="1:39" x14ac:dyDescent="0.25">
@@ -3753,43 +3648,183 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" t="s">
+        <v>72</v>
+      </c>
+      <c r="G34">
+        <v>824075</v>
+      </c>
+      <c r="H34" t="s">
+        <v>95</v>
+      </c>
+      <c r="I34">
+        <v>2</v>
+      </c>
+      <c r="J34" t="b">
+        <v>1</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0.197</v>
+      </c>
+      <c r="N34">
+        <v>2</v>
+      </c>
+      <c r="O34">
+        <v>20</v>
+      </c>
+      <c r="P34">
+        <v>4.06</v>
+      </c>
+      <c r="Q34">
+        <v>0.25</v>
+      </c>
+      <c r="R34">
+        <v>0.091</v>
+      </c>
+      <c r="S34" t="s">
+        <v>43</v>
+      </c>
+      <c r="T34">
+        <v>0.241</v>
+      </c>
+      <c r="U34">
+        <v>0.1954</v>
+      </c>
+      <c r="V34">
+        <v>9</v>
+      </c>
+      <c r="W34">
+        <v>0.2478</v>
+      </c>
+      <c r="X34">
+        <v>0.2234</v>
+      </c>
+      <c r="Y34">
+        <v>1.0036</v>
+      </c>
+      <c r="AA34" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD34">
+        <v>1.77</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF34">
+        <v>0.2019</v>
+      </c>
+      <c r="AG34">
+        <v>1.0788</v>
+      </c>
+      <c r="AH34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>1.77</v>
+      </c>
+    </row>
+    <row r="35" spans="1:39" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
         <v>97</v>
       </c>
-      <c r="C34">
-        <v>4.5</v>
-      </c>
-      <c r="D34">
-        <v>122</v>
-      </c>
-      <c r="E34">
-        <v>-153</v>
-      </c>
-      <c r="F34" t="s">
-        <v>88</v>
-      </c>
-      <c r="G34" t="s">
-        <v>44</v>
-      </c>
-      <c r="H34" t="s">
-        <v>44</v>
-      </c>
-      <c r="L34">
-        <v>6</v>
-      </c>
-      <c r="S34" t="s">
-        <v>44</v>
-      </c>
-      <c r="V34" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA34" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC34" t="s">
-        <v>44</v>
-      </c>
-      <c r="AE34" t="s">
-        <v>44</v>
+      <c r="F35" t="s">
+        <v>77</v>
+      </c>
+      <c r="G35">
+        <v>824639</v>
+      </c>
+      <c r="H35" t="s">
+        <v>95</v>
+      </c>
+      <c r="I35">
+        <v>1.2</v>
+      </c>
+      <c r="J35" t="b">
+        <v>1</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0.2283</v>
+      </c>
+      <c r="N35">
+        <v>5</v>
+      </c>
+      <c r="O35">
+        <v>20</v>
+      </c>
+      <c r="P35">
+        <v>4.24</v>
+      </c>
+      <c r="Q35">
+        <v>0.2</v>
+      </c>
+      <c r="R35">
+        <v>0.091</v>
+      </c>
+      <c r="S35" t="s">
+        <v>43</v>
+      </c>
+      <c r="T35">
+        <v>0.2422</v>
+      </c>
+      <c r="U35">
+        <v>0.2319</v>
+      </c>
+      <c r="V35">
+        <v>9</v>
+      </c>
+      <c r="W35">
+        <v>0.2191</v>
+      </c>
+      <c r="X35">
+        <v>0.2234</v>
+      </c>
+      <c r="Y35">
+        <v>0.889</v>
+      </c>
+      <c r="AA35" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC35" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD35">
+        <v>1.08</v>
+      </c>
+      <c r="AE35" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF35">
+        <v>0.2257</v>
+      </c>
+      <c r="AG35">
+        <v>1.0845</v>
+      </c>
+      <c r="AH35">
+        <v>0</v>
+      </c>
+      <c r="AM35">
+        <v>1.08</v>
       </c>
     </row>
   </sheetData>

--- a/data/k-props/2026-08-18.xlsx
+++ b/data/k-props/2026-08-18.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="102">
   <si>
     <t>date</t>
   </si>
@@ -145,6 +145,9 @@
     <t>lineup_unweighted_30d_posted</t>
   </si>
   <si>
+    <t>O</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -160,16 +163,25 @@
     <t>St. Louis Cardinals @ Cincinnati Reds</t>
   </si>
   <si>
+    <t>L</t>
+  </si>
+  <si>
     <t>&lt;6</t>
   </si>
   <si>
     <t>Kyle Leahy</t>
   </si>
   <si>
+    <t>W</t>
+  </si>
+  <si>
     <t>Carson Whisenhunt</t>
   </si>
   <si>
     <t>San Francisco Giants @ Cleveland Guardians</t>
+  </si>
+  <si>
+    <t>U</t>
   </si>
   <si>
     <t>Foster Griffin</t>
@@ -886,17 +898,23 @@
       <c r="Y2">
         <v>1.0455</v>
       </c>
+      <c r="Z2">
+        <v>10</v>
+      </c>
       <c r="AA2" t="s">
         <v>44</v>
       </c>
+      <c r="AB2">
+        <v>0.63</v>
+      </c>
       <c r="AC2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD2">
         <v>6.13</v>
       </c>
       <c r="AE2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF2">
         <v>0.2019</v>
@@ -906,6 +924,18 @@
       </c>
       <c r="AH2">
         <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>3.87</v>
+      </c>
+      <c r="AJ2">
+        <v>3.87</v>
+      </c>
+      <c r="AK2">
+        <v>3.87</v>
+      </c>
+      <c r="AL2">
+        <v>3.87</v>
       </c>
       <c r="AM2">
         <v>6.13</v>
@@ -916,7 +946,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3">
         <v>4.5</v>
@@ -931,28 +961,28 @@
         <v>41</v>
       </c>
       <c r="G3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L3">
         <v>6</v>
       </c>
       <c r="S3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:39" x14ac:dyDescent="0.25">
@@ -960,7 +990,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4">
         <v>4.5</v>
@@ -972,7 +1002,7 @@
         <v>-126</v>
       </c>
       <c r="F4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G4">
         <v>824475</v>
@@ -1031,17 +1061,23 @@
       <c r="Y4">
         <v>0.9052</v>
       </c>
+      <c r="Z4">
+        <v>6</v>
+      </c>
       <c r="AA4" t="s">
         <v>44</v>
       </c>
+      <c r="AB4">
+        <v>-1.09</v>
+      </c>
       <c r="AC4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AD4">
         <v>3.41</v>
       </c>
       <c r="AE4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF4">
         <v>0.166</v>
@@ -1051,6 +1087,18 @@
       </c>
       <c r="AH4">
         <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>2.59</v>
+      </c>
+      <c r="AJ4">
+        <v>2.59</v>
+      </c>
+      <c r="AK4">
+        <v>2.59</v>
+      </c>
+      <c r="AL4">
+        <v>2.59</v>
       </c>
       <c r="AM4">
         <v>3.41</v>
@@ -1061,7 +1109,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C5">
         <v>5.5</v>
@@ -1073,7 +1121,7 @@
         <v>-120</v>
       </c>
       <c r="F5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5">
         <v>824475</v>
@@ -1132,17 +1180,23 @@
       <c r="Y5">
         <v>1.0796</v>
       </c>
+      <c r="Z5">
+        <v>6</v>
+      </c>
       <c r="AA5" t="s">
         <v>44</v>
       </c>
+      <c r="AB5">
+        <v>1.29</v>
+      </c>
       <c r="AC5" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD5">
         <v>6.79</v>
       </c>
       <c r="AE5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF5">
         <v>0.2328</v>
@@ -1152,6 +1206,18 @@
       </c>
       <c r="AH5">
         <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>-0.79</v>
+      </c>
+      <c r="AJ5">
+        <v>0.79</v>
+      </c>
+      <c r="AK5">
+        <v>-0.79</v>
+      </c>
+      <c r="AL5">
+        <v>0.79</v>
       </c>
       <c r="AM5">
         <v>6.79</v>
@@ -1162,7 +1228,7 @@
         <v>39</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C6">
         <v>3.5</v>
@@ -1174,7 +1240,7 @@
         <v>-107</v>
       </c>
       <c r="F6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G6">
         <v>824398</v>
@@ -1233,17 +1299,23 @@
       <c r="Y6">
         <v>0.9198</v>
       </c>
+      <c r="Z6">
+        <v>1</v>
+      </c>
       <c r="AA6" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB6">
+        <v>-0.4</v>
       </c>
       <c r="AC6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD6">
         <v>3.1</v>
       </c>
       <c r="AE6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF6">
         <v>0.1754</v>
@@ -1253,6 +1325,18 @@
       </c>
       <c r="AH6">
         <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>-2.1</v>
+      </c>
+      <c r="AJ6">
+        <v>2.1</v>
+      </c>
+      <c r="AK6">
+        <v>-2.1</v>
+      </c>
+      <c r="AL6">
+        <v>2.1</v>
       </c>
       <c r="AM6">
         <v>3.1</v>
@@ -1263,7 +1347,7 @@
         <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>5.5</v>
@@ -1275,7 +1359,7 @@
         <v>-105</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G7">
         <v>824398</v>
@@ -1334,17 +1418,23 @@
       <c r="Y7">
         <v>1.0041</v>
       </c>
+      <c r="Z7">
+        <v>6</v>
+      </c>
       <c r="AA7" t="s">
         <v>44</v>
       </c>
+      <c r="AB7">
+        <v>-0.94</v>
+      </c>
       <c r="AC7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AD7">
         <v>4.56</v>
       </c>
       <c r="AE7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF7">
         <v>0.1877</v>
@@ -1354,6 +1444,18 @@
       </c>
       <c r="AH7">
         <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>1.44</v>
+      </c>
+      <c r="AJ7">
+        <v>1.44</v>
+      </c>
+      <c r="AK7">
+        <v>1.44</v>
+      </c>
+      <c r="AL7">
+        <v>1.44</v>
       </c>
       <c r="AM7">
         <v>4.56</v>
@@ -1364,7 +1466,7 @@
         <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>3.5</v>
@@ -1376,7 +1478,7 @@
         <v>122</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>823341</v>
@@ -1435,17 +1537,23 @@
       <c r="Y8">
         <v>1.0856</v>
       </c>
+      <c r="Z8">
+        <v>3</v>
+      </c>
       <c r="AA8" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB8">
+        <v>0.99</v>
       </c>
       <c r="AC8" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AD8">
         <v>4.49</v>
       </c>
       <c r="AE8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF8">
         <v>0.1563</v>
@@ -1455,6 +1563,18 @@
       </c>
       <c r="AH8">
         <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>-1.49</v>
+      </c>
+      <c r="AJ8">
+        <v>1.49</v>
+      </c>
+      <c r="AK8">
+        <v>-1.49</v>
+      </c>
+      <c r="AL8">
+        <v>1.49</v>
       </c>
       <c r="AM8">
         <v>4.49</v>
@@ -1465,7 +1585,7 @@
         <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C9">
         <v>5.5</v>
@@ -1477,7 +1597,7 @@
         <v>104</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>823341</v>
@@ -1536,17 +1656,23 @@
       <c r="Y9">
         <v>0.8825</v>
       </c>
+      <c r="Z9">
+        <v>4</v>
+      </c>
       <c r="AA9" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB9">
+        <v>-0.64</v>
       </c>
       <c r="AC9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD9">
         <v>4.86</v>
       </c>
       <c r="AE9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF9">
         <v>0.2588</v>
@@ -1556,6 +1682,18 @@
       </c>
       <c r="AH9">
         <v>0</v>
+      </c>
+      <c r="AI9">
+        <v>-0.86</v>
+      </c>
+      <c r="AJ9">
+        <v>0.86</v>
+      </c>
+      <c r="AK9">
+        <v>-0.86</v>
+      </c>
+      <c r="AL9">
+        <v>0.86</v>
       </c>
       <c r="AM9">
         <v>4.86</v>
@@ -1566,7 +1704,7 @@
         <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C10">
         <v>7.5</v>
@@ -1578,7 +1716,7 @@
         <v>-136</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G10">
         <v>823423</v>
@@ -1637,17 +1775,23 @@
       <c r="Y10">
         <v>0.8983</v>
       </c>
+      <c r="Z10">
+        <v>7</v>
+      </c>
       <c r="AA10" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB10">
+        <v>-0.97</v>
       </c>
       <c r="AC10" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD10">
         <v>6.53</v>
       </c>
       <c r="AE10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF10">
         <v>0.2988</v>
@@ -1657,6 +1801,18 @@
       </c>
       <c r="AH10">
         <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0.47</v>
+      </c>
+      <c r="AJ10">
+        <v>0.47</v>
+      </c>
+      <c r="AK10">
+        <v>0.47</v>
+      </c>
+      <c r="AL10">
+        <v>0.47</v>
       </c>
       <c r="AM10">
         <v>6.53</v>
@@ -1667,7 +1823,7 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C11">
         <v>4.5</v>
@@ -1679,31 +1835,31 @@
         <v>-142</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L11">
         <v>6</v>
       </c>
       <c r="S11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:39" x14ac:dyDescent="0.25">
@@ -1711,7 +1867,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C12">
         <v>3.5</v>
@@ -1723,7 +1879,7 @@
         <v>-136</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G12">
         <v>822938</v>
@@ -1782,17 +1938,23 @@
       <c r="Y12">
         <v>0.9953</v>
       </c>
+      <c r="Z12">
+        <v>5</v>
+      </c>
       <c r="AA12" t="s">
         <v>44</v>
       </c>
+      <c r="AB12">
+        <v>-0.63</v>
+      </c>
       <c r="AC12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD12">
         <v>2.87</v>
       </c>
       <c r="AE12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF12">
         <v>0.1366</v>
@@ -1802,6 +1964,18 @@
       </c>
       <c r="AH12">
         <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>2.13</v>
+      </c>
+      <c r="AJ12">
+        <v>2.13</v>
+      </c>
+      <c r="AK12">
+        <v>2.13</v>
+      </c>
+      <c r="AL12">
+        <v>2.13</v>
       </c>
       <c r="AM12">
         <v>2.87</v>
@@ -1812,7 +1986,7 @@
         <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C13">
         <v>3.5</v>
@@ -1824,7 +1998,7 @@
         <v>110</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G13">
         <v>824723</v>
@@ -1883,17 +2057,23 @@
       <c r="Y13">
         <v>0.9954</v>
       </c>
+      <c r="Z13">
+        <v>2</v>
+      </c>
       <c r="AA13" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB13">
+        <v>-0.19</v>
       </c>
       <c r="AC13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD13">
         <v>3.31</v>
       </c>
       <c r="AE13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF13">
         <v>0.1621</v>
@@ -1903,6 +2083,18 @@
       </c>
       <c r="AH13">
         <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>-1.31</v>
+      </c>
+      <c r="AJ13">
+        <v>1.31</v>
+      </c>
+      <c r="AK13">
+        <v>-1.31</v>
+      </c>
+      <c r="AL13">
+        <v>1.31</v>
       </c>
       <c r="AM13">
         <v>3.31</v>
@@ -1913,7 +2105,7 @@
         <v>39</v>
       </c>
       <c r="B14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C14">
         <v>4.5</v>
@@ -1925,7 +2117,7 @@
         <v>-105</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G14">
         <v>824723</v>
@@ -1984,17 +2176,23 @@
       <c r="Y14">
         <v>0.88</v>
       </c>
+      <c r="Z14">
+        <v>3</v>
+      </c>
       <c r="AA14" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB14">
+        <v>0.68</v>
       </c>
       <c r="AC14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD14">
         <v>5.18</v>
       </c>
       <c r="AE14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF14">
         <v>0.2375</v>
@@ -2004,6 +2202,18 @@
       </c>
       <c r="AH14">
         <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>-2.18</v>
+      </c>
+      <c r="AJ14">
+        <v>2.18</v>
+      </c>
+      <c r="AK14">
+        <v>-2.18</v>
+      </c>
+      <c r="AL14">
+        <v>2.18</v>
       </c>
       <c r="AM14">
         <v>5.18</v>
@@ -2014,7 +2224,7 @@
         <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C15">
         <v>4.5</v>
@@ -2026,7 +2236,7 @@
         <v>100</v>
       </c>
       <c r="F15" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G15">
         <v>823586</v>
@@ -2085,17 +2295,23 @@
       <c r="Y15">
         <v>0.9557</v>
       </c>
+      <c r="Z15">
+        <v>4</v>
+      </c>
       <c r="AA15" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB15">
+        <v>0.45</v>
       </c>
       <c r="AC15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD15">
         <v>4.95</v>
       </c>
       <c r="AE15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF15">
         <v>0.2051</v>
@@ -2105,6 +2321,18 @@
       </c>
       <c r="AH15">
         <v>0</v>
+      </c>
+      <c r="AI15">
+        <v>-0.95</v>
+      </c>
+      <c r="AJ15">
+        <v>0.95</v>
+      </c>
+      <c r="AK15">
+        <v>-0.95</v>
+      </c>
+      <c r="AL15">
+        <v>0.95</v>
       </c>
       <c r="AM15">
         <v>4.95</v>
@@ -2115,7 +2343,7 @@
         <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C16">
         <v>3.5</v>
@@ -2127,31 +2355,31 @@
         <v>100</v>
       </c>
       <c r="F16" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L16">
         <v>6</v>
       </c>
       <c r="S16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:39" x14ac:dyDescent="0.25">
@@ -2159,7 +2387,7 @@
         <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C17">
         <v>4.5</v>
@@ -2171,7 +2399,7 @@
         <v>-106</v>
       </c>
       <c r="F17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G17">
         <v>823667</v>
@@ -2230,17 +2458,23 @@
       <c r="Y17">
         <v>0.9597</v>
       </c>
+      <c r="Z17">
+        <v>3</v>
+      </c>
       <c r="AA17" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB17">
+        <v>0.35</v>
       </c>
       <c r="AC17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD17">
         <v>4.85</v>
       </c>
       <c r="AE17" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF17">
         <v>0.2536</v>
@@ -2250,6 +2484,18 @@
       </c>
       <c r="AH17">
         <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>-1.85</v>
+      </c>
+      <c r="AJ17">
+        <v>1.85</v>
+      </c>
+      <c r="AK17">
+        <v>-1.85</v>
+      </c>
+      <c r="AL17">
+        <v>1.85</v>
       </c>
       <c r="AM17">
         <v>4.85</v>
@@ -2260,7 +2506,7 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C18">
         <v>4.5</v>
@@ -2272,7 +2518,7 @@
         <v>-123</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G18">
         <v>823667</v>
@@ -2331,17 +2577,23 @@
       <c r="Y18">
         <v>0.9903</v>
       </c>
+      <c r="Z18">
+        <v>4</v>
+      </c>
       <c r="AA18" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB18">
+        <v>0.82</v>
       </c>
       <c r="AC18" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AD18">
         <v>5.32</v>
       </c>
       <c r="AE18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF18">
         <v>0.2013</v>
@@ -2351,6 +2603,18 @@
       </c>
       <c r="AH18">
         <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>-1.32</v>
+      </c>
+      <c r="AJ18">
+        <v>1.32</v>
+      </c>
+      <c r="AK18">
+        <v>-1.32</v>
+      </c>
+      <c r="AL18">
+        <v>1.32</v>
       </c>
       <c r="AM18">
         <v>5.32</v>
@@ -2361,7 +2625,7 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="C19">
         <v>3.5</v>
@@ -2373,31 +2637,31 @@
         <v>130</v>
       </c>
       <c r="F19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L19">
         <v>3</v>
       </c>
       <c r="S19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AA19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:39" x14ac:dyDescent="0.25">
@@ -2405,7 +2669,7 @@
         <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C20">
         <v>5.5</v>
@@ -2417,7 +2681,7 @@
         <v>135</v>
       </c>
       <c r="F20" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G20">
         <v>823749</v>
@@ -2476,17 +2740,23 @@
       <c r="Y20">
         <v>1.0058</v>
       </c>
+      <c r="Z20">
+        <v>8</v>
+      </c>
       <c r="AA20" t="s">
         <v>44</v>
       </c>
+      <c r="AB20">
+        <v>-0.03</v>
+      </c>
       <c r="AC20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD20">
         <v>5.47</v>
       </c>
       <c r="AE20" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF20">
         <v>0.2938</v>
@@ -2496,6 +2766,18 @@
       </c>
       <c r="AH20">
         <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>2.53</v>
+      </c>
+      <c r="AJ20">
+        <v>2.53</v>
+      </c>
+      <c r="AK20">
+        <v>2.53</v>
+      </c>
+      <c r="AL20">
+        <v>2.53</v>
       </c>
       <c r="AM20">
         <v>5.47</v>
@@ -2506,7 +2788,7 @@
         <v>39</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C21">
         <v>5.5</v>
@@ -2518,7 +2800,7 @@
         <v>-154</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G21">
         <v>823749</v>
@@ -2577,17 +2859,23 @@
       <c r="Y21">
         <v>1.0453</v>
       </c>
+      <c r="Z21">
+        <v>3</v>
+      </c>
       <c r="AA21" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB21">
+        <v>-0.15</v>
       </c>
       <c r="AC21" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD21">
         <v>5.35</v>
       </c>
       <c r="AE21" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF21">
         <v>0.2207</v>
@@ -2597,6 +2885,18 @@
       </c>
       <c r="AH21">
         <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>-2.35</v>
+      </c>
+      <c r="AJ21">
+        <v>2.35</v>
+      </c>
+      <c r="AK21">
+        <v>-2.35</v>
+      </c>
+      <c r="AL21">
+        <v>2.35</v>
       </c>
       <c r="AM21">
         <v>5.35</v>
@@ -2607,7 +2907,7 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C22">
         <v>6.5</v>
@@ -2619,7 +2919,7 @@
         <v>-138</v>
       </c>
       <c r="F22" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G22">
         <v>824639</v>
@@ -2678,17 +2978,23 @@
       <c r="Y22">
         <v>1.0865</v>
       </c>
+      <c r="Z22">
+        <v>5</v>
+      </c>
       <c r="AA22" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB22">
+        <v>-0.4</v>
       </c>
       <c r="AC22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD22">
         <v>6.1</v>
       </c>
       <c r="AE22" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AF22">
         <v>0.2168</v>
@@ -2698,6 +3004,18 @@
       </c>
       <c r="AH22">
         <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>-1.1</v>
+      </c>
+      <c r="AJ22">
+        <v>1.1</v>
+      </c>
+      <c r="AK22">
+        <v>-1.1</v>
+      </c>
+      <c r="AL22">
+        <v>1.1</v>
       </c>
       <c r="AM22">
         <v>6.1</v>
@@ -2708,7 +3026,7 @@
         <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C23">
         <v>3.5</v>
@@ -2720,7 +3038,7 @@
         <v>100</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G23">
         <v>822859</v>
@@ -2779,17 +3097,23 @@
       <c r="Y23">
         <v>0.989</v>
       </c>
+      <c r="Z23">
+        <v>5</v>
+      </c>
       <c r="AA23" t="s">
         <v>44</v>
       </c>
+      <c r="AB23">
+        <v>-0.07</v>
+      </c>
       <c r="AC23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD23">
         <v>3.43</v>
       </c>
       <c r="AE23" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF23">
         <v>0.1733</v>
@@ -2799,6 +3123,18 @@
       </c>
       <c r="AH23">
         <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>1.57</v>
+      </c>
+      <c r="AJ23">
+        <v>1.57</v>
+      </c>
+      <c r="AK23">
+        <v>1.57</v>
+      </c>
+      <c r="AL23">
+        <v>1.57</v>
       </c>
       <c r="AM23">
         <v>3.43</v>
@@ -2809,7 +3145,7 @@
         <v>39</v>
       </c>
       <c r="B24" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C24">
         <v>4.5</v>
@@ -2821,31 +3157,34 @@
         <v>-153</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
       <c r="S24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V24" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="Z24">
+        <v>3</v>
       </c>
       <c r="AA24" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="AC24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE24" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:39" x14ac:dyDescent="0.25">
@@ -2853,7 +3192,7 @@
         <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="C25">
         <v>4.5</v>
@@ -2865,31 +3204,34 @@
         <v>-150</v>
       </c>
       <c r="F25" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L25">
         <v>6</v>
       </c>
       <c r="S25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V25" t="s">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="Z25">
+        <v>7</v>
       </c>
       <c r="AA25" t="s">
         <v>44</v>
       </c>
       <c r="AC25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AE25" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:39" x14ac:dyDescent="0.25">
@@ -2897,7 +3239,7 @@
         <v>39</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C26">
         <v>4.5</v>
@@ -2909,13 +3251,13 @@
         <v>-106</v>
       </c>
       <c r="F26" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="G26">
         <v>824154</v>
       </c>
       <c r="H26" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="I26">
         <v>3.9</v>
@@ -2968,17 +3310,23 @@
       <c r="Y26">
         <v>0.9877</v>
       </c>
+      <c r="Z26">
+        <v>5</v>
+      </c>
       <c r="AA26" t="s">
         <v>44</v>
       </c>
+      <c r="AB26">
+        <v>-1.91</v>
+      </c>
       <c r="AC26" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AD26">
         <v>2.59</v>
       </c>
       <c r="AE26" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF26">
         <v>0.1531</v>
@@ -2988,6 +3336,18 @@
       </c>
       <c r="AH26">
         <v>0</v>
+      </c>
+      <c r="AI26">
+        <v>2.41</v>
+      </c>
+      <c r="AJ26">
+        <v>2.41</v>
+      </c>
+      <c r="AK26">
+        <v>2.41</v>
+      </c>
+      <c r="AL26">
+        <v>2.41</v>
       </c>
       <c r="AM26">
         <v>2.59</v>
@@ -2998,7 +3358,7 @@
         <v>39</v>
       </c>
       <c r="B27" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C27">
         <v>3.5</v>
@@ -3010,7 +3370,7 @@
         <v>-141</v>
       </c>
       <c r="F27" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G27">
         <v>824319</v>
@@ -3069,17 +3429,23 @@
       <c r="Y27">
         <v>0.9839</v>
       </c>
+      <c r="Z27">
+        <v>3</v>
+      </c>
       <c r="AA27" t="s">
-        <v>44</v>
+        <v>56</v>
+      </c>
+      <c r="AB27">
+        <v>-0.82</v>
       </c>
       <c r="AC27" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="AD27">
         <v>2.68</v>
       </c>
       <c r="AE27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF27">
         <v>0.1458</v>
@@ -3089,6 +3455,18 @@
       </c>
       <c r="AH27">
         <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0.32</v>
+      </c>
+      <c r="AJ27">
+        <v>0.32</v>
+      </c>
+      <c r="AK27">
+        <v>0.32</v>
+      </c>
+      <c r="AL27">
+        <v>0.32</v>
       </c>
       <c r="AM27">
         <v>2.68</v>
@@ -3099,7 +3477,7 @@
         <v>39</v>
       </c>
       <c r="B28" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C28">
         <v>3.5</v>
@@ -3111,7 +3489,7 @@
         <v>108</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G28">
         <v>824319</v>
@@ -3170,17 +3548,23 @@
       <c r="Y28">
         <v>1.0214</v>
       </c>
+      <c r="Z28">
+        <v>6</v>
+      </c>
       <c r="AA28" t="s">
         <v>44</v>
       </c>
+      <c r="AB28">
+        <v>0.22</v>
+      </c>
       <c r="AC28" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD28">
         <v>3.72</v>
       </c>
       <c r="AE28" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF28">
         <v>0.1555</v>
@@ -3190,6 +3574,18 @@
       </c>
       <c r="AH28">
         <v>0</v>
+      </c>
+      <c r="AI28">
+        <v>2.28</v>
+      </c>
+      <c r="AJ28">
+        <v>2.28</v>
+      </c>
+      <c r="AK28">
+        <v>2.28</v>
+      </c>
+      <c r="AL28">
+        <v>2.28</v>
       </c>
       <c r="AM28">
         <v>3.72</v>
@@ -3200,7 +3596,7 @@
         <v>39</v>
       </c>
       <c r="B29" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F29" t="s">
         <v>41</v>
@@ -3263,16 +3659,16 @@
         <v>1.0725</v>
       </c>
       <c r="AA29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD29">
         <v>7.38</v>
       </c>
       <c r="AE29" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="AF29">
         <v>0.2735</v>
@@ -3292,10 +3688,10 @@
         <v>39</v>
       </c>
       <c r="B30" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F30" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G30">
         <v>822938</v>
@@ -3355,16 +3751,16 @@
         <v>0.88</v>
       </c>
       <c r="AA30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC30" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD30">
         <v>3.68</v>
       </c>
       <c r="AE30" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF30">
         <v>0.2197</v>
@@ -3384,16 +3780,16 @@
         <v>39</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F31" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G31">
         <v>823423</v>
       </c>
       <c r="H31" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="I31">
         <v>4.5</v>
@@ -3435,16 +3831,16 @@
         <v>0.9664</v>
       </c>
       <c r="AA31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD31">
         <v>2.94</v>
       </c>
       <c r="AE31" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF31">
         <v>0.1859</v>
@@ -3464,10 +3860,10 @@
         <v>39</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G32">
         <v>823586</v>
@@ -3527,16 +3923,16 @@
         <v>1.0025</v>
       </c>
       <c r="AA32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD32">
         <v>2.74</v>
       </c>
       <c r="AE32" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF32">
         <v>0.1509</v>
@@ -3556,16 +3952,16 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="F33" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G33">
         <v>824075</v>
       </c>
       <c r="H33" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I33">
         <v>2.3</v>
@@ -3619,16 +4015,16 @@
         <v>0.924</v>
       </c>
       <c r="AA33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC33" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD33">
         <v>1.75</v>
       </c>
       <c r="AE33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF33">
         <v>0.2027</v>
@@ -3648,16 +4044,16 @@
         <v>39</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F34" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G34">
         <v>824075</v>
       </c>
       <c r="H34" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I34">
         <v>2</v>
@@ -3711,16 +4107,16 @@
         <v>1.0036</v>
       </c>
       <c r="AA34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC34" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD34">
         <v>1.77</v>
       </c>
       <c r="AE34" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF34">
         <v>0.2019</v>
@@ -3740,16 +4136,16 @@
         <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F35" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G35">
         <v>824639</v>
       </c>
       <c r="H35" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I35">
         <v>1.2</v>
@@ -3803,16 +4199,16 @@
         <v>0.889</v>
       </c>
       <c r="AA35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AC35" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AD35">
         <v>1.08</v>
       </c>
       <c r="AE35" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AF35">
         <v>0.2257</v>
